--- a/Results/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04936054212503877</v>
+        <v>0.04936054212503863</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04857456394482008</v>
+        <v>0.04857456394482009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05451882148336122</v>
+        <v>0.05451882148336119</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04901535976758018</v>
+        <v>0.04901535976758015</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04726712286595693</v>
+        <v>0.04726712286595692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05074526474680836</v>
+        <v>0.05074526474680833</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05728563146684275</v>
+        <v>0.05728563146684276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0468540298888346</v>
+        <v>0.04685402988883457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05274292291584149</v>
+        <v>0.0527429229158415</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04898513167732774</v>
+        <v>0.04898513167732776</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06341445224618508</v>
+        <v>0.0634144522461851</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05307643508498634</v>
+        <v>0.05307643508498645</v>
       </c>
       <c r="C3" t="n">
         <v>0.05191313519787825</v>
@@ -567,10 +567,10 @@
         <v>0.05235494290701691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05060670600539367</v>
+        <v>0.05060670600539368</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05466915294444857</v>
+        <v>0.05466915294444854</v>
       </c>
       <c r="H3" t="n">
         <v>0.06219270487443913</v>
@@ -579,13 +579,13 @@
         <v>0.05019219421514458</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05657961126175368</v>
+        <v>0.05657961126175366</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05233540466963064</v>
+        <v>0.05233540466963055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06924070804679802</v>
+        <v>0.06924070804679805</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03815585322045777</v>
+        <v>0.03148318305979071</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0360395463450961</v>
+        <v>0.02988354629654756</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04122223172414293</v>
+        <v>0.03454956156347591</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03625448567217442</v>
+        <v>0.02992137708197926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03625448567217443</v>
+        <v>0.02992137708197927</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03895483881445883</v>
+        <v>0.03230208747688304</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04286561458148003</v>
+        <v>0.03619294442081301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03651216703268886</v>
+        <v>0.02996623159448942</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03863391128040681</v>
+        <v>0.03196124111973983</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03670888096224161</v>
+        <v>0.03003621080157461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04650779654664348</v>
+        <v>0.03983512638597649</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3500827603209681</v>
+        <v>0.08638231841200254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2010722587881278</v>
+        <v>0.05892930352913364</v>
       </c>
       <c r="D5" t="n">
-        <v>0.679325264260632</v>
+        <v>0.1468556946813553</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2010722605649128</v>
+        <v>0.05892930530591878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2010722605649128</v>
+        <v>0.05892930530591878</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4548552905976028</v>
+        <v>0.1055005665940826</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9549689379087017</v>
+        <v>0.196723128456555</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2010716569160126</v>
+        <v>0.05892870165701813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4300399314240333</v>
+        <v>0.100848700291744</v>
       </c>
       <c r="K5" t="n">
-        <v>0.208166800888042</v>
+        <v>0.06021280454500005</v>
       </c>
       <c r="L5" t="n">
-        <v>1.428940242770469</v>
+        <v>0.09901014517374082</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05232322044303437</v>
+        <v>0.03232949854183433</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04090158144726005</v>
+        <v>0.03073926446989163</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04668317147413634</v>
+        <v>0.03551067285667329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.040368549716438</v>
+        <v>0.03064545234984618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04130546652727565</v>
+        <v>0.03081034970766009</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05312220603703543</v>
+        <v>0.03479554409454548</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05761660198516654</v>
+        <v>0.03878911818979424</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05067953425526546</v>
+        <v>0.03081254707653301</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0439643318971837</v>
+        <v>0.03289939514320909</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04123270308930056</v>
+        <v>0.03083240349162273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05169495710569564</v>
+        <v>0.0407480666394228</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04430233078004849</v>
+        <v>0.03256496310441701</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04265924646439513</v>
+        <v>0.03104861351123116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04736792810871994</v>
+        <v>0.03563120412130049</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04264963366393176</v>
+        <v>0.03104692312242966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04264963366393176</v>
+        <v>0.03104692312242966</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04510131637404962</v>
+        <v>0.0333838675215093</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04901209214107079</v>
+        <v>0.03727472446543927</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04265864459227966</v>
+        <v>0.03104801163911566</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04478038883999761</v>
+        <v>0.03304302116436608</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04285535852183235</v>
+        <v>0.03111799084620084</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05265427410623431</v>
+        <v>0.04091690643060276</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0525994742064718</v>
+        <v>0.0340252603395547</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06248054342716673</v>
+        <v>0.0345371617577759</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06958680018710151</v>
+        <v>0.03954172558590609</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05932759460006511</v>
+        <v>0.03398224423128377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05131660864261644</v>
+        <v>0.0325723107104127</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06492856487804433</v>
+        <v>0.03687346323930365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06883934064506587</v>
+        <v>0.04076432018323365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06248589309627435</v>
+        <v>0.03453760735690997</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06460990333843006</v>
+        <v>0.0365330156971793</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0509383243269989</v>
+        <v>0.03254059282020166</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08452568149400011</v>
+        <v>0.04652627410045467</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06837548811745468</v>
+        <v>0.03680183877284255</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07611385734251684</v>
+        <v>0.03693662499387578</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08082332260926896</v>
+        <v>0.04151935352149159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08693984421778291</v>
+        <v>0.03884200013766902</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07611384665452675</v>
+        <v>0.03693662457686041</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07855592725217132</v>
+        <v>0.03927187900415392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08246670301919252</v>
+        <v>0.04316273594808389</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0761132554704014</v>
+        <v>0.03693602312176027</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07823499971811931</v>
+        <v>0.03893103264701069</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06449704417434264</v>
+        <v>0.03604932793474587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08610888498435601</v>
+        <v>0.0468049179132474</v>
       </c>
     </row>
   </sheetData>
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04421399530771697</v>
+        <v>0.04421399530771696</v>
       </c>
       <c r="C2" t="n">
         <v>0.04637051299224005</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04481236449174653</v>
+        <v>0.04481236449174652</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04664975919788156</v>
+        <v>0.04664975919788155</v>
       </c>
       <c r="F2" t="n">
         <v>0.04541983199334675</v>
@@ -935,13 +935,13 @@
         <v>0.04505598741315998</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04750924839939</v>
+        <v>0.04750924839938998</v>
       </c>
       <c r="K2" t="n">
         <v>0.04664035495926889</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04426526290347823</v>
+        <v>0.04426526290347822</v>
       </c>
     </row>
     <row r="3">
@@ -957,13 +957,13 @@
         <v>0.04947887919816502</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04788469264139035</v>
+        <v>0.04788469264139034</v>
       </c>
       <c r="E3" t="n">
         <v>0.04975894903415388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04852902182961907</v>
+        <v>0.04852902182961906</v>
       </c>
       <c r="G3" t="n">
         <v>0.04848067778156485</v>
@@ -972,10 +972,10 @@
         <v>0.04782992733732828</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04816565228239449</v>
+        <v>0.04816565228239448</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05072797249899234</v>
+        <v>0.05072797249899232</v>
       </c>
       <c r="K3" t="n">
         <v>0.04968859279485995</v>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03336152615329261</v>
+        <v>0.02813976088129933</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03331588137972181</v>
+        <v>0.02854503434464875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03371723127814504</v>
+        <v>0.02849546600615177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0334707245658308</v>
+        <v>0.0285722886429858</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03347072456583081</v>
+        <v>0.0285722886429858</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03400598870774638</v>
+        <v>0.0288000965858598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03368885576943691</v>
+        <v>0.02846709049744363</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0337392979951132</v>
+        <v>0.0286194658319526</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03429660575725135</v>
+        <v>0.02907484048525808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03362189180215703</v>
+        <v>0.02840012653016375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03339242271351026</v>
+        <v>0.02817065744151698</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05874209076790311</v>
+        <v>0.03260674022926598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1013648387895294</v>
+        <v>0.04052165078387834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08858240603647151</v>
+        <v>0.03815173671129373</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1013648410925991</v>
+        <v>0.04052165308694817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1013648410925991</v>
+        <v>0.04052165308694817</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1176450819647942</v>
+        <v>0.04352057691933586</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09386508166270749</v>
+        <v>0.03905810619727072</v>
       </c>
       <c r="I5" t="n">
-        <v>0.101364729764528</v>
+        <v>0.04052154175887697</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1500062260426675</v>
+        <v>0.04943973354514201</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07917101663453611</v>
+        <v>0.03641677245722345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08204128406027372</v>
+        <v>0.03402685022714157</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04302118409938824</v>
+        <v>0.0298398606706</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03724412209249287</v>
+        <v>0.02923640470635019</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03727476972128457</v>
+        <v>0.03020522870905466</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0368026765765671</v>
+        <v>0.02915871219369779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03734846195165827</v>
+        <v>0.02925477041919333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04366564665384202</v>
+        <v>0.02943604442154572</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04369878324667379</v>
+        <v>0.0302288377238911</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03735263799018059</v>
+        <v>0.02925541366763852</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0440323560486908</v>
+        <v>0.03078833252726668</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03721244159957793</v>
+        <v>0.02903206329108551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03700475151831954</v>
+        <v>0.02880642730771843</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03719421698989268</v>
+        <v>0.0288143144648858</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03757209785671464</v>
+        <v>0.02929412844054044</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03754926187720674</v>
+        <v>0.02916990338793211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03756332932434207</v>
+        <v>0.02929258707658076</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03756332932434208</v>
+        <v>0.02929258707658076</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03783867954434643</v>
+        <v>0.02947465016944626</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03752154660603696</v>
+        <v>0.0291416440810301</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03757198883171327</v>
+        <v>0.02929401941553908</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03812929659385141</v>
+        <v>0.02974939406884454</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03745458263875709</v>
+        <v>0.02907468011375022</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03722511355011031</v>
+        <v>0.02884521102510345</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04307443189564454</v>
+        <v>0.02984923228269031</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05133730661921138</v>
+        <v>0.03171680516961234</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05295739669513649</v>
+        <v>0.0318817351011934</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04917965871435486</v>
+        <v>0.03133706103814482</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04369760946348294</v>
+        <v>0.03037222037521945</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05160990225194851</v>
+        <v>0.03189838535285096</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05129276931363883</v>
+        <v>0.03156537926443476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05134321153931536</v>
+        <v>0.03171775459894378</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05190207010974172</v>
+        <v>0.03217340219450649</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04318821802340104</v>
+        <v>0.03008379993597954</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05923915374131487</v>
+        <v>0.03271968207776122</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04630650206519188</v>
+        <v>0.0304180766294483</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05101281375082279</v>
+        <v>0.03165969442508541</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05099064181991833</v>
+        <v>0.03153558624503065</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05600773581950686</v>
+        <v>0.03253880260213979</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05101281520040808</v>
+        <v>0.03165969657794195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05127939543845464</v>
+        <v>0.03184021615399124</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05096226250014516</v>
+        <v>0.03150721006557507</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05101270472582146</v>
+        <v>0.03165958540008405</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0515700124879596</v>
+        <v>0.03211496005338952</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04838739032030712</v>
+        <v>0.03099885425527668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05066582944421849</v>
+        <v>0.03121077700964842</v>
       </c>
     </row>
   </sheetData>
@@ -1331,13 +1331,13 @@
         <v>0.04588857282619754</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05056030707685424</v>
+        <v>0.05056030707685425</v>
       </c>
       <c r="K2" t="n">
         <v>0.04677585950629002</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04849091911877938</v>
+        <v>0.04849091911877939</v>
       </c>
     </row>
     <row r="3">
@@ -1350,10 +1350,10 @@
         <v>0.04854375223056143</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04874693603484022</v>
+        <v>0.04874693603484025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05087275266935105</v>
+        <v>0.05087275266935103</v>
       </c>
       <c r="E3" t="n">
         <v>0.0484680252762346</v>
@@ -1368,7 +1368,7 @@
         <v>0.05427972681587408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04896042762603423</v>
+        <v>0.04896042762603424</v>
       </c>
       <c r="J3" t="n">
         <v>0.05419025988726285</v>
@@ -1377,7 +1377,7 @@
         <v>0.04983013586315922</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05195327023514286</v>
+        <v>0.05195327023514285</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03389586560283189</v>
+        <v>0.0285863812641106</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03334591527014713</v>
+        <v>0.02877384853049349</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03509955493261192</v>
+        <v>0.02979007059389048</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03372501391914662</v>
+        <v>0.02873442567317488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03372501391914662</v>
+        <v>0.02873442567317488</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03484304765703117</v>
+        <v>0.02955351265408926</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03685933256427697</v>
+        <v>0.0315498482255556</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0339559826365162</v>
+        <v>0.02877487158367266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03632096301154142</v>
+        <v>0.03101147867282005</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03404267426449838</v>
+        <v>0.028733189925777</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03565797434557345</v>
+        <v>0.03034849000685202</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09677395575354449</v>
+        <v>0.03965292507067077</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1334609322472987</v>
+        <v>0.04639409142299503</v>
       </c>
       <c r="D5" t="n">
-        <v>0.213997387560536</v>
+        <v>0.06127608896579487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1189640796818089</v>
+        <v>0.04373650116611319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1189640796818089</v>
+        <v>0.04373650116611319</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1961882369172389</v>
+        <v>0.05795026581001524</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4313744616070033</v>
+        <v>0.1009845105608365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1189638314008152</v>
+        <v>0.04373625288511954</v>
       </c>
       <c r="J5" t="n">
-        <v>0.348291558234239</v>
+        <v>0.08591830313449651</v>
       </c>
       <c r="K5" t="n">
-        <v>0.111849282916422</v>
+        <v>0.04242715297431342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3048122240337216</v>
+        <v>0.07771963769528059</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04450448159034366</v>
+        <v>0.02924044620978151</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0377040923955713</v>
+        <v>0.02954088770041186</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03891758391704565</v>
+        <v>0.03046203260823541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03702247349063202</v>
+        <v>0.02931477855461161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0376599953122124</v>
+        <v>0.02942698239460178</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04545166364454294</v>
+        <v>0.03142062905777417</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0480878001621003</v>
+        <v>0.03352605851206422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04456459862402798</v>
+        <v>0.03064198798735758</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04699614116518965</v>
+        <v>0.0328903100176815</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03759149477730876</v>
+        <v>0.02935778233264717</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03941245471390953</v>
+        <v>0.03100927854809865</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03853512066024053</v>
+        <v>0.02940289014979017</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03886673543869106</v>
+        <v>0.02974551287489216</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03973816475382273</v>
+        <v>0.03060646591799989</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03859620569582742</v>
+        <v>0.02959175542122517</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03859620569582742</v>
+        <v>0.02959175542122517</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03948230271443975</v>
+        <v>0.03037002153976882</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04149858762168551</v>
+        <v>0.03236635711123517</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03859523769392476</v>
+        <v>0.02959138046935223</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04096021806894998</v>
+        <v>0.03182798755849964</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03868192932190692</v>
+        <v>0.02954969881145658</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04029722940298197</v>
+        <v>0.0311649988925316</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04527846969564456</v>
+        <v>0.03058971957359031</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05482251614136198</v>
+        <v>0.03255373026335639</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05760087977882956</v>
+        <v>0.03375030374536588</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0520321482819016</v>
+        <v>0.03195648130356071</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04563156493910247</v>
+        <v>0.03082997864133213</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05543479637359555</v>
+        <v>0.03317766040856674</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05745108128085571</v>
+        <v>0.03517399598003565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05454773135308045</v>
+        <v>0.03239901933815015</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05691452158727066</v>
+        <v>0.03463594496250886</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04525421376805638</v>
+        <v>0.03070642086771105</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06586944467636892</v>
+        <v>0.03566570875626012</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05123616601713496</v>
+        <v>0.03163827412049094</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05722372254511818</v>
+        <v>0.03297634258811675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05809579946699667</v>
+        <v>0.03383740961001126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06347930596821538</v>
+        <v>0.03397118104543508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05695246819360093</v>
+        <v>0.03282245760332741</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05783928982086689</v>
+        <v>0.03360085125299341</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05985557472811253</v>
+        <v>0.03559718682445975</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05695222480035184</v>
+        <v>0.03282221018257683</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05931720517537714</v>
+        <v>0.03505881727172421</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04991707556924612</v>
+        <v>0.03220376352752549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05865421650940911</v>
+        <v>0.03439582860575618</v>
       </c>
     </row>
   </sheetData>
@@ -1727,7 +1727,7 @@
         <v>0.04522640059213912</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04885372718088334</v>
+        <v>0.04885372718088333</v>
       </c>
       <c r="K2" t="n">
         <v>0.04603590357564784</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04780977774319538</v>
+        <v>0.04780977774319537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04812199627099174</v>
+        <v>0.04812199627099172</v>
       </c>
       <c r="D3" t="n">
         <v>0.04974528702508502</v>
@@ -1764,13 +1764,13 @@
         <v>0.05084815482700214</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04822563488881663</v>
+        <v>0.04822563488881661</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05223523037883755</v>
+        <v>0.05223523037883752</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04899478688717812</v>
+        <v>0.04899478688717813</v>
       </c>
       <c r="L3" t="n">
         <v>0.04875064789026193</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03324177242210853</v>
+        <v>0.02818063076005057</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03283950490767608</v>
+        <v>0.028417454816498</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03424209506331474</v>
+        <v>0.02918095340125682</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03368391105122396</v>
+        <v>0.02843581138364655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03368391105122396</v>
+        <v>0.02843581138364655</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03391056496087475</v>
+        <v>0.02886743487952037</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03481148785952166</v>
+        <v>0.0297503461974637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03331626781114781</v>
+        <v>0.02837095602302417</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03497422976182878</v>
+        <v>0.02991308809977091</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03330167545533202</v>
+        <v>0.02824053379327398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03372832850841616</v>
+        <v>0.02866718684635828</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06276224249871852</v>
+        <v>0.03337623346538104</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1002946653749026</v>
+        <v>0.04028956299439961</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1560725535048625</v>
+        <v>0.05062311397078259</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08431837207671251</v>
+        <v>0.03734747647584372</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08431837207671251</v>
+        <v>0.03734747647584372</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1304283162047506</v>
+        <v>0.04585455900639597</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2318026889358127</v>
+        <v>0.06442079739902545</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0843181898549657</v>
+        <v>0.03734729425409685</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2334634886771573</v>
+        <v>0.06484719747957475</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06981040749557507</v>
+        <v>0.03466607059753937</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1208417394269587</v>
+        <v>0.04399914708494396</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0432154777609294</v>
+        <v>0.02993600289017144</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03706340551934423</v>
+        <v>0.02916086132012337</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03797838314814401</v>
+        <v>0.03094725701810162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03645468054152784</v>
+        <v>0.02892346681129761</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03700273444355944</v>
+        <v>0.02901992429753252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03755914215982815</v>
+        <v>0.02950958446305666</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04539135095950821</v>
+        <v>0.0316124020929716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03696484501010141</v>
+        <v>0.02901310560656044</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0390499877229487</v>
+        <v>0.03063042149704104</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03686895685740971</v>
+        <v>0.02886837531663766</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03735167181405854</v>
+        <v>0.02930489526469584</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03740538021191515</v>
+        <v>0.02891342572708583</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03776701196313838</v>
+        <v>0.02928469605356012</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03840510350629114</v>
+        <v>0.02991364288325052</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03751464439383789</v>
+        <v>0.02911002044829333</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03751464439383789</v>
+        <v>0.02911002044829333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03807417275068134</v>
+        <v>0.02960022984655562</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03897509564932835</v>
+        <v>0.03048314116449896</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0374798756009545</v>
+        <v>0.02910375099005942</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03913783755163547</v>
+        <v>0.03064588306680612</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0374652832451387</v>
+        <v>0.02897332876030923</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03789193629822285</v>
+        <v>0.02939998181339355</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04366016404556156</v>
+        <v>0.03001426767584258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0525358712377333</v>
+        <v>0.0318840152718152</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05489721468801645</v>
+        <v>0.03281625443550604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04992620958560372</v>
+        <v>0.03129445591020753</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04402459121439498</v>
+        <v>0.03025577108250299</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05280758562170033</v>
+        <v>0.0321933104978041</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05370850852038657</v>
+        <v>0.03307622181575426</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0522132884719736</v>
+        <v>0.0316968316413079</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05387291671359123</v>
+        <v>0.03323925698525791</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04356257219167651</v>
+        <v>0.03004645160908504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06148198616787112</v>
+        <v>0.03355183056795441</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04731793079478451</v>
+        <v>0.03065803462021748</v>
       </c>
       <c r="C9" t="n">
-        <v>0.052381486889251</v>
+        <v>0.0318568436266185</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05302018084904959</v>
+        <v>0.03248589648163797</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05752045359234168</v>
+        <v>0.03263104284815095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05209453040743503</v>
+        <v>0.03167608037278195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05268864767679398</v>
+        <v>0.03217237741961398</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05358957057544095</v>
+        <v>0.03305528873755734</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05209435052706715</v>
+        <v>0.0316758985631178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05375231247774813</v>
+        <v>0.0332180306398645</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04935544603204692</v>
+        <v>0.03106599739946573</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0525064112243355</v>
+        <v>0.0319721293864519</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04431929578628559</v>
+        <v>0.04431929578628558</v>
       </c>
       <c r="C2" t="n">
         <v>0.04470136268021706</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04549770614276442</v>
+        <v>0.04549770614276441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04414119539879652</v>
+        <v>0.04414119539879651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04414119539879652</v>
+        <v>0.04414119539879651</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04505958327482625</v>
+        <v>0.04505958327482624</v>
       </c>
       <c r="H2" t="n">
         <v>0.04562836878360062</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04440683324293048</v>
+        <v>0.04440683324293046</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04641514317547563</v>
+        <v>0.04641514317547561</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0456166274220774</v>
+        <v>0.04561662742207738</v>
       </c>
       <c r="L2" t="n">
         <v>0.04457301767817869</v>
@@ -2139,34 +2139,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04730465171247157</v>
+        <v>0.04730465171247156</v>
       </c>
       <c r="C3" t="n">
         <v>0.04777877157522537</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04866006772939217</v>
+        <v>0.04866006772939215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04713996520346097</v>
+        <v>0.04713996520346095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04713996520346096</v>
+        <v>0.04713996520346095</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04815613567438459</v>
+        <v>0.04815613567438456</v>
       </c>
       <c r="H3" t="n">
         <v>0.0488110854566937</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04740703807742842</v>
+        <v>0.04740703807742839</v>
       </c>
       <c r="J3" t="n">
         <v>0.04960776819456565</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04861241045175935</v>
+        <v>0.04861241045175936</v>
       </c>
       <c r="L3" t="n">
         <v>0.04759645078802614</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03287358057820167</v>
+        <v>0.0279311098672963</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03249697423596388</v>
+        <v>0.02816796619460539</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0335740956016458</v>
+        <v>0.02863162489074041</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03310705179907904</v>
+        <v>0.02801594413574099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03310705179907904</v>
+        <v>0.02801594413574099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03329337781493851</v>
+        <v>0.02836761148465688</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03365175578690816</v>
+        <v>0.02870928507600272</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0327964439155947</v>
+        <v>0.02796114554963898</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03369386572113185</v>
+        <v>0.02875139501022644</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03291484673111288</v>
+        <v>0.02797237602020751</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03302468538663616</v>
+        <v>0.02808221467573078</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04441944081280768</v>
+        <v>0.02996318125757594</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08150558228188233</v>
+        <v>0.03679348116394879</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1107336277219759</v>
+        <v>0.04221170247033334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05130825545026828</v>
+        <v>0.03121935596099224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05130825545026828</v>
+        <v>0.03121935596099224</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08839754580359629</v>
+        <v>0.03806594499810918</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1293095403679415</v>
+        <v>0.04554505507103822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05130809574286009</v>
+        <v>0.03121919625358347</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1264998182748313</v>
+        <v>0.04508524257117089</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05022926892732785</v>
+        <v>0.03101971431022902</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0647162766229986</v>
+        <v>0.03365993470310712</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04268646823811884</v>
+        <v>0.02857050195197187</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03671405358824808</v>
+        <v>0.02891017215658554</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03724207100860037</v>
+        <v>0.02927718855886602</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03590477212185324</v>
+        <v>0.02850834290988114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03645804970984077</v>
+        <v>0.02860571976483929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03692628740664411</v>
+        <v>0.03009467970344401</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04402511387052201</v>
+        <v>0.03053499608882597</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03642935350730031</v>
+        <v>0.02968821376842611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0377270684784942</v>
+        <v>0.03048764006187988</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03652576879121545</v>
+        <v>0.02860789829934191</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03661103047134139</v>
+        <v>0.02871341140721871</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03682795778302291</v>
+        <v>0.02862708025157364</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03718540161506206</v>
+        <v>0.02899312940885544</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0375278758203531</v>
+        <v>0.02932749020546228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03679527399701162</v>
+        <v>0.02866507123905976</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03679527399701162</v>
+        <v>0.02866507123905976</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03724775501975975</v>
+        <v>0.02906358186893424</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03760613299172932</v>
+        <v>0.02940525546028006</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03675082112041594</v>
+        <v>0.02865711593391633</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03764824292595301</v>
+        <v>0.0294473653945038</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03686922393593412</v>
+        <v>0.02866834640448485</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03697906259145744</v>
+        <v>0.02877818506000813</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0429558602632894</v>
+        <v>0.02970559108225651</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05161658296840612</v>
+        <v>0.03153301731326971</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05362743584219675</v>
+        <v>0.03216101275395302</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04891864599600452</v>
+        <v>0.03079878469932077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04316744696829157</v>
+        <v>0.02978657367592806</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05163424594246829</v>
+        <v>0.03159560425761092</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05199262391447285</v>
+        <v>0.03193727784896291</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05113731204312455</v>
+        <v>0.03118913832259301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05203635689424429</v>
+        <v>0.03197967343920147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04284371889621372</v>
+        <v>0.02971985751179634</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05999233971086801</v>
+        <v>0.03282852181107723</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04504024605018802</v>
+        <v>0.03007244297876286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0495687142018267</v>
+        <v>0.03117259241231637</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04991178854214377</v>
+        <v>0.03150705883268721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05394756819516432</v>
+        <v>0.03168387500157693</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0491342920619559</v>
+        <v>0.03083673840672254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0496310676065244</v>
+        <v>0.03124304487239516</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04998944557849396</v>
+        <v>0.03158471846374099</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04913413370718055</v>
+        <v>0.03083657893737726</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05003155551271771</v>
+        <v>0.03162682839796471</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04673778101033252</v>
+        <v>0.029923445980045</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04936237517822202</v>
+        <v>0.03095764806346905</v>
       </c>
     </row>
   </sheetData>
@@ -2504,10 +2504,10 @@
         <v>0.04597812734031541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04466064644040632</v>
+        <v>0.04466064644040631</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04466064644040632</v>
+        <v>0.04466064644040631</v>
       </c>
       <c r="G2" t="n">
         <v>0.04603718889682349</v>
@@ -2516,13 +2516,13 @@
         <v>0.04903810941573011</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04510171103180451</v>
+        <v>0.0451017110318045</v>
       </c>
       <c r="J2" t="n">
         <v>0.0501591068466677</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04626700898013247</v>
+        <v>0.04626700898013246</v>
       </c>
       <c r="L2" t="n">
         <v>0.04809061180372443</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04752931644122567</v>
+        <v>0.04752931644122566</v>
       </c>
       <c r="C3" t="n">
         <v>0.04695925694489719</v>
@@ -2550,22 +2550,22 @@
         <v>0.04762008957263598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04913689087259858</v>
+        <v>0.04913689087259857</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05258928637014984</v>
+        <v>0.05258928637014983</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04806277162514939</v>
+        <v>0.04806277162514938</v>
       </c>
       <c r="J3" t="n">
         <v>0.05372703277170814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04924163270945395</v>
+        <v>0.04924163270945394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05149860611079721</v>
+        <v>0.05149860611079719</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03306042717712257</v>
+        <v>0.02803538406051068</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03208267390138222</v>
+        <v>0.02780689316790278</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03385615477863583</v>
+        <v>0.02883111166202395</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03317604240431826</v>
+        <v>0.02828295103119975</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03317604240431824</v>
+        <v>0.02828295103119975</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03386806651557558</v>
+        <v>0.028862138432127</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0356746114405854</v>
+        <v>0.03064956832397351</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03318645816795477</v>
+        <v>0.02828461848997679</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03574430065264441</v>
+        <v>0.03071925753603252</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0333962565250938</v>
+        <v>0.02837121340848191</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03511165680664986</v>
+        <v>0.03008661369003798</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0513923069148926</v>
+        <v>0.03126179487687555</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04702969221678431</v>
+        <v>0.03043756837715896</v>
       </c>
       <c r="D5" t="n">
-        <v>0.130429842209055</v>
+        <v>0.04582808055767787</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08035309962619619</v>
+        <v>0.03658611305725874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08035309962619619</v>
+        <v>0.03658611305725874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1368332322187578</v>
+        <v>0.04698400749769174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3432173816008718</v>
+        <v>0.08477709557888831</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08035289851501549</v>
+        <v>0.03658591194607807</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3283924826804525</v>
+        <v>0.08222533729383562</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0860621851175029</v>
+        <v>0.03764041679051974</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2864073528430967</v>
+        <v>0.07431465595279839</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04308199237711439</v>
+        <v>0.02864650062517602</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03614917644572784</v>
+        <v>0.02852259761182948</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03736135757828721</v>
+        <v>0.02944802735141979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03608228581373119</v>
+        <v>0.02879444986848484</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03666388775135626</v>
+        <v>0.02889681180895217</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0373403197427162</v>
+        <v>0.02947325499679235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04625000190469594</v>
+        <v>0.03251083703557148</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04320802336794659</v>
+        <v>0.02889573505464214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04581827071192128</v>
+        <v>0.03249227625685796</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0367430703970683</v>
+        <v>0.02896025264675766</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03863072334124197</v>
+        <v>0.03070596939677014</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03743317861125993</v>
+        <v>0.02880498830874868</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0373516686203745</v>
+        <v>0.02873423623342052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03822826419545071</v>
+        <v>0.02960060291521379</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03761852212208228</v>
+        <v>0.02906482745728954</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03761852212208228</v>
+        <v>0.02906482745728954</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03824081794971294</v>
+        <v>0.029631742680365</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04004736287472276</v>
+        <v>0.0314191725722115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03755920960209214</v>
+        <v>0.02905422273821478</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04011705208678178</v>
+        <v>0.03148886178427051</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03776900795923117</v>
+        <v>0.02914081765671991</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03948440824078723</v>
+        <v>0.03085621793827596</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04394743447330513</v>
+        <v>0.02995149733425615</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05275489323751489</v>
+        <v>0.03144520375134757</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05540407264578878</v>
+        <v>0.03262354518609316</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05054134162362208</v>
+        <v>0.03133924367723637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0443892085150051</v>
+        <v>0.03025646825598692</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05358503451015229</v>
+        <v>0.03233232478036893</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05539157943516673</v>
+        <v>0.03411975467221624</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05290342616253149</v>
+        <v>0.03175480483821871</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05546300398599922</v>
+        <v>0.03418974930389775</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04411924276810666</v>
+        <v>0.03025845897702593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06405225709866796</v>
+        <v>0.03518015931383325</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04883370569644681</v>
+        <v>0.03081148106486918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0539467885109189</v>
+        <v>0.03165497731833</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05482402821539745</v>
+        <v>0.03252145736689747</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06014897782857061</v>
+        <v>0.03303018764014477</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05415452689282026</v>
+        <v>0.03197516428116946</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05483593784025737</v>
+        <v>0.03255248376527448</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05664248276526718</v>
+        <v>0.03433991365712098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05415432949263659</v>
+        <v>0.03197496382312425</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05671217197732621</v>
+        <v>0.03440960286917999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04782320772888909</v>
+        <v>0.03091035680659127</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05607952813133164</v>
+        <v>0.03377695902318545</v>
       </c>
     </row>
   </sheetData>
@@ -2897,7 +2897,7 @@
         <v>0.04395980093130995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04438356807054804</v>
+        <v>0.04438356807054807</v>
       </c>
       <c r="E2" t="n">
         <v>0.04431896723899847</v>
@@ -2906,16 +2906,16 @@
         <v>0.04431896723899847</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04449742826468388</v>
+        <v>0.04449742826468387</v>
       </c>
       <c r="H2" t="n">
         <v>0.04455718576741326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04463795132025576</v>
+        <v>0.04463795132025578</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04689681084391882</v>
+        <v>0.04689681084391883</v>
       </c>
       <c r="K2" t="n">
         <v>0.04550618071494178</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04715026208129973</v>
+        <v>0.04715026208129972</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04682100424886548</v>
+        <v>0.04682100424886549</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04726159169464774</v>
+        <v>0.04726159169464775</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04723548544142278</v>
+        <v>0.04723548544142279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04723548544142278</v>
+        <v>0.04723548544142279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04739255450397211</v>
+        <v>0.04739255450397212</v>
       </c>
       <c r="H3" t="n">
         <v>0.0474619815033762</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04755708963388187</v>
+        <v>0.04755708963388188</v>
       </c>
       <c r="J3" t="n">
         <v>0.04998231018597801</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04837787818786189</v>
+        <v>0.04837787818786191</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04765305447537462</v>
+        <v>0.04765305447537461</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03256503451594696</v>
+        <v>0.02783663543385497</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03185712907519445</v>
+        <v>0.0277072894725128</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03262257261917944</v>
+        <v>0.02789417353708743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03319134354840479</v>
+        <v>0.02811980998017551</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03319134354840479</v>
+        <v>0.02811980998017551</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03267062796759949</v>
+        <v>0.02795840376848448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03272588270890297</v>
+        <v>0.02799748362681097</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0326483474919062</v>
+        <v>0.02802420001397345</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03344367549841923</v>
+        <v>0.02871527641632722</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03259753633541986</v>
+        <v>0.02786913725332786</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03282500995438552</v>
+        <v>0.02809661087229352</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04151934688425712</v>
+        <v>0.02941259440213805</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04327333728248896</v>
+        <v>0.0297165421061093</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04878405581495215</v>
+        <v>0.03073859456413064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06297689825609486</v>
+        <v>0.03336206758032324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06297689825609486</v>
+        <v>0.03336206758032324</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05565435787827535</v>
+        <v>0.03200354021084447</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06183907865446405</v>
+        <v>0.03312140608546522</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06297684648330833</v>
+        <v>0.03336201580753669</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1291379465095771</v>
+        <v>0.04555746802302986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0465463635922994</v>
+        <v>0.03032413083723602</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07298424299646011</v>
+        <v>0.03516463584939981</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03592168980971833</v>
+        <v>0.02842740676235757</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0357338521720358</v>
+        <v>0.02838959273385976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04185714182070898</v>
+        <v>0.02848097588717783</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03561554372407505</v>
+        <v>0.02854646920878158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0360589839817323</v>
+        <v>0.02862451469370635</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03602728326137085</v>
+        <v>0.02958348500944313</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04238126911133697</v>
+        <v>0.02969683162443126</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03600500278567756</v>
+        <v>0.02964928125493209</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03716922294033224</v>
+        <v>0.02937097276255096</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03592232519043161</v>
+        <v>0.02845430008863917</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03615090632377756</v>
+        <v>0.02868196863013469</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03630953597133611</v>
+        <v>0.02849566768643242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03629414649808935</v>
+        <v>0.02848820453471084</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03636646537078828</v>
+        <v>0.02855309865780014</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03646806063740426</v>
+        <v>0.02869651218471449</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03646806063740426</v>
+        <v>0.02869651218471449</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03641512942298865</v>
+        <v>0.02861743602106194</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03647038416429214</v>
+        <v>0.02865651587938843</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03639284894729536</v>
+        <v>0.0286832322665509</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0371881769538084</v>
+        <v>0.02937430866890468</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03634203779080902</v>
+        <v>0.02852816950590532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03656951140977467</v>
+        <v>0.02875564312487097</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04220142823871463</v>
+        <v>0.02953264071987209</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05011525985183991</v>
+        <v>0.0309207204717901</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05174287599480729</v>
+        <v>0.03125934691296339</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04805774296208189</v>
+        <v>0.03073629626280497</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04257898728131942</v>
+        <v>0.02977203526821573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05016212458656481</v>
+        <v>0.03103690715674118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05021737932788353</v>
+        <v>0.03107598701507035</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05013984411087152</v>
+        <v>0.03110270340223016</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05093671586855802</v>
+        <v>0.03179405150478898</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04208801748919287</v>
+        <v>0.02953946192734109</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05852181838003666</v>
+        <v>0.03261924913070174</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04491297434654112</v>
+        <v>0.03000987283226363</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0490664351768497</v>
+        <v>0.03073612732999206</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04913936576984427</v>
+        <v>0.0308011291158528</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05397595672251867</v>
+        <v>0.0317779018789978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04916518919117185</v>
+        <v>0.03093120679806867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04918741810174899</v>
+        <v>0.03086535881634316</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04924267284305249</v>
+        <v>0.03090443867466966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0491651376260557</v>
+        <v>0.03093115506183213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04996046563256875</v>
+        <v>0.03162223146418591</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04669887950008563</v>
+        <v>0.02985221067479226</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04934180008853504</v>
+        <v>0.03100356592015219</v>
       </c>
     </row>
   </sheetData>
@@ -3308,16 +3308,16 @@
         <v>0.04410052547487259</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04418643127356722</v>
+        <v>0.04418643127356721</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04509205963962698</v>
+        <v>0.04509205963962697</v>
       </c>
       <c r="K2" t="n">
         <v>0.04535877953499767</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04405373786472283</v>
+        <v>0.04405373786472282</v>
       </c>
     </row>
     <row r="3">
@@ -3351,7 +3351,7 @@
         <v>0.04716158966000563</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04808025746148991</v>
+        <v>0.04808025746148992</v>
       </c>
       <c r="K3" t="n">
         <v>0.04830406941261293</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03242839567107235</v>
+        <v>0.02778570759088546</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0318115814235882</v>
+        <v>0.02767890420597318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03247829477484353</v>
+        <v>0.02783560669465665</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03281337459944634</v>
+        <v>0.02794149887305906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03281337459944634</v>
+        <v>0.02794149887305906</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03245394921014227</v>
+        <v>0.0278265270121703</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03248315777666824</v>
+        <v>0.02784046969648135</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03241612200568331</v>
+        <v>0.02787153703193233</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03259592523328229</v>
+        <v>0.02795323715309542</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0324261133781383</v>
+        <v>0.02778342529795141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03245536967848275</v>
+        <v>0.02781268159829587</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03985021308095708</v>
+        <v>0.02909194744794718</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04236608817195896</v>
+        <v>0.02953649738362105</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04646843939719003</v>
+        <v>0.03029787213484758</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05178925455085179</v>
+        <v>0.03128125372640959</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05178925455085179</v>
+        <v>0.03128125372640959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0463153711010847</v>
+        <v>0.03026613725175685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04898133315594974</v>
+        <v>0.03074414854750101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05178919947196439</v>
+        <v>0.03128119864752219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05864718307785624</v>
+        <v>0.03253825850889603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04171644929721622</v>
+        <v>0.02941852441084917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04639876428964996</v>
+        <v>0.03026671903656383</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04163100371475058</v>
+        <v>0.02940536659779655</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03567073781648515</v>
+        <v>0.02835811572744265</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03582384323044627</v>
+        <v>0.02842442321965217</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03538712576399261</v>
+        <v>0.02839447907556468</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03584791967602864</v>
+        <v>0.02847557880364358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04165655725382049</v>
+        <v>0.02944618601908134</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04207105819956517</v>
+        <v>0.02952794016176747</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03580786531960782</v>
+        <v>0.02846848385194845</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04178696736172962</v>
+        <v>0.02957086055893688</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03581963579405003</v>
+        <v>0.02838068523991565</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0358012514836431</v>
+        <v>0.02840155679281321</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0360151856458261</v>
+        <v>0.02841698262302149</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03600813832255338</v>
+        <v>0.02841749821618891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03606447071381062</v>
+        <v>0.02846677365649482</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03606416092100335</v>
+        <v>0.0285136372625529</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03606416092100335</v>
+        <v>0.0285136372625529</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03604073918489602</v>
+        <v>0.0284578020443063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.036069947751422</v>
+        <v>0.02847174472861739</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03600291198043707</v>
+        <v>0.02850281206406838</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03618271520803606</v>
+        <v>0.02858451218523145</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03601290335289206</v>
+        <v>0.02841470033008744</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03604215965323651</v>
+        <v>0.0284439566304319</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04181956016181225</v>
+        <v>0.02943855253229957</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04953504529331513</v>
+        <v>0.03079823383014271</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05111995349569626</v>
+        <v>0.03111653861174866</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0474278699656929</v>
+        <v>0.03051365004358099</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04208707943116583</v>
+        <v>0.0295736709145976</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04950688892627819</v>
+        <v>0.03082784438594723</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0495360974928209</v>
+        <v>0.03084178707026126</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04946906172181922</v>
+        <v>0.03087285440570932</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04965037070626147</v>
+        <v>0.03095481954007535</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04167495646060973</v>
+        <v>0.029411221671646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05751167428345008</v>
+        <v>0.03222259118487455</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04362786600756167</v>
+        <v>0.02975681435942694</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04745572693748917</v>
+        <v>0.03043227380150032</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04751267619500421</v>
+        <v>0.03048165781026703</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05187596079600693</v>
+        <v>0.03129651402547422</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04745055547590565</v>
+        <v>0.0305176426933568</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04748832779983179</v>
+        <v>0.03047257762961772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04751753636635778</v>
+        <v>0.03048652031392881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04745050059537284</v>
+        <v>0.0305175876493798</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04763030382297184</v>
+        <v>0.03059928777054288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04523853225556206</v>
+        <v>0.03002254499067234</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04748974826817227</v>
+        <v>0.03045873221574332</v>
       </c>
     </row>
   </sheetData>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04447386074692466</v>
+        <v>0.04447386074692464</v>
       </c>
       <c r="C2" t="n">
         <v>0.04402048185594255</v>
@@ -3692,10 +3692,10 @@
         <v>0.04468943978892762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04453184495428528</v>
+        <v>0.04453184495428526</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04453184495428528</v>
+        <v>0.04453184495428526</v>
       </c>
       <c r="G2" t="n">
         <v>0.04501911348703946</v>
@@ -3707,13 +3707,13 @@
         <v>0.0449019533399457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04625313793214086</v>
+        <v>0.04625313793214085</v>
       </c>
       <c r="K2" t="n">
         <v>0.0457495231720273</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04724735163482828</v>
+        <v>0.04724735163482827</v>
       </c>
     </row>
     <row r="3">
@@ -3723,28 +3723,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04734615710466367</v>
+        <v>0.04734615710466365</v>
       </c>
       <c r="C3" t="n">
         <v>0.04687762477213697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0475941176600311</v>
+        <v>0.04759411766003108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04746871989787496</v>
+        <v>0.04746871989787498</v>
       </c>
       <c r="F3" t="n">
         <v>0.04746871989787495</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04797331070456055</v>
+        <v>0.04797331070456053</v>
       </c>
       <c r="H3" t="n">
         <v>0.05153557856001211</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04784112467415649</v>
+        <v>0.04784112467415648</v>
       </c>
       <c r="J3" t="n">
         <v>0.04923803365003036</v>
@@ -3753,7 +3753,7 @@
         <v>0.04864573116023757</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05053607825344544</v>
+        <v>0.05053607825344543</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03287628371082139</v>
+        <v>0.02795438511579888</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03194387514886084</v>
+        <v>0.02774391641624895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03300443631643327</v>
+        <v>0.02808253772141074</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03304728745462984</v>
+        <v>0.02819507579783887</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03304728745462984</v>
+        <v>0.02819507579783887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03317891190226292</v>
+        <v>0.02827473050884923</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03504053956783576</v>
+        <v>0.03011864097281323</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03299301752238701</v>
+        <v>0.02818545084280188</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0333219052983952</v>
+        <v>0.02840000670337266</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03297091603127015</v>
+        <v>0.0280490174362476</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03452464715030934</v>
+        <v>0.02960274855528685</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04829912292822282</v>
+        <v>0.03066880480335317</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04511880169526585</v>
+        <v>0.03006270347585164</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06264929202536952</v>
+        <v>0.03330003229791198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07530864963423946</v>
+        <v>0.03563307550114685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07530864963423946</v>
+        <v>0.03563307550114685</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08309284898812028</v>
+        <v>0.03705958338835841</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2903700134517088</v>
+        <v>0.07505662813287368</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07530856049951387</v>
+        <v>0.03563298636642113</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09669927069155948</v>
+        <v>0.03955442295212824</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05951541483936169</v>
+        <v>0.0327208492011569</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2377763517765404</v>
+        <v>0.06537504837566745</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04252856804665853</v>
+        <v>0.02853356897156548</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03587103306894261</v>
+        <v>0.02843509620643811</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03626324917963094</v>
+        <v>0.02865608878222564</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03579257381749169</v>
+        <v>0.02867824619508445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03629742410109309</v>
+        <v>0.02876709984451683</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04283119623810003</v>
+        <v>0.02997353254275143</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04522276439140765</v>
+        <v>0.03191071253205138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.036283834902529</v>
+        <v>0.02988425287670407</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04300950526507127</v>
+        <v>0.03010502428826885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03615233243227716</v>
+        <v>0.02860894671979081</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03784856305622016</v>
+        <v>0.03018775775155722</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03700255890754701</v>
+        <v>0.02868060954648746</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03693558742633883</v>
+        <v>0.02862245777232461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03713007190924503</v>
+        <v>0.02880864958181112</v>
       </c>
       <c r="E7" t="n">
-        <v>0.037188936753091</v>
+        <v>0.02892400607041825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.037188936753091</v>
+        <v>0.02892400607041825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03730518709898854</v>
+        <v>0.02900095493953781</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03916681476456135</v>
+        <v>0.03084486540350181</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03711929271911261</v>
+        <v>0.02891167527349046</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03744818049512079</v>
+        <v>0.02912623113406126</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03709719122799573</v>
+        <v>0.02877524186693619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03865092234703499</v>
+        <v>0.03032897298597543</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04334574954544512</v>
+        <v>0.0297970110927082</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05186774015252345</v>
+        <v>0.03125051663789269</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05376062507248165</v>
+        <v>0.03173562692268059</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04971395588503814</v>
+        <v>0.03112840942569616</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04377451895763277</v>
+        <v>0.03008306853213711</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05216841535533013</v>
+        <v>0.03161688309847926</v>
       </c>
       <c r="H8" t="n">
-        <v>0.054030043020906</v>
+        <v>0.0334607935624438</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05198252097545419</v>
+        <v>0.03152760343243192</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05231308318141114</v>
+        <v>0.03174245399267207</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04328211779305539</v>
+        <v>0.0298637889364883</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06241404232839973</v>
+        <v>0.03451128208003337</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04740824767151322</v>
+        <v>0.03051201075902186</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0521731563749807</v>
+        <v>0.03130426989275389</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05236828143946313</v>
+        <v>0.03149057444459719</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0579328349720195</v>
+        <v>0.03257493213716676</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05235694760651721</v>
+        <v>0.03159357596615592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05254275604763038</v>
+        <v>0.03168276705996709</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05440438371320318</v>
+        <v>0.03352667752393111</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05235686166775445</v>
+        <v>0.03159348739391973</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05268574944376262</v>
+        <v>0.03180804325449055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04942156648104751</v>
+        <v>0.03096432263988124</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05388849129567683</v>
+        <v>0.03301078510640471</v>
       </c>
     </row>
   </sheetData>
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04405115315925065</v>
+        <v>0.04405115315925064</v>
       </c>
       <c r="C2" t="n">
         <v>0.04397299325052333</v>
@@ -4091,7 +4091,7 @@
         <v>0.04429372209950589</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04429372209950589</v>
+        <v>0.04429372209950588</v>
       </c>
       <c r="G2" t="n">
         <v>0.04412051772604712</v>
@@ -4100,16 +4100,16 @@
         <v>0.04410991396737469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0443470687843364</v>
+        <v>0.04434706878433642</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04575682459147193</v>
+        <v>0.04575682459147194</v>
       </c>
       <c r="K2" t="n">
         <v>0.04555458180423323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04406476748778148</v>
+        <v>0.04406476748778149</v>
       </c>
     </row>
     <row r="3">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04691557029293211</v>
+        <v>0.04691557029293213</v>
       </c>
       <c r="C3" t="n">
         <v>0.04683216071055831</v>
@@ -4137,16 +4137,16 @@
         <v>0.04699535391357477</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04698383203464498</v>
+        <v>0.04698383203464499</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04725926630276704</v>
+        <v>0.04725926630276703</v>
       </c>
       <c r="J3" t="n">
         <v>0.04867029337698866</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04842893917452698</v>
+        <v>0.04842893917452697</v>
       </c>
       <c r="L3" t="n">
         <v>0.04693117233696365</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0325513953423582</v>
+        <v>0.02784530868844816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03183042840184561</v>
+        <v>0.02770395900011721</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03257707523126912</v>
+        <v>0.02787098857735908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03320588539770383</v>
+        <v>0.02810638450806517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03320588539770383</v>
+        <v>0.02810638450806517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03257326221561938</v>
+        <v>0.02788313431784581</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03258644383700417</v>
+        <v>0.02788035718309413</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03260352722007929</v>
+        <v>0.02800033550974281</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03274552144515953</v>
+        <v>0.02803943479124947</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03259073467798228</v>
+        <v>0.02788464802407226</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03255963244526908</v>
+        <v>0.02785354579135903</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04321800762656992</v>
+        <v>0.02972263244029695</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04384904094897067</v>
+        <v>0.02981923479694937</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04749301622816108</v>
+        <v>0.03049619417858712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06158361445383613</v>
+        <v>0.03310086479488131</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06158361445383613</v>
+        <v>0.03310086479488131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0493916875343599</v>
+        <v>0.03084317715790484</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05060342715423773</v>
+        <v>0.03105134622974488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06158357324068699</v>
+        <v>0.03310082358173222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06463912075143799</v>
+        <v>0.03365270823873837</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04882084389552147</v>
+        <v>0.03074114723088089</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04815597163873963</v>
+        <v>0.03059850147453601</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04175308420168527</v>
+        <v>0.02843322426143715</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03569996729833452</v>
+        <v>0.02838499784220897</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03589807237809022</v>
+        <v>0.02845547274700811</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03556948341799319</v>
+        <v>0.02852237775738199</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03600106359197158</v>
+        <v>0.0285983358675906</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03591369162570276</v>
+        <v>0.0284710498908348</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04219664517259658</v>
+        <v>0.0295717526089934</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03594395663016264</v>
+        <v>0.02961983274020897</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03643136064944647</v>
+        <v>0.02965764371401469</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0359115804849673</v>
+        <v>0.02846911688293461</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03586110701069991</v>
+        <v>0.02843460531172633</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03622736257171808</v>
+        <v>0.02849227891730983</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03620057290255641</v>
+        <v>0.02847310442807461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03625243589414939</v>
+        <v>0.02851785205052091</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03637081578111769</v>
+        <v>0.0286634122525277</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03637081578111769</v>
+        <v>0.0286634122525277</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03624922944497924</v>
+        <v>0.02853010454670747</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03626241106636407</v>
+        <v>0.0285273274119558</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03627949444943919</v>
+        <v>0.02864730573860448</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03642148867451941</v>
+        <v>0.02868640502011113</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03626670190734219</v>
+        <v>0.02853161825293392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03623559967462896</v>
+        <v>0.02850051602022071</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04207091497461927</v>
+        <v>0.02952074413464759</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04990382062151823</v>
+        <v>0.03088487601354345</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05147798467574234</v>
+        <v>0.03119754862156103</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04784811061990351</v>
+        <v>0.03068341613320838</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04242420596701852</v>
+        <v>0.02972880891947327</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04986297209448645</v>
+        <v>0.03092612324003765</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04987615371588341</v>
+        <v>0.0309233461052881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04989323709894637</v>
+        <v>0.03104332443193466</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05003675838731302</v>
+        <v>0.03108269247657827</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04196591903732192</v>
+        <v>0.02953468046237515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05796595576792398</v>
+        <v>0.03232505867191693</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04475265775124508</v>
+        <v>0.02999273086077621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04884951764312714</v>
+        <v>0.03069931869035208</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04890199016487463</v>
+        <v>0.030744173590105</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05368708718233238</v>
+        <v>0.0317110760026274</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04892848035685773</v>
+        <v>0.03087356120588202</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04889817418555002</v>
+        <v>0.03075631880898494</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0489113558069348</v>
+        <v>0.03075354167423328</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04892843919000992</v>
+        <v>0.03087352000088196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04907043341509016</v>
+        <v>0.03091261928238861</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04372323501359535</v>
+        <v>0.03033732319678949</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04888454441519974</v>
+        <v>0.03072673028249818</v>
       </c>
     </row>
   </sheetData>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04394561500805</v>
+        <v>0.04394561500805001</v>
       </c>
       <c r="C2" t="n">
         <v>0.04392945291084427</v>
@@ -4502,10 +4502,10 @@
         <v>0.04509203688285734</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04544716009394</v>
+        <v>0.04544716009393999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04396340835991331</v>
+        <v>0.0439634083599133</v>
       </c>
     </row>
     <row r="3">
@@ -4539,10 +4539,10 @@
         <v>0.04706543712407904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04807304666854807</v>
+        <v>0.04807304666854809</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04839692401290451</v>
+        <v>0.0483969240129045</v>
       </c>
       <c r="L3" t="n">
         <v>0.04690777579791711</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03242462114030664</v>
+        <v>0.02779706912519234</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0317869610886603</v>
+        <v>0.02767590475036771</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03244996245028033</v>
+        <v>0.02782241043516602</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03282725186054016</v>
+        <v>0.02794350023672484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03282725186054017</v>
+        <v>0.02794350023672484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03243451617562636</v>
+        <v>0.02782205707891132</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03245610490995914</v>
+        <v>0.02782855289484484</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03239860140816943</v>
+        <v>0.02786801149795799</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03257997441856071</v>
+        <v>0.02795242240344641</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03245631623154208</v>
+        <v>0.02782876421642778</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03243533290406219</v>
+        <v>0.02780778088894788</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04133791532520315</v>
+        <v>0.02936580889323375</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04262462767271075</v>
+        <v>0.02958333405882498</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04565127045825848</v>
+        <v>0.03014584063198044</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05184046482570003</v>
+        <v>0.03128982570046051</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05184046482570003</v>
+        <v>0.03128982570046051</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0462967833961647</v>
+        <v>0.03026181609650592</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04819026970547579</v>
+        <v>0.03059776588385051</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05184040868545912</v>
+        <v>0.03128976956021984</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05898521796759092</v>
+        <v>0.03259974524289372</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04629750539321562</v>
+        <v>0.03026481349568233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04633679991724279</v>
+        <v>0.0302544390700102</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04164055592096878</v>
+        <v>0.02839734624331992</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0356706325732864</v>
+        <v>0.02835943092795816</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03581087380441161</v>
+        <v>0.02841393083028792</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03539124664938104</v>
+        <v>0.02839476331711562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03585085461452851</v>
+        <v>0.02847565431854325</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04165045095628853</v>
+        <v>0.02944406159151886</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04205288823263537</v>
+        <v>0.02951758675048365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03580926687055722</v>
+        <v>0.02949001601056553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04178494883913497</v>
+        <v>0.02861369440338655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03587801133875081</v>
+        <v>0.02843098255203333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03579952347861117</v>
+        <v>0.02839987842686004</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03596321621304576</v>
+        <v>0.02841986185461975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03594323905486459</v>
+        <v>0.02840740966845593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03598794548194429</v>
+        <v>0.02844509544536479</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03600775731643217</v>
+        <v>0.02850326919392867</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03600775731643217</v>
+        <v>0.02850326919392867</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03597311124836548</v>
+        <v>0.02844484980833874</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03599469998269825</v>
+        <v>0.02845134562427225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03593719648090857</v>
+        <v>0.02849080422738541</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03611856949129982</v>
+        <v>0.02857521513287383</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03599491130428119</v>
+        <v>0.02845155694585519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03597392797680131</v>
+        <v>0.0284305736183753</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04172961491531568</v>
+        <v>0.02943474802072</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04937814830197051</v>
+        <v>0.03077195368313404</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05092949863855602</v>
+        <v>0.03107480878667909</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04728642272484541</v>
+        <v>0.03048831429505323</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04198694828197818</v>
+        <v>0.02955560679816256</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04933837764545979</v>
+        <v>0.03079713668148123</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04935996637980841</v>
+        <v>0.03080363249741753</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04930246287800286</v>
+        <v>0.03084309110052789</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0494853292820287</v>
+        <v>0.03092776484329457</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04162015713796804</v>
+        <v>0.02944160020721942</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05727684708672983</v>
+        <v>0.03217988736140667</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04359214017319651</v>
+        <v>0.02976255246433077</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04739468519266736</v>
+        <v>0.03042286417778825</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04744000649405453</v>
+        <v>0.03046065817257465</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05179981067311872</v>
+        <v>0.03128267056964501</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04738869860738098</v>
+        <v>0.03050631485028195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04742455738616824</v>
+        <v>0.03046030431767107</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04744614612050105</v>
+        <v>0.03046680013360459</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04738864261871133</v>
+        <v>0.03050625873671774</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0475700156291026</v>
+        <v>0.03059066964220616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0451417176059394</v>
+        <v>0.03006139484622395</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04742537411460405</v>
+        <v>0.03044602812770763</v>
       </c>
     </row>
   </sheetData>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04813567707127261</v>
+        <v>0.04813567707127263</v>
       </c>
       <c r="C2" t="n">
         <v>0.04715415737312478</v>
@@ -4880,7 +4880,7 @@
         <v>0.04887256225451098</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04756386901056671</v>
+        <v>0.0475638690105667</v>
       </c>
       <c r="F2" t="n">
         <v>0.04592079409050116</v>
@@ -4889,10 +4889,10 @@
         <v>0.04893101094214602</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05565301983342468</v>
+        <v>0.05565301983342469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04555698138073592</v>
+        <v>0.04555698138073593</v>
       </c>
       <c r="J2" t="n">
         <v>0.05216697397116644</v>
@@ -4901,7 +4901,7 @@
         <v>0.04818729315976187</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06257474246420616</v>
+        <v>0.06257474246420615</v>
       </c>
     </row>
     <row r="3">
@@ -4914,28 +4914,28 @@
         <v>0.05167250166799837</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05030259251821577</v>
+        <v>0.05030259251821578</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05252007227402833</v>
+        <v>0.05252007227402834</v>
       </c>
       <c r="E3" t="n">
         <v>0.05071354296457876</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04907046804451323</v>
+        <v>0.04907046804451322</v>
       </c>
       <c r="G3" t="n">
         <v>0.05258730037241779</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06031967562840722</v>
+        <v>0.06031967562840725</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04870521160514289</v>
+        <v>0.04870521160514291</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05595090036425042</v>
+        <v>0.05595090036425043</v>
       </c>
       <c r="K3" t="n">
         <v>0.05142830425906715</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03643027080177254</v>
+        <v>0.03058175394805642</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03395975161689761</v>
+        <v>0.0288844219530574</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03686831781873384</v>
+        <v>0.03101980096501772</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03415575549937559</v>
+        <v>0.02891892149828424</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03415575549937559</v>
+        <v>0.02891892149828424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0368769743469911</v>
+        <v>0.03104995461494515</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04089758969039697</v>
+        <v>0.03504907283668087</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03473036029009127</v>
+        <v>0.02901961002217229</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03740819727167725</v>
+        <v>0.03155968041796114</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03525956361329392</v>
+        <v>0.02941104675957781</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04501086485703555</v>
+        <v>0.03916234800331944</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.268275680505455</v>
+        <v>0.07138654583479956</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1230414276069627</v>
+        <v>0.04456279684235391</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3167894634734066</v>
+        <v>0.08028592233328656</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1230414310803817</v>
+        <v>0.04456280031577338</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1230414310803817</v>
+        <v>0.04456280031577338</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3270866787215339</v>
+        <v>0.08212686230809899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7956616788165959</v>
+        <v>0.1678875518030927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1230408947712444</v>
+        <v>0.0445622640066357</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3911723140454994</v>
+        <v>0.09382216463277802</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1612981067122396</v>
+        <v>0.05159383022479246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3516945009083148</v>
+        <v>0.09313866765586827</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04835543887418283</v>
+        <v>0.03268058351742792</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03832030359368984</v>
+        <v>0.02965187909681429</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04102913873230746</v>
+        <v>0.0317521054418386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03785917250887068</v>
+        <v>0.02957072288842353</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03868993182363024</v>
+        <v>0.02971693652702893</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04089121710767393</v>
+        <v>0.03314878418431663</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04509562352156308</v>
+        <v>0.03723563721061221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04665552836250157</v>
+        <v>0.03111843959154377</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04940237881907308</v>
+        <v>0.03367065635886427</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03902677990504164</v>
+        <v>0.03007407682333271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04935951001666559</v>
+        <v>0.03992770954726715</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04152388226834914</v>
+        <v>0.03147822956131627</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03982450459238608</v>
+        <v>0.02991661847115031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04196121902209698</v>
+        <v>0.03191615157195266</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03981528071114589</v>
+        <v>0.02991499793015847</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03981528071114589</v>
+        <v>0.02991499793015847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0419705858135677</v>
+        <v>0.03194643022820499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04599120115697359</v>
+        <v>0.03594554844994071</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03982397175666788</v>
+        <v>0.02991608563543212</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04250180873825387</v>
+        <v>0.03245615603122098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04035317507987052</v>
+        <v>0.03030752237283764</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05010447632361214</v>
+        <v>0.04005882361657927</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04871684923635572</v>
+        <v>0.03274419174082567</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05687020899279256</v>
+        <v>0.03291666242936581</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06105791115985342</v>
+        <v>0.03527716936998579</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05417439310840666</v>
+        <v>0.03244220169838245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04732490103603016</v>
+        <v>0.03123669110017637</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05902229356337402</v>
+        <v>0.03494753077590913</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0630429089067803</v>
+        <v>0.03894664899764495</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05687567950647426</v>
+        <v>0.03291718618313627</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05955545401172119</v>
+        <v>0.03545759758308761</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0473630108764769</v>
+        <v>0.03154125346635527</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07745446319323902</v>
+        <v>0.04487242127955064</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05717032690388538</v>
+        <v>0.03423200380224903</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06209985268518734</v>
+        <v>0.03383707971423991</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06423727808115565</v>
+        <v>0.03583673794510288</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06974945734833221</v>
+        <v>0.0351834129897558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0620998453745757</v>
+        <v>0.0338370812896699</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06424593390636896</v>
+        <v>0.03586689147129458</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06826654924977488</v>
+        <v>0.03986600969303033</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0620993198494692</v>
+        <v>0.03383654687852171</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06477715683105514</v>
+        <v>0.03637661727431057</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05878771077151767</v>
+        <v>0.03355200063698701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07237982441641344</v>
+        <v>0.04397928485966886</v>
       </c>
     </row>
   </sheetData>
@@ -5273,7 +5273,7 @@
         <v>0.04728472908213835</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04871657388533213</v>
+        <v>0.04871657388533209</v>
       </c>
       <c r="E2" t="n">
         <v>0.0477004271871258</v>
@@ -5282,7 +5282,7 @@
         <v>0.04604645718902977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04859355407270719</v>
+        <v>0.04859355407270718</v>
       </c>
       <c r="H2" t="n">
         <v>0.05371048465540602</v>
@@ -5291,7 +5291,7 @@
         <v>0.04569086881958675</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05059689030526415</v>
+        <v>0.05059689030526414</v>
       </c>
       <c r="K2" t="n">
         <v>0.04812914590431018</v>
@@ -5313,16 +5313,16 @@
         <v>0.05045033577748717</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0523375613995318</v>
+        <v>0.05233756139953175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05086713019579593</v>
+        <v>0.05086713019579592</v>
       </c>
       <c r="F3" t="n">
         <v>0.0492131601976999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05219606313153573</v>
+        <v>0.05219606313153571</v>
       </c>
       <c r="H3" t="n">
         <v>0.05808220257251902</v>
@@ -5334,10 +5334,10 @@
         <v>0.05414134989457739</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05135904306216104</v>
+        <v>0.05135904306216105</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06665379888029931</v>
+        <v>0.06665379888029933</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03560185747424891</v>
+        <v>0.0299696459675139</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03397026463733855</v>
+        <v>0.02895381108456386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03651541630522169</v>
+        <v>0.03088320479848666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03414323197608517</v>
+        <v>0.0289842556898364</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03414323197608517</v>
+        <v>0.0289842556898364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03641808780372029</v>
+        <v>0.03080581580801488</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03948303128560448</v>
+        <v>0.0338508197788695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03456210946664884</v>
+        <v>0.02905758936423668</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03621255050442106</v>
+        <v>0.03058033899768603</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03496764280768096</v>
+        <v>0.02933543130094594</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0439121753236511</v>
+        <v>0.03827996381691606</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2061970238706003</v>
+        <v>0.05999439509057947</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1235538841336842</v>
+        <v>0.04472052803048716</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2861698803179938</v>
+        <v>0.07482239022664519</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1235538869902595</v>
+        <v>0.04472053088706249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1235538869902595</v>
+        <v>0.04472053088706249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2864168418544998</v>
+        <v>0.07480559628253471</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6283564854187196</v>
+        <v>0.1374925471447039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1235534151898483</v>
+        <v>0.04472005908665106</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2779988621485073</v>
+        <v>0.07313472961645991</v>
       </c>
       <c r="K5" t="n">
-        <v>0.144307318576364</v>
+        <v>0.04857921413195968</v>
       </c>
       <c r="L5" t="n">
-        <v>1.126017934303805</v>
+        <v>0.09600052653895078</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03954401836714502</v>
+        <v>0.03194683270929957</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0381630854567921</v>
+        <v>0.0296917475447891</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04059998346881074</v>
+        <v>0.03160208861538297</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03771250882406785</v>
+        <v>0.02961244841167743</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03846558898178157</v>
+        <v>0.02974499051871684</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0403602486966164</v>
+        <v>0.03278300254980052</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05109911013039156</v>
+        <v>0.03589524964447405</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03850427035954494</v>
+        <v>0.03103477610602233</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04059007121352886</v>
+        <v>0.03256170044246768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03875718378081167</v>
+        <v>0.03000239050860296</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04810728437087208</v>
+        <v>0.03901830300522618</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0401985777652461</v>
+        <v>0.03077866873434565</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0391592987014821</v>
+        <v>0.02986708107490448</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04111147371840582</v>
+        <v>0.03169211089882393</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03914821340648812</v>
+        <v>0.0298651324168142</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03914821340648812</v>
+        <v>0.0298651324168142</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04101480809471751</v>
+        <v>0.03161483857484661</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04407975157660172</v>
+        <v>0.0346598425457012</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03915882975764603</v>
+        <v>0.02986661213106841</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04080927079541823</v>
+        <v>0.03138936176451775</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03956436309867815</v>
+        <v>0.03014445406777767</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04850889561464826</v>
+        <v>0.03908898658374779</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04676770918105361</v>
+        <v>0.03193483585726294</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05469249421006526</v>
+        <v>0.03260092346960972</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05851377187294356</v>
+        <v>0.03475491535742643</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05223939974450073</v>
+        <v>0.03216918119981969</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04600661499642399</v>
+        <v>0.03107221109010222</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05655602334149002</v>
+        <v>0.03435009244345733</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05962096682337576</v>
+        <v>0.03739509641431219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05470004500441866</v>
+        <v>0.03260186599967912</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05635224931242866</v>
+        <v>0.03412492596868865</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04596683345115508</v>
+        <v>0.03127128884370773</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07342220265511634</v>
+        <v>0.04347372859911101</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05315815472719933</v>
+        <v>0.0330595542672902</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05779131568750295</v>
+        <v>0.03314631604667527</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0597441551199446</v>
+        <v>0.03497146280772524</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06433718493314765</v>
+        <v>0.03429839138148421</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05779131013319711</v>
+        <v>0.03314631742293554</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05964682508073835</v>
+        <v>0.03489407354661742</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06271176856262255</v>
+        <v>0.037939077517472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05779084674366693</v>
+        <v>0.0331458471028392</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05944128778143911</v>
+        <v>0.03466859673628854</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05105376516889518</v>
+        <v>0.03216658882117872</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06714091260066912</v>
+        <v>0.04236822155551855</v>
       </c>
     </row>
   </sheetData>
@@ -5663,22 +5663,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04668477750059652</v>
+        <v>0.04668477750059651</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04749288024203218</v>
+        <v>0.04749288024203219</v>
       </c>
       <c r="D2" t="n">
         <v>0.04788020633593394</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04778040548624193</v>
+        <v>0.04778040548624195</v>
       </c>
       <c r="F2" t="n">
         <v>0.04652577874162486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04793014558496272</v>
+        <v>0.0479301455849627</v>
       </c>
       <c r="H2" t="n">
         <v>0.05095301115744733</v>
@@ -5690,10 +5690,10 @@
         <v>0.04840588692657549</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04779978784971848</v>
+        <v>0.04779978784971847</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0594712225860637</v>
+        <v>0.05947122258606372</v>
       </c>
     </row>
     <row r="3">
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05004685556881285</v>
+        <v>0.05004685556881282</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05077685677102943</v>
+        <v>0.05077685677102944</v>
       </c>
       <c r="D3" t="n">
         <v>0.0514218463617881</v>
@@ -5715,25 +5715,25 @@
         <v>0.0510653555051311</v>
       </c>
       <c r="F3" t="n">
-        <v>0.049810728760514</v>
+        <v>0.04981072876051402</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05147928684305544</v>
+        <v>0.05147928684305547</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0549567837139198</v>
+        <v>0.05495678371391979</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04945421965123694</v>
+        <v>0.04945421965123695</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05176216284833962</v>
+        <v>0.05176216284833961</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05102708126490071</v>
+        <v>0.0510270812649007</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0647533234802516</v>
+        <v>0.06475332348025155</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03532918021205661</v>
+        <v>0.02968384859269762</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03439037972984697</v>
+        <v>0.02926709924101203</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03603981200004806</v>
+        <v>0.03039448038068906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03455532088456487</v>
+        <v>0.02929613089560027</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03455532088456487</v>
+        <v>0.02929613089560027</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03604705003472184</v>
+        <v>0.03042021617118537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03786589233545966</v>
+        <v>0.03222056071610066</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03487966572834549</v>
+        <v>0.02935295548492841</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03530621772177322</v>
+        <v>0.02966088610241421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03479575843252458</v>
+        <v>0.02915042681316557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04292780111395997</v>
+        <v>0.03728246949460096</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1771223247602433</v>
+        <v>0.0546394418979539</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1480084490980571</v>
+        <v>0.04926387934146233</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2369701101770344</v>
+        <v>0.06575821266821653</v>
       </c>
       <c r="E5" t="n">
-        <v>0.148008451539216</v>
+        <v>0.0492638817826215</v>
       </c>
       <c r="F5" t="n">
-        <v>0.148008451539216</v>
+        <v>0.0492638817826215</v>
       </c>
       <c r="G5" t="n">
-        <v>0.246997173823033</v>
+        <v>0.06754743775675004</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4444964136305087</v>
+        <v>0.1037875320762363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1480081358803962</v>
+        <v>0.04926356612380147</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1906510138473723</v>
+        <v>0.05700157007237127</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1248844798591766</v>
+        <v>0.04500604169834101</v>
       </c>
       <c r="L5" t="n">
-        <v>1.005954872527151</v>
+        <v>0.2067752331449083</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03929883384568608</v>
+        <v>0.03038250762843064</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03862935800320781</v>
+        <v>0.03001315941308092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04715131504470575</v>
+        <v>0.03235010490595206</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03817231493693922</v>
+        <v>0.02993272184536874</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03884280256601069</v>
+        <v>0.03005072766744589</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0400167036683513</v>
+        <v>0.0311188752069184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04933155740807588</v>
+        <v>0.0342385177579466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04599019594029028</v>
+        <v>0.03130840879163487</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04643161708961935</v>
+        <v>0.03043277412099627</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03865037336583621</v>
+        <v>0.02982883903775237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04716941569705256</v>
+        <v>0.03802899365718014</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03978611519263991</v>
+        <v>0.0304682691450298</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03933691392658949</v>
+        <v>0.03013768925492134</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04049608193368327</v>
+        <v>0.03117878388475903</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03932524137235682</v>
+        <v>0.03013563689690271</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03932524137235682</v>
+        <v>0.03013563689690271</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04050398501530508</v>
+        <v>0.03120463672351754</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04232282731604292</v>
+        <v>0.03300498126843284</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03933660070892876</v>
+        <v>0.0301373760372606</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03976315270235649</v>
+        <v>0.0304453066547464</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03925269341310783</v>
+        <v>0.02993484736549776</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04738473609454325</v>
+        <v>0.0380668900469332</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04619539331855285</v>
+        <v>0.03159630208907811</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05448769172624965</v>
+        <v>0.03280422613321259</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05747053554997048</v>
+        <v>0.03416628770503746</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05209536135818927</v>
+        <v>0.03238317800223069</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04601699171519827</v>
+        <v>0.03131338495086106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05566337987770978</v>
+        <v>0.03387269020484364</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05748222217844973</v>
+        <v>0.03567303474975932</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0544959955713334</v>
+        <v>0.0328054295185867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05492426721216549</v>
+        <v>0.03311366279401401</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04549943362842244</v>
+        <v>0.03103427363743577</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07168435955993979</v>
+        <v>0.042343623753669</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05108361873357363</v>
+        <v>0.03245662975746</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05579479812208617</v>
+        <v>0.03303427685763327</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05695463351226077</v>
+        <v>0.03407548894689257</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0617497649215316</v>
+        <v>0.03408235302017178</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05579479447432477</v>
+        <v>0.03303427822714249</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05696186921080175</v>
+        <v>0.0341012243262295</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0587807115115396</v>
+        <v>0.0359015688711448</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05579448490442544</v>
+        <v>0.03303396363997255</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05622103689785315</v>
+        <v>0.03334189425745836</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0527206337735408</v>
+        <v>0.03230520485608993</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06384262029003988</v>
+        <v>0.04096347764964511</v>
       </c>
     </row>
   </sheetData>
@@ -6068,7 +6068,7 @@
         <v>0.04536189474035609</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04656899454941796</v>
+        <v>0.04656899454941795</v>
       </c>
       <c r="F2" t="n">
         <v>0.04496779195236376</v>
@@ -6083,7 +6083,7 @@
         <v>0.04458265367327593</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04939037202529342</v>
+        <v>0.0493903720252934</v>
       </c>
       <c r="K2" t="n">
         <v>0.04728039668282919</v>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04768159012424299</v>
+        <v>0.04768159012424298</v>
       </c>
       <c r="C3" t="n">
         <v>0.04917060296974166</v>
@@ -6120,7 +6120,7 @@
         <v>0.05126531533553971</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04758019224530651</v>
+        <v>0.0475801922453065</v>
       </c>
       <c r="J3" t="n">
         <v>0.05276204286157685</v>
@@ -6129,7 +6129,7 @@
         <v>0.05038075577518447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0518654096186949</v>
+        <v>0.05186540961869491</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03380720061821742</v>
+        <v>0.02843943117507396</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03293354423596728</v>
+        <v>0.02824322261081936</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03421794338250613</v>
+        <v>0.02885017393936268</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03311806102752229</v>
+        <v>0.02827570034344961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03311806102752229</v>
+        <v>0.02827570034344961</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03439147066535708</v>
+        <v>0.02904119560552483</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03565868772734044</v>
+        <v>0.03029091828419699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03361922817302359</v>
+        <v>0.02836372069283287</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03523597459516519</v>
+        <v>0.02986820515202173</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03416223518940747</v>
+        <v>0.02879446574626403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03596919569031203</v>
+        <v>0.03060142624716859</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0850705638877423</v>
+        <v>0.0374617830616218</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08025096549332508</v>
+        <v>0.03657108870698893</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1194172374040381</v>
+        <v>0.04384524960589991</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08025096886406852</v>
+        <v>0.03657109207773229</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08025096886406852</v>
+        <v>0.03657109207773229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1419815440325099</v>
+        <v>0.04797704841553782</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2713530276495307</v>
+        <v>0.07177312188572671</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08025074426728838</v>
+        <v>0.03657086748095219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2372540613635611</v>
+        <v>0.06542338823059986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1162414061573339</v>
+        <v>0.04324039975834226</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1734039012607883</v>
+        <v>0.08236441270286723</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03737423872432007</v>
+        <v>0.02906722987834624</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03693971605442112</v>
+        <v>0.02894830884704664</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03779116595979975</v>
+        <v>0.03066560042023459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03650040210586323</v>
+        <v>0.02887099237001196</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03713790550804371</v>
+        <v>0.02898319296818776</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04459862247545196</v>
+        <v>0.0296689943087971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04631270134084142</v>
+        <v>0.0321660246700127</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04382637998311847</v>
+        <v>0.02899151939610514</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04554511099443224</v>
+        <v>0.03168261314846117</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0376460760401015</v>
+        <v>0.02940762173266372</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03959144930266147</v>
+        <v>0.03123894287948763</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0380712637019066</v>
+        <v>0.02918990627373674</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03788351248274952</v>
+        <v>0.02911441701753237</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03848130634342918</v>
+        <v>0.02960052581641927</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03787408271256986</v>
+        <v>0.0291127601554823</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03787408271256986</v>
+        <v>0.0291127601554823</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03865553374904628</v>
+        <v>0.02979167070418761</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03992275081102963</v>
+        <v>0.03104139338285977</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03788329125671278</v>
+        <v>0.02911419579149564</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03950003767885438</v>
+        <v>0.03061868025068451</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03842629827309667</v>
+        <v>0.0295449408449268</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04023325877400121</v>
+        <v>0.03135190134583136</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04454037688562618</v>
+        <v>0.03032847018790195</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05305263377981263</v>
+        <v>0.03178418235134079</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05546290425380208</v>
+        <v>0.03258928703245001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05067200748554709</v>
+        <v>0.03136519490332124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04462340027122275</v>
+        <v>0.03030064003936856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05383109318839578</v>
+        <v>0.03246256915104058</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05509831025037935</v>
+        <v>0.03371229182971277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05305885069606229</v>
+        <v>0.03178509423834861</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05467730818334406</v>
+        <v>0.03328987984500052</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04473368474779158</v>
+        <v>0.03065504085845791</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0645034293476343</v>
+        <v>0.03562345134364494</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05008115701654241</v>
+        <v>0.03130364748565911</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05521524602499828</v>
+        <v>0.03216480210443933</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05581374235893225</v>
+        <v>0.03265103453861831</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06135653759574621</v>
+        <v>0.03324567219252671</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05521524563077153</v>
+        <v>0.03216480481254796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05598726729129507</v>
+        <v>0.03284205579109455</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05725448435327843</v>
+        <v>0.03409177846976671</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05521502479896154</v>
+        <v>0.03216458087840259</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05683177122110317</v>
+        <v>0.03366906533759145</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04905688441446454</v>
+        <v>0.03205263096617807</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05756499231625</v>
+        <v>0.03440228643273831</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04479928358268692</v>
+        <v>0.04479928358268693</v>
       </c>
       <c r="C2" t="n">
         <v>0.04670833181785636</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04485995585638371</v>
+        <v>0.04485995585638373</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04710966531160651</v>
+        <v>0.04710966531160649</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0454969338954699</v>
+        <v>0.04549693389546989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04533694200977977</v>
+        <v>0.04533694200977978</v>
       </c>
       <c r="H2" t="n">
         <v>0.04442002365324354</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04510756655810863</v>
+        <v>0.04510756655810864</v>
       </c>
       <c r="J2" t="n">
         <v>0.04888849546385498</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04759600566249214</v>
+        <v>0.04759600566249213</v>
       </c>
       <c r="L2" t="n">
         <v>0.04403887290941185</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0478293054130719</v>
+        <v>0.04782930541307191</v>
       </c>
       <c r="C3" t="n">
         <v>0.04978406493315583</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04789909109604686</v>
+        <v>0.04789909109604687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05018626301291633</v>
+        <v>0.05018626301291635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04857353159677973</v>
+        <v>0.04857353159677974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04844772397983633</v>
+        <v>0.04844772397983635</v>
       </c>
       <c r="H3" t="n">
         <v>0.04739372203257431</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04818458593456552</v>
+        <v>0.04818458593456551</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05218206798899894</v>
+        <v>0.05218206798899893</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05074224195847289</v>
+        <v>0.05074224195847288</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04695468867915285</v>
+        <v>0.04695468867915283</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03370328864284061</v>
+        <v>0.02848720385505611</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03328387289947597</v>
+        <v>0.02856527074823381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03373935573865102</v>
+        <v>0.02852327095086655</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03344244595144352</v>
+        <v>0.0285931818041815</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03344244595144352</v>
+        <v>0.0285931818041815</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03400438208517749</v>
+        <v>0.0288035591864916</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03347816235265996</v>
+        <v>0.02826207756487548</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03376871956750094</v>
+        <v>0.02865051961633846</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03474631303345631</v>
+        <v>0.0295302282456718</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03416321731906587</v>
+        <v>0.02894713253128138</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03325173616771272</v>
+        <v>0.02803565137992823</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08948418858718776</v>
+        <v>0.03830464219206439</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1027409278149114</v>
+        <v>0.04078971234711104</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08866504088258637</v>
+        <v>0.03819019148381792</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1027409304835433</v>
+        <v>0.04078971501574287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1027409304835433</v>
+        <v>0.04078971501574287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1150464524499592</v>
+        <v>0.0430669634934054</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07185530122691973</v>
+        <v>0.03501645397014591</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1027408256971866</v>
+        <v>0.0407896102293862</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1854009610196816</v>
+        <v>0.05604544614757198</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1253418933898326</v>
+        <v>0.04499457943278155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07502050067036406</v>
+        <v>0.03538695389256104</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03730141667473649</v>
+        <v>0.0301820087471482</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03721996991531107</v>
+        <v>0.02925802381926704</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03729264303447792</v>
+        <v>0.02914863981012885</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03678447203061163</v>
+        <v>0.02918137839092789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03733327225354522</v>
+        <v>0.02927796722964082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03760251011707338</v>
+        <v>0.02943682971667383</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04338601434760882</v>
+        <v>0.0288850951019925</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03736684759939683</v>
+        <v>0.02928379014652068</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03871329472349553</v>
+        <v>0.03123027725060555</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03778024951537533</v>
+        <v>0.02958373019438238</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03677780899768664</v>
+        <v>0.02865624019464091</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03752922163112945</v>
+        <v>0.02916056805734626</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03759475467351461</v>
+        <v>0.02932398593635344</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03756463037662468</v>
+        <v>0.02919651928350185</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03758629089080016</v>
+        <v>0.0293224985095564</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03758629089080017</v>
+        <v>0.0293224985095564</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03783031507346633</v>
+        <v>0.02947692338878174</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03730409534094879</v>
+        <v>0.02893544176716563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03759465255578977</v>
+        <v>0.0293238838186286</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03857224602174513</v>
+        <v>0.03020359244796194</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03798915030735471</v>
+        <v>0.02962049673357152</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03707766915600156</v>
+        <v>0.02870901558221837</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0434001251117046</v>
+        <v>0.03019384706432854</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05133783948721716</v>
+        <v>0.03174276885045866</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05294764295165249</v>
+        <v>0.03190392948203635</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04918374794379524</v>
+        <v>0.03136365093982332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04371072062029376</v>
+        <v>0.03040039813610656</v>
       </c>
       <c r="G8" t="n">
-        <v>0.051579132517979</v>
+        <v>0.03189671524590407</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05105291278546012</v>
+        <v>0.03135523362428771</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05134347000030242</v>
+        <v>0.03174367567575092</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05232261170122664</v>
+        <v>0.03262365679443732</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04371371749158245</v>
+        <v>0.03062802055253623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05905562647552548</v>
+        <v>0.03257713604949476</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04759778030743866</v>
+        <v>0.03093263437477456</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05225308218006958</v>
+        <v>0.03190385156352783</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0522236203345917</v>
+        <v>0.03177650150212413</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05754958379439089</v>
+        <v>0.03283603804154987</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05225308431038138</v>
+        <v>0.03190385413741533</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0524886425800213</v>
+        <v>0.03205678901595613</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05196242284750384</v>
+        <v>0.03151530739434003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05225298006234476</v>
+        <v>0.03190374944580299</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05323057352830008</v>
+        <v>0.03278345807513635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0498802569759404</v>
+        <v>0.03171333149590237</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05173599666255655</v>
+        <v>0.03128888120939276</v>
       </c>
     </row>
   </sheetData>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04545583177263487</v>
+        <v>0.04545583177263488</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04657755796613759</v>
+        <v>0.04657755796613761</v>
       </c>
       <c r="D2" t="n">
         <v>0.0445019104916545</v>
@@ -6869,19 +6869,19 @@
         <v>0.04520895681747606</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04431986442473775</v>
+        <v>0.04431986442473776</v>
       </c>
       <c r="I2" t="n">
         <v>0.04525943445231268</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04785606386925942</v>
+        <v>0.04785606386925943</v>
       </c>
       <c r="K2" t="n">
         <v>0.04744744080515337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04424223992821974</v>
+        <v>0.04424223992821975</v>
       </c>
     </row>
     <row r="3">
@@ -6894,7 +6894,7 @@
         <v>0.04863190208107698</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04972360932158836</v>
+        <v>0.04972360932158837</v>
       </c>
       <c r="D3" t="n">
         <v>0.0475346950037515</v>
@@ -6906,16 +6906,16 @@
         <v>0.04877717668457935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04834794474265145</v>
+        <v>0.04834794474265146</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04732592445815126</v>
+        <v>0.04732592445815127</v>
       </c>
       <c r="I3" t="n">
         <v>0.0484068858477542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05113457046903153</v>
+        <v>0.05113457046903154</v>
       </c>
       <c r="K3" t="n">
         <v>0.05061962921297047</v>
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03411347885559657</v>
+        <v>0.0288820579757534</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03346743517283686</v>
+        <v>0.02867305441830041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03354641307512719</v>
+        <v>0.02831499219528406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03362069372993402</v>
+        <v>0.02870002980639543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03362069372993402</v>
+        <v>0.02870002980639543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03394805171481197</v>
+        <v>0.02873201527830625</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03343851514642875</v>
+        <v>0.02820709426658551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03387782515173644</v>
+        <v>0.02874522966478781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03451887923004486</v>
+        <v>0.02928745835020167</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03409811590222808</v>
+        <v>0.02886669502238479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03339244293578421</v>
+        <v>0.02816102205594099</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1234812863418311</v>
+        <v>0.04461079200810288</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1121356112918617</v>
+        <v>0.04251865334022485</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07332490386827666</v>
+        <v>0.03531600653694261</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1121356135760754</v>
+        <v>0.04251865562443859</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1121356135760754</v>
+        <v>0.04251865562443859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1109094484413149</v>
+        <v>0.04227722102877477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06833996727216153</v>
+        <v>0.03434974980742988</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1121355464988914</v>
+        <v>0.04251858854725476</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1658389909490082</v>
+        <v>0.0523997978875026</v>
       </c>
       <c r="K5" t="n">
-        <v>0.116966788379179</v>
+        <v>0.04345158129929846</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09396024005776123</v>
+        <v>0.0337658609425437</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03779507036316323</v>
+        <v>0.02953001807757407</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03743786963107995</v>
+        <v>0.02937185087916472</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04326558993020557</v>
+        <v>0.02894059484227154</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03699447582264029</v>
+        <v>0.02929381545149424</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03752703870624834</v>
+        <v>0.02938754651850137</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03762964322237833</v>
+        <v>0.03045213835789244</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0434275299898465</v>
+        <v>0.02996516086950078</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03755941665930301</v>
+        <v>0.0293931897666085</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03855673965977539</v>
+        <v>0.03100227418030637</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03780236359968099</v>
+        <v>0.02951864261360386</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03703819954271501</v>
+        <v>0.02880267521528395</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03789485198674598</v>
+        <v>0.02954757964322948</v>
       </c>
       <c r="C7" t="n">
-        <v>0.037659263075856</v>
+        <v>0.02941081612523414</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03732712563895537</v>
+        <v>0.02898039760291226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03765059169492016</v>
+        <v>0.02940929184438979</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03765059169492016</v>
+        <v>0.02940929184438979</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03772942484596144</v>
+        <v>0.02939753694578233</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03721988827757816</v>
+        <v>0.0288726159340616</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03765919828288576</v>
+        <v>0.0294107513322639</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03830025236119428</v>
+        <v>0.02995298001767775</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03787948903337712</v>
+        <v>0.02953221668986087</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03717381606693361</v>
+        <v>0.02882654372341707</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04372360267941199</v>
+        <v>0.03057343975957995</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0512945603035115</v>
+        <v>0.03181062842430477</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0525889888252464</v>
+        <v>0.03166648550914456</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04915838006177434</v>
+        <v>0.03143466258598143</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04373087949087726</v>
+        <v>0.03047942249067962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05137065827583415</v>
+        <v>0.03179839401643068</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05086112170744935</v>
+        <v>0.03127347300470966</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05130043171275882</v>
+        <v>0.03181160840291226</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05194302116698373</v>
+        <v>0.03235410731448594</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04356311884831859</v>
+        <v>0.03053253553187024</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05897584098428336</v>
+        <v>0.03266370008807866</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04696837345234032</v>
+        <v>0.03114451941252094</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05103054946048585</v>
+        <v>0.03176416251617715</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05069907640437357</v>
+        <v>0.03133386092487336</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05599008420782484</v>
+        <v>0.03263704250917111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05103055128598006</v>
+        <v>0.03176416471965621</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05110071123059101</v>
+        <v>0.03175088333672533</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05059117466220771</v>
+        <v>0.03122596232500461</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05103048466751562</v>
+        <v>0.03176409772320691</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05167153874582377</v>
+        <v>0.03230632640862077</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04876063514922249</v>
+        <v>0.03142951741676344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05054510245156318</v>
+        <v>0.03117989011436008</v>
       </c>
     </row>
   </sheetData>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04656467280826546</v>
+        <v>0.04656467280826547</v>
       </c>
       <c r="C2" t="n">
         <v>0.04686055980496729</v>
@@ -7262,7 +7262,7 @@
         <v>0.04563962472635834</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0482983889733619</v>
+        <v>0.04829838897336189</v>
       </c>
       <c r="H2" t="n">
         <v>0.05537095096182688</v>
@@ -7274,10 +7274,10 @@
         <v>0.05021135187530338</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0480699285553664</v>
+        <v>0.04806992855536639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06002803151487082</v>
+        <v>0.06002803151487083</v>
       </c>
     </row>
     <row r="3">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04986317585134687</v>
+        <v>0.04986317585134688</v>
       </c>
       <c r="C3" t="n">
         <v>0.04996462794909365</v>
@@ -7302,22 +7302,22 @@
         <v>0.04874488771672641</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05185730857942941</v>
+        <v>0.0518573085794294</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05999279402570188</v>
+        <v>0.05999279402570185</v>
       </c>
       <c r="I3" t="n">
         <v>0.04838092518691943</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05370646797419536</v>
+        <v>0.05370646797419537</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05129162849016619</v>
+        <v>0.05129162849016618</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06534821361906702</v>
+        <v>0.06534821361906701</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03534914014487898</v>
+        <v>0.02962525156227637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03366153677448934</v>
+        <v>0.02869806496090568</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03657589475615195</v>
+        <v>0.03085200617354936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03385548385513348</v>
+        <v>0.02873220250529033</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03385548385513348</v>
+        <v>0.02873220250529032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03635443348382984</v>
+        <v>0.03065141472615994</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04058259240864132</v>
+        <v>0.03485870382603874</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03442153548138411</v>
+        <v>0.02883142585563099</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03612725311062725</v>
+        <v>0.03040336452802465</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03504518528228197</v>
+        <v>0.02932129669967937</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04335013335115835</v>
+        <v>0.03762624476855576</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1818905132778959</v>
+        <v>0.05541653309393463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1098469503216531</v>
+        <v>0.04210669767255042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2937301264309526</v>
+        <v>0.07611115070307273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1098469537905565</v>
+        <v>0.04210670114145363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1098469537905564</v>
+        <v>0.04210670114145363</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2851060243077748</v>
+        <v>0.07443169447394629</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7193623899152111</v>
+        <v>0.1543239475398603</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1098464662476691</v>
+        <v>0.0421062135985663</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2766844290948274</v>
+        <v>0.0727414272718306</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1545393450470642</v>
+        <v>0.05035226870432259</v>
       </c>
       <c r="L5" t="n">
-        <v>1.121167005540719</v>
+        <v>0.2273220132460323</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0392354257740011</v>
+        <v>0.03030923782929562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03791242507141113</v>
+        <v>0.02944622129710994</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04063751980637193</v>
+        <v>0.03156685217851461</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0374603306156145</v>
+        <v>0.02936665553169714</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03825461648842214</v>
+        <v>0.02950644984455379</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04787558144049182</v>
+        <v>0.03267913675554504</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05266860365315509</v>
+        <v>0.03698584179354705</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03830782111050623</v>
+        <v>0.03085914788501608</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04777631418261299</v>
+        <v>0.03245359926558473</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03872936084690996</v>
+        <v>0.0299697115955404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04752396129072835</v>
+        <v>0.03836083848193963</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04021747127521055</v>
+        <v>0.03048207783657194</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03929035068569982</v>
+        <v>0.02968873620391067</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04144351917019902</v>
+        <v>0.03170870806577951</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03928050130657774</v>
+        <v>0.02968700557157082</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03928050130657774</v>
+        <v>0.02968700557157082</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04122276461416142</v>
+        <v>0.0315082410004555</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04545092353897293</v>
+        <v>0.03571553010033429</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03928986661171569</v>
+        <v>0.02968825212992655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04099558424095885</v>
+        <v>0.0312601908023202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03991351641261357</v>
+        <v>0.03017812297397494</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04821846448148994</v>
+        <v>0.03848307104285131</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04722764618125921</v>
+        <v>0.03171586861335108</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05585110363011752</v>
+        <v>0.03260342870634399</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0599934003137366</v>
+        <v>0.03497348712935158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05323781551043387</v>
+        <v>0.03214349285813876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04659802279366786</v>
+        <v>0.03097488934632014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0577901824585841</v>
+        <v>0.03442410652527397</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06201834138339678</v>
+        <v>0.03863139562515298</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05585728445613838</v>
+        <v>0.03260411765474503</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05756488035614352</v>
+        <v>0.034176386902791</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04674616062448644</v>
+        <v>0.03138066834874845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07476922173749785</v>
+        <v>0.04315600429458793</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0551591348213484</v>
+        <v>0.03311181060644271</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06058533168815253</v>
+        <v>0.03343665284003387</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06273920686854406</v>
+        <v>0.03545674908037909</v>
       </c>
       <c r="E9" t="n">
-        <v>0.067916915676158</v>
+        <v>0.03472701447330714</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06058532468108638</v>
+        <v>0.03343665446516648</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06251774561661416</v>
+        <v>0.03525615763657871</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06674590454142562</v>
+        <v>0.03946344673645751</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06058484761416842</v>
+        <v>0.03343616876604977</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06229056524341153</v>
+        <v>0.03500810743844342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05737801193984244</v>
+        <v>0.03327815948503513</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06951344548394268</v>
+        <v>0.04223098767897455</v>
       </c>
     </row>
   </sheetData>
@@ -7652,7 +7652,7 @@
         <v>0.04823070594531392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04686391635222415</v>
+        <v>0.04686391635222414</v>
       </c>
       <c r="F2" t="n">
         <v>0.04523375070463324</v>
@@ -7664,7 +7664,7 @@
         <v>0.04552108798598484</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04487543094897554</v>
+        <v>0.04487543094897555</v>
       </c>
       <c r="J2" t="n">
         <v>0.04916114538519303</v>
@@ -7673,7 +7673,7 @@
         <v>0.04677578579918763</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05346787732729388</v>
+        <v>0.05346787732729387</v>
       </c>
     </row>
     <row r="3">
@@ -7689,16 +7689,16 @@
         <v>0.04949680057114327</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05177586884558173</v>
+        <v>0.05177586884558175</v>
       </c>
       <c r="E3" t="n">
         <v>0.0499053158564606</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04827515020886971</v>
+        <v>0.0482751502088697</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05010099700525509</v>
+        <v>0.0501009970052551</v>
       </c>
       <c r="H3" t="n">
         <v>0.04865995020917587</v>
@@ -7707,13 +7707,13 @@
         <v>0.04791629461154485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05249400223856165</v>
+        <v>0.05249400223856166</v>
       </c>
       <c r="K3" t="n">
         <v>0.04980561149214539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05779932982238101</v>
+        <v>0.057799329822381</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03357206252113906</v>
+        <v>0.02825186550377759</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03317327712324501</v>
+        <v>0.02842298341706814</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0358585967942875</v>
+        <v>0.03053839977692606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03333883398291298</v>
+        <v>0.02845212369982419</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03333883398291298</v>
+        <v>0.02845212369982419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03497104017632687</v>
+        <v>0.02966892034627971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03424825565870582</v>
+        <v>0.02892805864134439</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03372400966320798</v>
+        <v>0.02851963998124475</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03501837747559606</v>
+        <v>0.02969818045823462</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03381910576920137</v>
+        <v>0.02849890875183993</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03897057016458553</v>
+        <v>0.03365037314722411</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06378901895782263</v>
+        <v>0.03357004980781676</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0882332093171677</v>
+        <v>0.03811353143068929</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2513590220133392</v>
+        <v>0.06846647440996192</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08823321207883322</v>
+        <v>0.03811353419235477</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08823321207883322</v>
+        <v>0.03811353419235477</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1874017262187868</v>
+        <v>0.05649672094438346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1291016852687961</v>
+        <v>0.04562226216226095</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08823287878035783</v>
+        <v>0.03811320089387941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2052197417973689</v>
+        <v>0.05965362041654998</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08372961171634949</v>
+        <v>0.03728315775093961</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6263676041788587</v>
+        <v>0.04503130954644046</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03724030066776621</v>
+        <v>0.03005885915427998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03713015788620146</v>
+        <v>0.0291193944275749</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0397714452375741</v>
+        <v>0.03122706109921277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0366928827484258</v>
+        <v>0.02904243627935578</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03735544140648733</v>
+        <v>0.02915904660254274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04523804960981425</v>
+        <v>0.03031453025658778</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04483477867911079</v>
+        <v>0.03079128668283957</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04399101909669533</v>
+        <v>0.03032663363174714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04534044115087831</v>
+        <v>0.03041377518975085</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03734932585228419</v>
+        <v>0.02912022748309583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04275711815050216</v>
+        <v>0.03431680558913427</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03768906939981295</v>
+        <v>0.02897645871049791</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03784134707869177</v>
+        <v>0.02924456372477495</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03997494562498834</v>
+        <v>0.03126287716720375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03783141532232218</v>
+        <v>0.02924281801127574</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03783141532232218</v>
+        <v>0.02924281801127574</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03908804705500078</v>
+        <v>0.03039351355300003</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03836526253737974</v>
+        <v>0.02965265184806471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03784101654188187</v>
+        <v>0.02924423318796507</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03913538435426996</v>
+        <v>0.03042277366495494</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0379361126478753</v>
+        <v>0.02922350195856026</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04308757704325944</v>
+        <v>0.03437496635394442</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0438755616085872</v>
+        <v>0.03006528133334229</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05235043243086625</v>
+        <v>0.03179816273292823</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05621894260577776</v>
+        <v>0.03412182062033121</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05007293751135961</v>
+        <v>0.03139732590487191</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04428634495345433</v>
+        <v>0.03037888562019911</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05360418059524003</v>
+        <v>0.03294835304223848</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05288139607761823</v>
+        <v>0.03220749133730302</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05235715008212114</v>
+        <v>0.0317990726772035</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0536531549066635</v>
+        <v>0.03297790126833097</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04396787749255261</v>
+        <v>0.03028509256547114</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06630471746655182</v>
+        <v>0.03846118304630228</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04897742117350617</v>
+        <v>0.03096320861190251</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05416614461730557</v>
+        <v>0.03211772807600245</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05630040663030299</v>
+        <v>0.03413615828856995</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05997810153282889</v>
+        <v>0.0331406347632042</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05416614548507009</v>
+        <v>0.03211773050434137</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0554128445936146</v>
+        <v>0.03326667790422751</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05469006007599352</v>
+        <v>0.03252581619929221</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05416581408049569</v>
+        <v>0.03211739753919255</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05546018189288376</v>
+        <v>0.03329593801618243</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0513427760097413</v>
+        <v>0.03098051204586362</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05941237458187325</v>
+        <v>0.03724813070517189</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04936054212503863</v>
+        <v>0.007977678264216912</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04857456394482009</v>
+        <v>0.009270658354505594</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05451882148336119</v>
+        <v>0.008249148261677415</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04901535976758015</v>
+        <v>0.009643487227668101</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04726712286595692</v>
+        <v>0.008188263545260793</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05074526474680833</v>
+        <v>0.008050553465520001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05728563146684276</v>
+        <v>0.008394948946009456</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04685402988883457</v>
+        <v>0.007845830755464675</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0527429229158415</v>
+        <v>0.01016600694487216</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04898513167732776</v>
+        <v>0.009563170620994054</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0634144522461851</v>
+        <v>0.008724793519334228</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05307643508498645</v>
+        <v>0.009069548850156492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05191313519787825</v>
+        <v>0.01049020587719172</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05900952488140741</v>
+        <v>0.01100489537173959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05235494290701691</v>
+        <v>0.01110044217378913</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05060670600539368</v>
+        <v>0.008698358134617491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05466915294444854</v>
+        <v>0.009593946220075802</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06219270487443913</v>
+        <v>0.01207180006401295</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05019219421514458</v>
+        <v>0.008132862109249975</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05657961126175366</v>
+        <v>0.01292212781572801</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05233540466963055</v>
+        <v>0.01098887512232688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06924070804679805</v>
+        <v>0.0144025129254956</v>
       </c>
     </row>
     <row r="4">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03148318305979071</v>
+        <v>0.03148318305979077</v>
       </c>
       <c r="C4" t="n">
         <v>0.02988354629654756</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03454956156347591</v>
+        <v>0.03454956156347593</v>
       </c>
       <c r="E4" t="n">
         <v>0.02992137708197926</v>
@@ -610,7 +610,7 @@
         <v>0.02992137708197927</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03230208747688304</v>
+        <v>0.03230208747688307</v>
       </c>
       <c r="H4" t="n">
         <v>0.03619294442081301</v>
@@ -619,7 +619,7 @@
         <v>0.02996623159448942</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03196124111973983</v>
+        <v>0.03196124111973984</v>
       </c>
       <c r="K4" t="n">
         <v>0.03003621080157461</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08638231841200254</v>
+        <v>0.08638231841200308</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05892930352913364</v>
+        <v>0.05892930352913367</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1468556946813553</v>
+        <v>0.1468556946813556</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05892930530591878</v>
+        <v>0.05892930530591885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05892930530591878</v>
+        <v>0.05892930530591885</v>
       </c>
       <c r="G5" t="n">
         <v>0.1055005665940826</v>
       </c>
       <c r="H5" t="n">
-        <v>0.196723128456555</v>
+        <v>0.1967231284565548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05892870165701813</v>
+        <v>0.05892870165701809</v>
       </c>
       <c r="J5" t="n">
-        <v>0.100848700291744</v>
+        <v>0.1008487002917442</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06021280454500005</v>
+        <v>0.06021280454500023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09901014517374082</v>
+        <v>0.2831432356029807</v>
       </c>
     </row>
     <row r="6">
@@ -675,34 +675,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03232949854183433</v>
+        <v>0.03232949854183435</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03073926446989163</v>
+        <v>0.03073926446989161</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03551067285667329</v>
+        <v>0.03551068695426683</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03064545234984618</v>
+        <v>0.03064545234984619</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03081034970766009</v>
+        <v>0.03081034970766008</v>
       </c>
       <c r="G6" t="n">
         <v>0.03479554409454548</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03878911818979424</v>
+        <v>0.03878911818979422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03081254707653301</v>
+        <v>0.03245968821215185</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03289939514320909</v>
+        <v>0.03445472078059639</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03083240349162273</v>
+        <v>0.03083240349162271</v>
       </c>
       <c r="L6" t="n">
         <v>0.0407480666394228</v>
@@ -721,7 +721,7 @@
         <v>0.03104861351123116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03563120412130049</v>
+        <v>0.0356312041213005</v>
       </c>
       <c r="E7" t="n">
         <v>0.03104692312242966</v>
@@ -736,10 +736,10 @@
         <v>0.03727472446543927</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03104801163911566</v>
+        <v>0.03104801163911565</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03304302116436608</v>
+        <v>0.03304302116436607</v>
       </c>
       <c r="K7" t="n">
         <v>0.03111799084620084</v>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0340252603395547</v>
+        <v>0.03402526033955472</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0345371617577759</v>
+        <v>0.03453716175778699</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03954172558590609</v>
+        <v>0.03954172558590608</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03398224423128377</v>
+        <v>0.03398224423128379</v>
       </c>
       <c r="F8" t="n">
         <v>0.0325723107104127</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03687346323930365</v>
+        <v>0.03687346323930362</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04076432018323365</v>
+        <v>0.04076432018323364</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03453760735690997</v>
+        <v>0.03453760735690999</v>
       </c>
       <c r="J8" t="n">
         <v>0.0365330156971793</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03254059282020166</v>
+        <v>0.03254059282020164</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04652627410045467</v>
+        <v>0.0465262741004546</v>
       </c>
     </row>
     <row r="9">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03680183877284255</v>
+        <v>0.03680183877284254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03693662499387578</v>
+        <v>0.03693662499387577</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04151935352149159</v>
+        <v>0.04151935352149156</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03884200013766902</v>
+        <v>0.03884200013766901</v>
       </c>
       <c r="F9" t="n">
         <v>0.03693662457686041</v>
@@ -813,7 +813,7 @@
         <v>0.03927187900415392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04316273594808389</v>
+        <v>0.04316273594808386</v>
       </c>
       <c r="I9" t="n">
         <v>0.03693602312176027</v>
@@ -822,10 +822,10 @@
         <v>0.03893103264701069</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03604932793474587</v>
+        <v>0.03492692750040352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0468049179132474</v>
+        <v>0.04680491791324739</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04421399530771696</v>
+        <v>0.007152263675101958</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04637051299224005</v>
+        <v>0.008286329726259733</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04481236449174652</v>
+        <v>0.007183754656800509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04664975919788155</v>
+        <v>0.008521422313958986</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04541983199334675</v>
+        <v>0.007497626850974945</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04533051910458983</v>
+        <v>0.0072110241049365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04476421679267895</v>
+        <v>0.007178804490114186</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04505598741315998</v>
+        <v>0.007196669869971867</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04750924839938998</v>
+        <v>0.008668601379089841</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04664035495926889</v>
+        <v>0.008830373527198893</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04426526290347822</v>
+        <v>0.007153313094347738</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04719644412795329</v>
+        <v>0.006831674759062863</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04947887919816502</v>
+        <v>0.008947746622924822</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04788469264139034</v>
+        <v>0.007054987480625639</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04975894903415388</v>
+        <v>0.00933378785499725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04852902182961906</v>
+        <v>0.007643853088696435</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04848067778156485</v>
+        <v>0.007249464953963114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04782992733732828</v>
+        <v>0.007037337757197448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04816565228239448</v>
+        <v>0.00714680026301105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05072797249899232</v>
+        <v>0.009789417714153825</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04968859279485995</v>
+        <v>0.009726631593883574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04725541634153876</v>
+        <v>0.006851196757054698</v>
       </c>
     </row>
     <row r="4">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02813976088129933</v>
+        <v>0.02813976088129934</v>
       </c>
       <c r="C4" t="n">
         <v>0.02854503434464875</v>
@@ -1000,19 +1000,19 @@
         <v>0.02849546600615177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0285722886429858</v>
+        <v>0.02857228864298581</v>
       </c>
       <c r="F4" t="n">
         <v>0.0285722886429858</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0288000965858598</v>
+        <v>0.02880009658585981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02846709049744363</v>
+        <v>0.02846709049744364</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0286194658319526</v>
+        <v>0.02861946583195261</v>
       </c>
       <c r="J4" t="n">
         <v>0.02907484048525808</v>
@@ -1034,34 +1034,34 @@
         <v>0.03260674022926598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04052165078387834</v>
+        <v>0.04052165078387835</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03815173671129373</v>
+        <v>0.03815173671129372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04052165308694817</v>
+        <v>0.04052165308694818</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04052165308694817</v>
+        <v>0.04052165308694818</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04352057691933586</v>
+        <v>0.04352057691933574</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03905810619727072</v>
+        <v>0.03905810619727074</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04052154175887697</v>
+        <v>0.04052154175887698</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04943973354514201</v>
+        <v>0.04943973354514208</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03641677245722345</v>
+        <v>0.03641677245722343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03402685022714157</v>
+        <v>0.03402685022714158</v>
       </c>
     </row>
     <row r="6">
@@ -1071,34 +1071,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0298398606706</v>
+        <v>0.02877570871698525</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02923640470635019</v>
+        <v>0.02923640470635017</v>
       </c>
       <c r="D6" t="n">
         <v>0.03020522870905466</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02915871219369779</v>
+        <v>0.02915871219369777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02925477041919333</v>
+        <v>0.02925477041919334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02943604442154572</v>
+        <v>0.03050019637516046</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0302288377238911</v>
+        <v>0.03022883772389111</v>
       </c>
       <c r="I6" t="n">
         <v>0.02925541366763852</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03078833252726668</v>
+        <v>0.02977827278434075</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02903206329108551</v>
+        <v>0.02903206329108561</v>
       </c>
       <c r="L6" t="n">
         <v>0.02880642730771843</v>
@@ -1120,16 +1120,16 @@
         <v>0.02916990338793211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02929258707658076</v>
+        <v>0.02929258707658077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02929258707658076</v>
+        <v>0.02929258707658077</v>
       </c>
       <c r="G7" t="n">
         <v>0.02947465016944626</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0291416440810301</v>
+        <v>0.02914164408103011</v>
       </c>
       <c r="I7" t="n">
         <v>0.02929401941553908</v>
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02984923228269031</v>
+        <v>0.02984923228269032</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03171680516961234</v>
+        <v>0.03171680516961933</v>
       </c>
       <c r="D8" t="n">
         <v>0.0318817351011934</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03133706103814482</v>
+        <v>0.03133706103814483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03037222037521945</v>
+        <v>0.03037222037521946</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03189838535285096</v>
+        <v>0.03189838535285097</v>
       </c>
       <c r="H8" t="n">
         <v>0.03156537926443476</v>
@@ -1175,13 +1175,13 @@
         <v>0.03171775459894378</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03217340219450649</v>
+        <v>0.0321734021945065</v>
       </c>
       <c r="K8" t="n">
         <v>0.03008379993597954</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03271968207776122</v>
+        <v>0.03271968207776121</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0304180766294483</v>
+        <v>0.03041807662944831</v>
       </c>
       <c r="C9" t="n">
         <v>0.03165969442508541</v>
@@ -1206,7 +1206,7 @@
         <v>0.03165969657794195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03184021615399124</v>
+        <v>0.03184021615399123</v>
       </c>
       <c r="H9" t="n">
         <v>0.03150721006557507</v>
@@ -1215,7 +1215,7 @@
         <v>0.03165958540008405</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03211496005338952</v>
+        <v>0.03211496005338951</v>
       </c>
       <c r="K9" t="n">
         <v>0.03099885425527668</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04552657138663223</v>
+        <v>0.007675113038642964</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04564356595228558</v>
+        <v>0.00731624571055085</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04755142442293377</v>
+        <v>0.007781677032261457</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04539622574098796</v>
+        <v>0.007282735650925775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04539622574098796</v>
+        <v>0.007282690654328672</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04716065322859708</v>
+        <v>0.007761111520437633</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05051282564620656</v>
+        <v>0.007937010215365038</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04588857282619754</v>
+        <v>0.007694249765852828</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05056030707685425</v>
+        <v>0.008684075812714737</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04677585950629002</v>
+        <v>0.008522415536322514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04849091911877939</v>
+        <v>0.007830995164726243</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04854375223056143</v>
+        <v>0.007982336608527749</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04874693603484025</v>
+        <v>0.007561208588044775</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05087275266935103</v>
+        <v>0.008741452137321066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0484680252762346</v>
+        <v>0.007440023351873581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0484680252762346</v>
+        <v>0.007439978355276488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05042328484785481</v>
+        <v>0.008596508578074301</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05427972681587408</v>
+        <v>0.009865603585303178</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04896042762603424</v>
+        <v>0.008119074895289987</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05419025988726285</v>
+        <v>0.01082776002297185</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04983013586315922</v>
+        <v>0.009452346603220845</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05195327023514285</v>
+        <v>0.009105223610457652</v>
       </c>
     </row>
     <row r="4">
@@ -1393,13 +1393,13 @@
         <v>0.02877384853049349</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02979007059389048</v>
+        <v>0.02979007059389049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02873442567317488</v>
+        <v>0.02873442567317489</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02873442567317488</v>
+        <v>0.02873442567317489</v>
       </c>
       <c r="G4" t="n">
         <v>0.02955351265408926</v>
@@ -1411,7 +1411,7 @@
         <v>0.02877487158367266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03101147867282005</v>
+        <v>0.03101147867282006</v>
       </c>
       <c r="K4" t="n">
         <v>0.028733189925777</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03965292507067077</v>
+        <v>0.0396529250706708</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04639409142299503</v>
+        <v>0.04639409142299505</v>
       </c>
       <c r="D5" t="n">
         <v>0.06127608896579487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04373650116611319</v>
+        <v>0.04373650116611316</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04373650116611319</v>
+        <v>0.04373650116611316</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05795026581001524</v>
+        <v>0.05795026581001521</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1009845105608365</v>
+        <v>0.1009845105608364</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04373625288511954</v>
+        <v>0.04373625288511945</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08591830313449651</v>
+        <v>0.08591830313449644</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04242715297431342</v>
+        <v>0.0424271529743134</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07771963769528059</v>
+        <v>0.07771963769528051</v>
       </c>
     </row>
     <row r="6">
@@ -1467,34 +1467,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02924044620978151</v>
+        <v>0.03045349766779551</v>
       </c>
       <c r="C6" t="n">
         <v>0.02954088770041186</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03046203260823541</v>
+        <v>0.03046204369150957</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02931477855461161</v>
+        <v>0.0293147785546116</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02942698239460178</v>
+        <v>0.02942698239460177</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03142062905777417</v>
+        <v>0.03020757759976016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03352605851206422</v>
+        <v>0.03352605851206423</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03064198798735758</v>
+        <v>0.02942893652934357</v>
       </c>
       <c r="J6" t="n">
         <v>0.0328903100176815</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02935778233264717</v>
+        <v>0.02935778233264718</v>
       </c>
       <c r="L6" t="n">
         <v>0.03100927854809865</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02940289014979017</v>
+        <v>0.02940289014979018</v>
       </c>
       <c r="C7" t="n">
         <v>0.02974551287489216</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03058971957359031</v>
+        <v>0.03058971957359032</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03255373026335639</v>
+        <v>0.0325537302633564</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03375030374536588</v>
+        <v>0.03375030374536589</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03195648130356071</v>
+        <v>0.03195648130356072</v>
       </c>
       <c r="F8" t="n">
         <v>0.03082997864133213</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03317766040856674</v>
+        <v>0.03317766040856677</v>
       </c>
       <c r="H8" t="n">
         <v>0.03517399598003565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03239901933815015</v>
+        <v>0.03239901933815016</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03463594496250886</v>
+        <v>0.03463594496250887</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03070642086771105</v>
+        <v>0.03070642086771106</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03566570875626012</v>
+        <v>0.03566570875626014</v>
       </c>
     </row>
     <row r="9">
@@ -1599,7 +1599,7 @@
         <v>0.03397118104543508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03282245760332741</v>
+        <v>0.03282245760332739</v>
       </c>
       <c r="G9" t="n">
         <v>0.03360085125299341</v>
@@ -1611,7 +1611,7 @@
         <v>0.03282221018257683</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03505881727172421</v>
+        <v>0.0350588172717242</v>
       </c>
       <c r="K9" t="n">
         <v>0.03220376352752549</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04486603068942304</v>
+        <v>0.00751135522265732</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04508484941985351</v>
+        <v>0.007200653997838573</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04654877912559803</v>
+        <v>0.007599914930645613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04480382776633173</v>
+        <v>0.007176891686289037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04480382776633173</v>
+        <v>0.007176848641705886</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04602784815547713</v>
+        <v>0.007572499368340393</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04750698421617834</v>
+        <v>0.007649019466956145</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04522640059213912</v>
+        <v>0.00753041136074709</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04885372718088333</v>
+        <v>0.008558152847166675</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04603590357564784</v>
+        <v>0.008406547758477155</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04568405494967805</v>
+        <v>0.007553224986857556</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04780977774319537</v>
+        <v>0.007628621262566122</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04812199627099172</v>
+        <v>0.007300248078032076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04974528702508502</v>
+        <v>0.008259816693797701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0478019634996632</v>
+        <v>0.007181669472769392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0478019634996632</v>
+        <v>0.007181626428186236</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04914610849892063</v>
+        <v>0.008065525039652556</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05084815482700214</v>
+        <v>0.008625475673503271</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04822563488881661</v>
+        <v>0.007764990518918991</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05223523037883752</v>
+        <v>0.01019963257738518</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04899478688717813</v>
+        <v>0.009135840691794421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04875064789026193</v>
+        <v>0.007938739542803185</v>
       </c>
     </row>
     <row r="4">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02818063076005057</v>
+        <v>0.02818063076005059</v>
       </c>
       <c r="C4" t="n">
         <v>0.028417454816498</v>
@@ -1798,10 +1798,10 @@
         <v>0.02843581138364655</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02886743487952037</v>
+        <v>0.02886743487952038</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0297503461974637</v>
+        <v>0.02975034619746371</v>
       </c>
       <c r="I4" t="n">
         <v>0.02837095602302417</v>
@@ -1810,10 +1810,10 @@
         <v>0.02991308809977091</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02824053379327398</v>
+        <v>0.02824053379327399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02866718684635828</v>
+        <v>0.02866718684635829</v>
       </c>
     </row>
     <row r="5">
@@ -1826,31 +1826,31 @@
         <v>0.03337623346538104</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04028956299439961</v>
+        <v>0.04028956299439963</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05062311397078259</v>
+        <v>0.05062311397078262</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03734747647584372</v>
+        <v>0.03734747647584373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03734747647584372</v>
+        <v>0.03734747647584374</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04585455900639597</v>
+        <v>0.04585455900639616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06442079739902545</v>
+        <v>0.06442079739902544</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03734729425409685</v>
+        <v>0.03734729425409687</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06484719747957475</v>
+        <v>0.06484719747957476</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03466607059753937</v>
+        <v>0.03466607059753934</v>
       </c>
       <c r="L5" t="n">
         <v>0.04399914708494396</v>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02993600289017144</v>
+        <v>0.02993600289017142</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02916086132012337</v>
+        <v>0.02916086132012333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03094725701810162</v>
+        <v>0.03094725701810165</v>
       </c>
       <c r="E6" t="n">
         <v>0.02892346681129761</v>
@@ -1878,22 +1878,22 @@
         <v>0.02901992429753252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02950958446305666</v>
+        <v>0.03062280700964121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0316124020929716</v>
+        <v>0.03161240209297161</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02901310560656044</v>
+        <v>0.02901310560656045</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03063042149704104</v>
+        <v>0.03063042149704107</v>
       </c>
       <c r="K6" t="n">
         <v>0.02886837531663766</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02930489526469584</v>
+        <v>0.02930489526469586</v>
       </c>
     </row>
     <row r="7">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02891342572708583</v>
+        <v>0.02891342572708584</v>
       </c>
       <c r="C7" t="n">
         <v>0.02928469605356012</v>
@@ -1918,22 +1918,22 @@
         <v>0.02911002044829333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02960022984655562</v>
+        <v>0.02960022984655563</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03048314116449896</v>
+        <v>0.03048314116449895</v>
       </c>
       <c r="I7" t="n">
         <v>0.02910375099005942</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03064588306680612</v>
+        <v>0.03064588306680616</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02897332876030923</v>
+        <v>0.02897332876030925</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02939998181339355</v>
+        <v>0.02939998181339354</v>
       </c>
     </row>
     <row r="8">
@@ -1946,34 +1946,34 @@
         <v>0.03001426767584258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0318840152718152</v>
+        <v>0.03188401527180415</v>
       </c>
       <c r="D8" t="n">
         <v>0.03281625443550604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03129445591020753</v>
+        <v>0.03129445591020752</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03025577108250299</v>
+        <v>0.030255771082503</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0321933104978041</v>
+        <v>0.03219331049780412</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03307622181575426</v>
+        <v>0.03307622181575429</v>
       </c>
       <c r="I8" t="n">
         <v>0.0316968316413079</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03323925698525791</v>
+        <v>0.03323925698525788</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03004645160908504</v>
+        <v>0.03004645160908507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03355183056795441</v>
+        <v>0.0335518305679544</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03065803462021748</v>
+        <v>0.03065803462021749</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0318568436266185</v>
+        <v>0.03185684362661851</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03248589648163797</v>
+        <v>0.03248589648163798</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03263104284815095</v>
+        <v>0.03263104284815096</v>
       </c>
       <c r="F9" t="n">
         <v>0.03167608037278195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03217237741961398</v>
+        <v>0.03217237741961402</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03305528873755734</v>
+        <v>0.03305528873755732</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0316758985631178</v>
+        <v>0.03167589856311781</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0332180306398645</v>
+        <v>0.03321803063986453</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03106599739946573</v>
+        <v>0.03106599739946576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0319721293864519</v>
+        <v>0.03197212938645193</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04431929578628558</v>
+        <v>0.007236661457165865</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04470136268021706</v>
+        <v>0.007069428239555892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04549770614276441</v>
+        <v>0.007298678853715859</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04414119539879651</v>
+        <v>0.007018418735490317</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04414119539879651</v>
+        <v>0.00701837938998699</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04505958327482624</v>
+        <v>0.007275621317358381</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04562836878360062</v>
+        <v>0.007303909516598058</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04440683324293046</v>
+        <v>0.007241361271955951</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04641514317547561</v>
+        <v>0.007905224701450986</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04561662742207738</v>
+        <v>0.008262392491057962</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04457301767817869</v>
+        <v>0.007248859007820491</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04730465171247156</v>
+        <v>0.007214922066159771</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04777877157522537</v>
+        <v>0.007120343315695335</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04866006772939215</v>
+        <v>0.007657270765516331</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04713996520346095</v>
+        <v>0.00688135094993571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04713996520346095</v>
+        <v>0.006881311604432358</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04815613567438456</v>
+        <v>0.007493603765316431</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0488110854566937</v>
+        <v>0.007708477529021039</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04740703807742839</v>
+        <v>0.007249121239252301</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04960776819456565</v>
+        <v>0.008718117088958829</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04861241045175936</v>
+        <v>0.008928752849470537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04759645078802614</v>
+        <v>0.007311194281071668</v>
       </c>
     </row>
     <row r="4">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0279311098672963</v>
+        <v>0.02793110986729629</v>
       </c>
       <c r="C4" t="n">
         <v>0.02816796619460539</v>
@@ -2209,7 +2209,7 @@
         <v>0.02797237602020751</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02808221467573078</v>
+        <v>0.02808221467573077</v>
       </c>
     </row>
     <row r="5">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02996318125757594</v>
+        <v>0.02996318125757595</v>
       </c>
       <c r="C5" t="n">
         <v>0.03679348116394879</v>
@@ -2228,28 +2228,28 @@
         <v>0.04221170247033334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03121935596099224</v>
+        <v>0.03121935596099223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03121935596099224</v>
+        <v>0.03121935596099223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03806594499810918</v>
+        <v>0.03806594499810916</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04554505507103822</v>
+        <v>0.0455450550710382</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03121919625358347</v>
+        <v>0.03121919625358346</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04508524257117089</v>
+        <v>0.04508524257117087</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03101971431022902</v>
+        <v>0.031019714310229</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03365993470310712</v>
+        <v>0.0336599347031071</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02857050195197187</v>
+        <v>0.02857050195197186</v>
       </c>
       <c r="C6" t="n">
         <v>0.02891017215658554</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02927718855886602</v>
+        <v>0.02927717671694345</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02850834290988114</v>
+        <v>0.02850834290988113</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02860571976483929</v>
+        <v>0.02860571976483928</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03009467970344401</v>
+        <v>0.030094679703444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03053499608882597</v>
+        <v>0.03053499608882596</v>
       </c>
       <c r="I6" t="n">
         <v>0.02968821376842611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03048764006187988</v>
+        <v>0.03048764006187986</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02860789829934191</v>
+        <v>0.02860789829934189</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02871341140721871</v>
+        <v>0.02871341140721868</v>
       </c>
     </row>
     <row r="7">
@@ -2308,22 +2308,22 @@
         <v>0.02932749020546228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02866507123905976</v>
+        <v>0.02866507123905975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02866507123905976</v>
+        <v>0.02866507123905975</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02906358186893424</v>
+        <v>0.02906358186893423</v>
       </c>
       <c r="H7" t="n">
         <v>0.02940525546028006</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02865711593391633</v>
+        <v>0.02865711593391632</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0294473653945038</v>
+        <v>0.02944736539450379</v>
       </c>
       <c r="K7" t="n">
         <v>0.02866834640448485</v>
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02970559108225651</v>
+        <v>0.02970559108225652</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03153301731326971</v>
+        <v>0.03153301731328134</v>
       </c>
       <c r="D8" t="n">
         <v>0.03216101275395302</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03079878469932077</v>
+        <v>0.03079878469932075</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02978657367592806</v>
+        <v>0.02978657367592805</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03159560425761092</v>
+        <v>0.0315956042576109</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03193727784896291</v>
+        <v>0.0319372778489629</v>
       </c>
       <c r="I8" t="n">
         <v>0.03118913832259301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03197967343920147</v>
+        <v>0.03197967343920146</v>
       </c>
       <c r="K8" t="n">
         <v>0.02971985751179634</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03282852181107723</v>
+        <v>0.03282852181107722</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03007244297876286</v>
+        <v>0.03007244297876285</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03117259241231637</v>
+        <v>0.03117259241231635</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03150705883268721</v>
+        <v>0.03150705883268719</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03168387500157693</v>
+        <v>0.03168387500157692</v>
       </c>
       <c r="F9" t="n">
         <v>0.03083673840672254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03124304487239516</v>
+        <v>0.03124304487239515</v>
       </c>
       <c r="H9" t="n">
         <v>0.03158471846374099</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03083657893737726</v>
+        <v>0.03083657893737725</v>
       </c>
       <c r="J9" t="n">
         <v>0.03162682839796471</v>
       </c>
       <c r="K9" t="n">
-        <v>0.029923445980045</v>
+        <v>0.03040521244016756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03095764806346905</v>
+        <v>0.03095764806346904</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04463954984350589</v>
+        <v>0.007481017676850396</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04408776931260196</v>
+        <v>0.007108401974699086</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04597812734031541</v>
+        <v>0.007551464351878433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04466064644040631</v>
+        <v>0.007136540391258354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04466064644040631</v>
+        <v>0.00713649447315831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04603718889682349</v>
+        <v>0.00755457264429176</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04903810941573011</v>
+        <v>0.007712071018342349</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0451017110318045</v>
+        <v>0.007505430214054826</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0501591068466677</v>
+        <v>0.008554930462063818</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04626700898013246</v>
+        <v>0.008395162487898478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04809061180372443</v>
+        <v>0.007663246356107645</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04752931644122566</v>
+        <v>0.007539405911698661</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04695925694489719</v>
+        <v>0.006894691932553958</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04906895784804972</v>
+        <v>0.008041734110871609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04762008957263598</v>
+        <v>0.007105336302933103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04762008957263598</v>
+        <v>0.007105290384833063</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04913689087259857</v>
+        <v>0.008064843650344433</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05258928637014983</v>
+        <v>0.009199655849097831</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04806277162514938</v>
+        <v>0.007714035861928354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05372703277170814</v>
+        <v>0.01061751397585424</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04924163270945394</v>
+        <v>0.0092117174312999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05149860611079719</v>
+        <v>0.008844999966073783</v>
       </c>
     </row>
     <row r="4">
@@ -2584,10 +2584,10 @@
         <v>0.02883111166202395</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02828295103119975</v>
+        <v>0.02828295103119974</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02828295103119975</v>
+        <v>0.02828295103119974</v>
       </c>
       <c r="G4" t="n">
         <v>0.028862138432127</v>
@@ -2596,13 +2596,13 @@
         <v>0.03064956832397351</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02828461848997679</v>
+        <v>0.02828461848997678</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03071925753603252</v>
+        <v>0.03071925753603251</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02837121340848191</v>
+        <v>0.02837121340848192</v>
       </c>
       <c r="L4" t="n">
         <v>0.03008661369003798</v>
@@ -2621,31 +2621,31 @@
         <v>0.03043756837715896</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04582808055767787</v>
+        <v>0.04582808055767786</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03658611305725874</v>
+        <v>0.03658611305725868</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03658611305725874</v>
+        <v>0.03658611305725868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04698400749769174</v>
+        <v>0.04698400749769178</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08477709557888831</v>
+        <v>0.0847770955788883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03658591194607807</v>
+        <v>0.03658591194607803</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08222533729383562</v>
+        <v>0.08222533729383563</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03764041679051974</v>
+        <v>0.03764041679051978</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07431465595279839</v>
+        <v>0.07431465595279838</v>
       </c>
     </row>
     <row r="6">
@@ -2655,31 +2655,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02864650062517602</v>
+        <v>0.02864650062517603</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02852259761182948</v>
+        <v>0.02852259761182947</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02944802735141979</v>
+        <v>0.02944801601819532</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02879444986848484</v>
+        <v>0.02879444986848481</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02889681180895217</v>
+        <v>0.02889681180895216</v>
       </c>
       <c r="G6" t="n">
         <v>0.02947325499679235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03251083703557148</v>
+        <v>0.03251083703557149</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02889573505464214</v>
+        <v>0.03004841395561803</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03249227625685796</v>
+        <v>0.03140609327114993</v>
       </c>
       <c r="K6" t="n">
         <v>0.02896025264675766</v>
@@ -2701,7 +2701,7 @@
         <v>0.02873423623342052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02960060291521379</v>
+        <v>0.0296006029152138</v>
       </c>
       <c r="E7" t="n">
         <v>0.02906482745728954</v>
@@ -2716,7 +2716,7 @@
         <v>0.0314191725722115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02905422273821478</v>
+        <v>0.02905422273821477</v>
       </c>
       <c r="J7" t="n">
         <v>0.03148886178427051</v>
@@ -2725,7 +2725,7 @@
         <v>0.02914081765671991</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03085621793827596</v>
+        <v>0.03085621793827597</v>
       </c>
     </row>
     <row r="8">
@@ -2735,34 +2735,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02995149733425615</v>
+        <v>0.02995149733425616</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03144520375134757</v>
+        <v>0.03144520375135799</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03262354518609316</v>
+        <v>0.03262354518609317</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03133924367723637</v>
+        <v>0.03133924367723638</v>
       </c>
       <c r="F8" t="n">
         <v>0.03025646825598692</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03233232478036893</v>
+        <v>0.03233232478036894</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03411975467221624</v>
+        <v>0.03411975467221626</v>
       </c>
       <c r="I8" t="n">
         <v>0.03175480483821871</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03418974930389775</v>
+        <v>0.03418974930389776</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03025845897702593</v>
+        <v>0.03025845897702594</v>
       </c>
       <c r="L8" t="n">
         <v>0.03518015931383325</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03081148106486918</v>
+        <v>0.03081148106486917</v>
       </c>
       <c r="C9" t="n">
         <v>0.03165497731833</v>
@@ -2787,25 +2787,25 @@
         <v>0.03303018764014477</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03197516428116946</v>
+        <v>0.03197516428116945</v>
       </c>
       <c r="G9" t="n">
         <v>0.03255248376527448</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03433991365712098</v>
+        <v>0.03433991365712099</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03197496382312425</v>
+        <v>0.03197496382312426</v>
       </c>
       <c r="J9" t="n">
         <v>0.03440960286917999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03091035680659127</v>
+        <v>0.03153183982574537</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03377695902318545</v>
+        <v>0.03377695902318546</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04428677714605377</v>
+        <v>0.007250233732208979</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04395980093130995</v>
+        <v>0.006983315168614485</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04438356807054807</v>
+        <v>0.007255327646322868</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04431896723899847</v>
+        <v>0.007001380696848178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04431896723899847</v>
+        <v>0.007001336218100075</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04449742826468387</v>
+        <v>0.007261319882195671</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04455718576741326</v>
+        <v>0.007262711769106465</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04463795132025578</v>
+        <v>0.00726881497505022</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04689681084391883</v>
+        <v>0.008270245453367206</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04550618071494178</v>
+        <v>0.008222595871409662</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04472396901111696</v>
+        <v>0.007272755193762586</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04715026208129972</v>
+        <v>0.007227022642073088</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04682100424886549</v>
+        <v>0.006786294384599383</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04726159169464775</v>
+        <v>0.007263973161388062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04723548544142279</v>
+        <v>0.006918914544709782</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04723548544142279</v>
+        <v>0.006918870065961661</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04739255450397212</v>
+        <v>0.007306877591136474</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0474619815033762</v>
+        <v>0.007328559852726567</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04755708963388188</v>
+        <v>0.007360138841851212</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04998231018597801</v>
+        <v>0.009338674023643483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04837787818786191</v>
+        <v>0.008848520657871468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04765305447537461</v>
+        <v>0.007393020701381395</v>
       </c>
     </row>
     <row r="4">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02783663543385497</v>
+        <v>0.02783663543385496</v>
       </c>
       <c r="C4" t="n">
         <v>0.0277072894725128</v>
@@ -2989,13 +2989,13 @@
         <v>0.02795840376848448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02799748362681097</v>
+        <v>0.02799748362681098</v>
       </c>
       <c r="I4" t="n">
         <v>0.02802420001397345</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02871527641632722</v>
+        <v>0.02871527641632723</v>
       </c>
       <c r="K4" t="n">
         <v>0.02786913725332786</v>
@@ -3020,22 +3020,22 @@
         <v>0.03073859456413064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03336206758032324</v>
+        <v>0.03336206758032323</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03336206758032324</v>
+        <v>0.03336206758032323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03200354021084447</v>
+        <v>0.03200354021084442</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03312140608546522</v>
+        <v>0.0331214060854652</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03336201580753669</v>
+        <v>0.03336201580753671</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04555746802302986</v>
+        <v>0.04555746802302987</v>
       </c>
       <c r="K5" t="n">
         <v>0.03032413083723602</v>
@@ -3057,16 +3057,16 @@
         <v>0.02838959273385976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02848097588717783</v>
+        <v>0.02951945770774985</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02854646920878158</v>
+        <v>0.02854646920878157</v>
       </c>
       <c r="F6" t="n">
         <v>0.02862451469370635</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02958348500944313</v>
+        <v>0.02854917509698708</v>
       </c>
       <c r="H6" t="n">
         <v>0.02969683162443126</v>
@@ -3075,10 +3075,10 @@
         <v>0.02964928125493209</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02937097276255096</v>
+        <v>0.03033908106051166</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02845430008863917</v>
+        <v>0.02845430008863916</v>
       </c>
       <c r="L6" t="n">
         <v>0.02868196863013469</v>
@@ -3097,7 +3097,7 @@
         <v>0.02848820453471084</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02855309865780014</v>
+        <v>0.02855309865780013</v>
       </c>
       <c r="E7" t="n">
         <v>0.02869651218471449</v>
@@ -3106,7 +3106,7 @@
         <v>0.02869651218471449</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02861743602106194</v>
+        <v>0.02861743602106195</v>
       </c>
       <c r="H7" t="n">
         <v>0.02865651587938843</v>
@@ -3134,7 +3134,7 @@
         <v>0.02953264071987209</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0309207204717901</v>
+        <v>0.03092072047177976</v>
       </c>
       <c r="D8" t="n">
         <v>0.03125934691296339</v>
@@ -3149,19 +3149,19 @@
         <v>0.03103690715674118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03107598701507035</v>
+        <v>0.03107598701507034</v>
       </c>
       <c r="I8" t="n">
         <v>0.03110270340223016</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03179405150478898</v>
+        <v>0.03179405150478899</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02953946192734109</v>
+        <v>0.02953946192734107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03261924913070174</v>
+        <v>0.03261924913070173</v>
       </c>
     </row>
     <row r="9">
@@ -3186,19 +3186,19 @@
         <v>0.03093120679806867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03086535881634316</v>
+        <v>0.03086535881634317</v>
       </c>
       <c r="H9" t="n">
         <v>0.03090443867466966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03093115506183213</v>
+        <v>0.03093115506183212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03162223146418591</v>
+        <v>0.0316222314641859</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02985221067479226</v>
+        <v>0.03035097363686095</v>
       </c>
       <c r="L9" t="n">
         <v>0.03100356592015219</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04400858786663273</v>
+        <v>0.006978816891301013</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04391509891973331</v>
+        <v>0.0068960090122638</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04409252842278794</v>
+        <v>0.006983234516052088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04406521096035738</v>
+        <v>0.006885444512047889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04406521096035738</v>
+        <v>0.006885403696086255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04408273965336484</v>
+        <v>0.006982719352559409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04410052547487259</v>
+        <v>0.006981936582705012</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04418643127356721</v>
+        <v>0.006988275433153258</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04509205963962697</v>
+        <v>0.007660919618905605</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04535877953499767</v>
+        <v>0.008105668868261709</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04405373786472282</v>
+        <v>0.006980547983759076</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04695445443247678</v>
+        <v>0.006879413614084725</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04686075633979905</v>
+        <v>0.006746298578985473</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04705100346028909</v>
+        <v>0.006911566430839352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04703807342639248</v>
+        <v>0.006778034733838931</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04703807342639248</v>
+        <v>0.006777993917877297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04703974434771505</v>
+        <v>0.006908033336369976</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04706084714687186</v>
+        <v>0.006913605856926578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04716158966000563</v>
+        <v>0.006947538433764605</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04808025746148992</v>
+        <v>0.008087653104884627</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04830406941261293</v>
+        <v>0.008739088629680401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04700632618307309</v>
+        <v>0.006897146536805697</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02778570759088546</v>
+        <v>0.02778570759088548</v>
       </c>
       <c r="C4" t="n">
         <v>0.02767890420597318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02783560669465665</v>
+        <v>0.02783560669465666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02794149887305906</v>
+        <v>0.02794149887305907</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02794149887305906</v>
+        <v>0.02794149887305907</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0278265270121703</v>
+        <v>0.02782652701217046</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02784046969648135</v>
+        <v>0.02784046969648134</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02787153703193233</v>
+        <v>0.02787153703193232</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02795323715309542</v>
+        <v>0.02795323715309543</v>
       </c>
       <c r="K4" t="n">
         <v>0.02778342529795141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02781268159829587</v>
+        <v>0.02781268159829586</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02909194744794718</v>
+        <v>0.02909194744794721</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02953649738362105</v>
+        <v>0.02953649738362106</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03029787213484758</v>
+        <v>0.03029787213484759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03128125372640959</v>
+        <v>0.03128125372640965</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03128125372640959</v>
+        <v>0.03128125372640965</v>
       </c>
       <c r="G5" t="n">
         <v>0.03026613725175685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03074414854750101</v>
+        <v>0.03074414854750102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03128119864752219</v>
+        <v>0.03128119864752225</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03253825850889603</v>
+        <v>0.03253825850889601</v>
       </c>
       <c r="K5" t="n">
         <v>0.02941852441084917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03026671903656383</v>
+        <v>0.03026671903656384</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02940536659779655</v>
+        <v>0.02940536659779654</v>
       </c>
       <c r="C6" t="n">
         <v>0.02835811572744265</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02842442321965217</v>
+        <v>0.02842442321965216</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02839447907556468</v>
+        <v>0.02839447907556469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02847557880364358</v>
+        <v>0.02847557880364359</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02944618601908134</v>
+        <v>0.02944618601908133</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02952794016176747</v>
+        <v>0.02843147884226542</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02846848385194845</v>
+        <v>0.02949119603884343</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02957086055893688</v>
+        <v>0.02861141079111235</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02838068523991565</v>
+        <v>0.02838068523991557</v>
       </c>
       <c r="L6" t="n">
         <v>0.02840155679281321</v>
@@ -3487,25 +3487,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02841698262302149</v>
+        <v>0.0284169826230215</v>
       </c>
       <c r="C7" t="n">
         <v>0.02841749821618891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02846677365649482</v>
+        <v>0.02846677365649481</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0285136372625529</v>
+        <v>0.02851363726255291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0285136372625529</v>
+        <v>0.02851363726255291</v>
       </c>
       <c r="G7" t="n">
         <v>0.0284578020443063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02847174472861739</v>
+        <v>0.02847174472861738</v>
       </c>
       <c r="I7" t="n">
         <v>0.02850281206406838</v>
@@ -3517,7 +3517,7 @@
         <v>0.02841470033008744</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0284439566304319</v>
+        <v>0.02844395663043189</v>
       </c>
     </row>
     <row r="8">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02943855253229957</v>
+        <v>0.02943855253229956</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03079823383014271</v>
+        <v>0.03079823383015342</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03111653861174866</v>
+        <v>0.03111653861174864</v>
       </c>
       <c r="E8" t="n">
         <v>0.03051365004358099</v>
@@ -3545,7 +3545,7 @@
         <v>0.03082784438594723</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03084178707026126</v>
+        <v>0.03084178707026127</v>
       </c>
       <c r="I8" t="n">
         <v>0.03087285440570932</v>
@@ -3554,7 +3554,7 @@
         <v>0.03095481954007535</v>
       </c>
       <c r="K8" t="n">
-        <v>0.029411221671646</v>
+        <v>0.02941122167164599</v>
       </c>
       <c r="L8" t="n">
         <v>0.03222259118487455</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02975681435942694</v>
+        <v>0.02975681435942695</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03043227380150032</v>
+        <v>0.03043227380150033</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03048165781026703</v>
+        <v>0.03048165781026701</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03129651402547422</v>
+        <v>0.03129651402547423</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0305176426933568</v>
+        <v>0.03051764269335681</v>
       </c>
       <c r="G9" t="n">
         <v>0.03047257762961772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03048652031392881</v>
+        <v>0.03048652031392882</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0305175876493798</v>
+        <v>0.03051758764937981</v>
       </c>
       <c r="J9" t="n">
         <v>0.03059928777054288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03002254499067234</v>
+        <v>0.03003841100815913</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03045873221574332</v>
+        <v>0.03045873221574333</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04447386074692464</v>
+        <v>0.007345708980999326</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04402048185594255</v>
+        <v>0.007039541771541195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04468943978892762</v>
+        <v>0.007357054477805587</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04453184495428526</v>
+        <v>0.007058401278115844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04453184495428526</v>
+        <v>0.007058354771276688</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04501911348703946</v>
+        <v>0.007374404549752502</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04811559181499747</v>
+        <v>0.007537251564272797</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0449019533399457</v>
+        <v>0.007368335352141126</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04625313793214085</v>
+        <v>0.00824220961057958</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0457495231720273</v>
+        <v>0.008283403596429317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04724735163482827</v>
+        <v>0.007492583323217169</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04734615710466365</v>
+        <v>0.007374448169222252</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04687762477213697</v>
+        <v>0.006844730957757286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04759411766003108</v>
+        <v>0.0074558700315749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04746871989787498</v>
+        <v>0.007024971896432665</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04746871989787495</v>
+        <v>0.007024925389593481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04797331070456053</v>
+        <v>0.007579908149937679</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05153557856001211</v>
+        <v>0.008749359512027632</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04784112467415648</v>
+        <v>0.007536355150602523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04923803365003036</v>
+        <v>0.009071808580643013</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04864573116023757</v>
+        <v>0.008968779570738706</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05053607825344543</v>
+        <v>0.008424255695821966</v>
       </c>
     </row>
     <row r="4">
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02795438511579888</v>
+        <v>0.02795438511579889</v>
       </c>
       <c r="C4" t="n">
         <v>0.02774391641624895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02808253772141074</v>
+        <v>0.02808253772141075</v>
       </c>
       <c r="E4" t="n">
         <v>0.02819507579783887</v>
@@ -3778,22 +3778,22 @@
         <v>0.02819507579783887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02827473050884923</v>
+        <v>0.02827473050884924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03011864097281323</v>
+        <v>0.03011864097281325</v>
       </c>
       <c r="I4" t="n">
         <v>0.02818545084280188</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02840000670337266</v>
+        <v>0.02840000670337268</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0280490174362476</v>
+        <v>0.02804901743624762</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02960274855528685</v>
+        <v>0.02960274855528686</v>
       </c>
     </row>
     <row r="5">
@@ -3809,31 +3809,31 @@
         <v>0.03006270347585164</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03330003229791198</v>
+        <v>0.03330003229791199</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03563307550114685</v>
+        <v>0.03563307550114659</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03563307550114685</v>
+        <v>0.03563307550114659</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03705958338835841</v>
+        <v>0.03705958338835826</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07505662813287368</v>
+        <v>0.07505662813287375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03563298636642113</v>
+        <v>0.03563298636642095</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03955442295212824</v>
+        <v>0.03955442295212823</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0327208492011569</v>
+        <v>0.03272084920115693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06537504837566745</v>
+        <v>0.06537504837566752</v>
       </c>
     </row>
     <row r="6">
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02853356897156548</v>
+        <v>0.02853356897156551</v>
       </c>
       <c r="C6" t="n">
         <v>0.02843509620643811</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02865608878222564</v>
+        <v>0.02865608878222565</v>
       </c>
       <c r="E6" t="n">
         <v>0.02867824619508445</v>
@@ -3858,22 +3858,22 @@
         <v>0.02876709984451683</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02997353254275143</v>
+        <v>0.02885391436461585</v>
       </c>
       <c r="H6" t="n">
         <v>0.03191071253205138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02988425287670407</v>
+        <v>0.0287646346985685</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03010502428826885</v>
+        <v>0.02903967194479628</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02860894671979081</v>
+        <v>0.02860894671979079</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03018775775155722</v>
+        <v>0.03018775775155723</v>
       </c>
     </row>
     <row r="7">
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02868060954648746</v>
+        <v>0.02868060954648747</v>
       </c>
       <c r="C7" t="n">
         <v>0.02862245777232461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02880864958181112</v>
+        <v>0.02880864958181111</v>
       </c>
       <c r="E7" t="n">
         <v>0.02892400607041825</v>
@@ -3898,22 +3898,22 @@
         <v>0.02892400607041825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02900095493953781</v>
+        <v>0.02900095493953782</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03084486540350181</v>
+        <v>0.03084486540350182</v>
       </c>
       <c r="I7" t="n">
         <v>0.02891167527349046</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02912623113406126</v>
+        <v>0.02912623113406127</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02877524186693619</v>
+        <v>0.0287752418669362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03032897298597543</v>
+        <v>0.03032897298597544</v>
       </c>
     </row>
     <row r="8">
@@ -3926,13 +3926,13 @@
         <v>0.0297970110927082</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03125051663789269</v>
+        <v>0.03125051663788242</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03173562692268059</v>
+        <v>0.03173562692268062</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03112840942569616</v>
+        <v>0.03112840942569617</v>
       </c>
       <c r="F8" t="n">
         <v>0.03008306853213711</v>
@@ -3941,13 +3941,13 @@
         <v>0.03161688309847926</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0334607935624438</v>
+        <v>0.03346079356244379</v>
       </c>
       <c r="I8" t="n">
         <v>0.03152760343243192</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03174245399267207</v>
+        <v>0.03174245399267211</v>
       </c>
       <c r="K8" t="n">
         <v>0.0298637889364883</v>
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03051201075902186</v>
+        <v>0.03051201075902188</v>
       </c>
       <c r="C9" t="n">
         <v>0.03130426989275389</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03149057444459719</v>
+        <v>0.03149057444459721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03257493213716676</v>
+        <v>0.03257493213716674</v>
       </c>
       <c r="F9" t="n">
         <v>0.03159357596615592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03168276705996709</v>
+        <v>0.03168276705996711</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03352667752393111</v>
+        <v>0.03352667752393112</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03159348739391973</v>
+        <v>0.03159348739391974</v>
       </c>
       <c r="J9" t="n">
         <v>0.03180804325449055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03096432263988124</v>
+        <v>0.03096432263988127</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03301078510640471</v>
+        <v>0.03301078510640472</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04405115315925064</v>
+        <v>0.007017087402692039</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04397299325052333</v>
+        <v>0.006972818637188093</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0440943520144259</v>
+        <v>0.007019360872640077</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04429372209950589</v>
+        <v>0.006986423503851077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04429372209950588</v>
+        <v>0.006986378933502979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04412051772604712</v>
+        <v>0.007020737922073407</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04410991396737469</v>
+        <v>0.007018422767622619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04434706878433642</v>
+        <v>0.007032761451797277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04575682459147194</v>
+        <v>0.008182203835188711</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04555458180423323</v>
+        <v>0.008216894673675109</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04406476748778149</v>
+        <v>0.007017126491974617</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04691557029293213</v>
+        <v>0.006874426730239279</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04683216071055831</v>
+        <v>0.006795408680437999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04696525792499956</v>
+        <v>0.006891268876710498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04720287499392561</v>
+        <v>0.006910545769127301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04720287499392561</v>
+        <v>0.006910501198779203</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04699535391357477</v>
+        <v>0.006901242224488308</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04698383203464499</v>
+        <v>0.006896172436404622</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04725926630276703</v>
+        <v>0.006986812022172648</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04867029337698866</v>
+        <v>0.008892912869455075</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04842893917452697</v>
+        <v>0.008874658726676352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04693117233696365</v>
+        <v>0.006880350209799989</v>
       </c>
     </row>
     <row r="4">
@@ -4162,10 +4162,10 @@
         <v>0.02784530868844816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02770395900011721</v>
+        <v>0.0277039590001172</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02787098857735908</v>
+        <v>0.02787098857735907</v>
       </c>
       <c r="E4" t="n">
         <v>0.02810638450806517</v>
@@ -4174,19 +4174,19 @@
         <v>0.02810638450806517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02788313431784581</v>
+        <v>0.02788313431784579</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02788035718309413</v>
+        <v>0.02788035718309412</v>
       </c>
       <c r="I4" t="n">
         <v>0.02800033550974281</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02803943479124947</v>
+        <v>0.02803943479124946</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02788464802407226</v>
+        <v>0.02788464802407224</v>
       </c>
       <c r="L4" t="n">
         <v>0.02785354579135903</v>
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02972263244029695</v>
+        <v>0.02972263244029694</v>
       </c>
       <c r="C5" t="n">
         <v>0.02981923479694937</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03049619417858712</v>
+        <v>0.03049619417858711</v>
       </c>
       <c r="E5" t="n">
         <v>0.03310086479488131</v>
@@ -4214,22 +4214,22 @@
         <v>0.03310086479488131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03084317715790484</v>
+        <v>0.03084317715790464</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03105134622974488</v>
+        <v>0.03105134622974487</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03310082358173222</v>
+        <v>0.03310082358173223</v>
       </c>
       <c r="J5" t="n">
         <v>0.03365270823873837</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03074114723088089</v>
+        <v>0.03074114723088088</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03059850147453601</v>
+        <v>0.03059850147453602</v>
       </c>
     </row>
     <row r="6">
@@ -4239,13 +4239,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02843322426143715</v>
+        <v>0.0294648059189143</v>
       </c>
       <c r="C6" t="n">
         <v>0.02838499784220897</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02845547274700811</v>
+        <v>0.02845548407203242</v>
       </c>
       <c r="E6" t="n">
         <v>0.02852237775738199</v>
@@ -4254,19 +4254,19 @@
         <v>0.0285983358675906</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0284710498908348</v>
+        <v>0.02847104989083479</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0295717526089934</v>
+        <v>0.02957175260899339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02961983274020897</v>
+        <v>0.02961983274020896</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02965764371401469</v>
+        <v>0.02868814248768888</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02846911688293461</v>
+        <v>0.0284691168829346</v>
       </c>
       <c r="L6" t="n">
         <v>0.02843460531172633</v>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02849227891730983</v>
+        <v>0.02849227891730982</v>
       </c>
       <c r="C7" t="n">
         <v>0.02847310442807461</v>
@@ -4288,16 +4288,16 @@
         <v>0.02851785205052091</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0286634122525277</v>
+        <v>0.02866341225252769</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0286634122525277</v>
+        <v>0.02866341225252769</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02853010454670747</v>
+        <v>0.02853010454670746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0285273274119558</v>
+        <v>0.02852732741195579</v>
       </c>
       <c r="I7" t="n">
         <v>0.02864730573860448</v>
@@ -4306,10 +4306,10 @@
         <v>0.02868640502011113</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02853161825293392</v>
+        <v>0.02853161825293391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02850051602022071</v>
+        <v>0.0285005160202207</v>
       </c>
     </row>
     <row r="8">
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02952074413464759</v>
+        <v>0.02952074413464758</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03088487601354345</v>
+        <v>0.03088487601354343</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03119754862156103</v>
+        <v>0.03119754862156101</v>
       </c>
       <c r="E8" t="n">
         <v>0.03068341613320838</v>
@@ -4334,22 +4334,22 @@
         <v>0.02972880891947327</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03092612324003765</v>
+        <v>0.03092612324003763</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0309233461052881</v>
+        <v>0.03092334610528808</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03104332443193466</v>
+        <v>0.03104332443193463</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03108269247657827</v>
+        <v>0.03108269247657824</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02953468046237515</v>
+        <v>0.02953468046237514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03232505867191693</v>
+        <v>0.03232505867191691</v>
       </c>
     </row>
     <row r="9">
@@ -4362,34 +4362,34 @@
         <v>0.02999273086077621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03069931869035208</v>
+        <v>0.03069931869035207</v>
       </c>
       <c r="D9" t="n">
-        <v>0.030744173590105</v>
+        <v>0.03074417359010499</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0317110760026274</v>
+        <v>0.03171107600262738</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03087356120588202</v>
+        <v>0.03087356120588199</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03075631880898494</v>
+        <v>0.03075631880898492</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03075354167423328</v>
+        <v>0.03075354167423325</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03087352000088196</v>
+        <v>0.03087352000088193</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03091261928238861</v>
+        <v>0.03091261928238859</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03033732319678949</v>
+        <v>0.02984396807252336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03072673028249818</v>
+        <v>0.03072673028249816</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04394561500805001</v>
+        <v>0.006872754708786644</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04392945291084427</v>
+        <v>0.00687137268117303</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04398824430381144</v>
+        <v>0.006874998203953969</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04406592768471389</v>
+        <v>0.0068522420571715</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04406592768471389</v>
+        <v>0.006852201251794603</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04399307286305626</v>
+        <v>0.006875252321436733</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04399838858134097</v>
+        <v>0.006873814013184109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04409799957581929</v>
+        <v>0.00688087379957083</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04509203688285734</v>
+        <v>0.007623226634715133</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04544716009393999</v>
+        <v>0.008081021007326467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0439634083599133</v>
+        <v>0.006873042346772898</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04688737023288356</v>
+        <v>0.006766818662769325</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04686772031660987</v>
+        <v>0.006761786288761675</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04693640275364123</v>
+        <v>0.006783470918134592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04703085584337551</v>
+        <v>0.006778362685593326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04703085584337551</v>
+        <v>0.00677832188021643</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04694195659700581</v>
+        <v>0.006785416617909465</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0469487017194726</v>
+        <v>0.006786286475253074</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04706543712407904</v>
+        <v>0.006825387730080814</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04807304666854809</v>
+        <v>0.00808200559228427</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0483969240129045</v>
+        <v>0.008777331191908129</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04690777579791711</v>
+        <v>0.006774275390141173</v>
       </c>
     </row>
     <row r="4">
@@ -4595,28 +4595,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02936580889323375</v>
+        <v>0.02936580889323374</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02958333405882498</v>
+        <v>0.02958333405882497</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03014584063198044</v>
+        <v>0.03014584063198043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03128982570046051</v>
+        <v>0.03128982570046054</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03128982570046051</v>
+        <v>0.03128982570046054</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03026181609650592</v>
+        <v>0.03026181609650593</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03059776588385051</v>
+        <v>0.0305977658838505</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03128976956021984</v>
+        <v>0.03128976956021982</v>
       </c>
       <c r="J5" t="n">
         <v>0.03259974524289372</v>
@@ -4625,7 +4625,7 @@
         <v>0.03026481349568233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0302544390700102</v>
+        <v>0.03025443907001019</v>
       </c>
     </row>
     <row r="6">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02839734624331992</v>
+        <v>0.02941907363779988</v>
       </c>
       <c r="C6" t="n">
         <v>0.02835943092795816</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02841393083028792</v>
+        <v>0.02841391919188069</v>
       </c>
       <c r="E6" t="n">
         <v>0.02839476331711562</v>
@@ -4650,22 +4650,22 @@
         <v>0.02847565431854325</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02944406159151886</v>
+        <v>0.02842233419703891</v>
       </c>
       <c r="H6" t="n">
         <v>0.02951758675048365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02949001601056553</v>
+        <v>0.02846828861608557</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02861369440338655</v>
+        <v>0.02957249789268893</v>
       </c>
       <c r="K6" t="n">
         <v>0.02843098255203333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02839987842686004</v>
+        <v>0.02839987842686016</v>
       </c>
     </row>
     <row r="7">
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02841986185461975</v>
+        <v>0.02841986185461976</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02840740966845593</v>
+        <v>0.02840740966845592</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02844509544536479</v>
+        <v>0.0284450954453648</v>
       </c>
       <c r="E7" t="n">
         <v>0.02850326919392867</v>
@@ -4693,16 +4693,16 @@
         <v>0.02844484980833874</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02845134562427225</v>
+        <v>0.02845134562427226</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02849080422738541</v>
+        <v>0.0284908042273854</v>
       </c>
       <c r="J7" t="n">
         <v>0.02857521513287383</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02845155694585519</v>
+        <v>0.0284515569458552</v>
       </c>
       <c r="L7" t="n">
         <v>0.0284305736183753</v>
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02943474802072</v>
+        <v>0.02943474802071999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03077195368313404</v>
+        <v>0.03077195368312344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03107480878667909</v>
+        <v>0.03107480878667908</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03048831429505323</v>
+        <v>0.03048831429505322</v>
       </c>
       <c r="F8" t="n">
         <v>0.02955560679816256</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03079713668148123</v>
+        <v>0.03079713668148122</v>
       </c>
       <c r="H8" t="n">
         <v>0.03080363249741753</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03084309110052789</v>
+        <v>0.03084309110052788</v>
       </c>
       <c r="J8" t="n">
         <v>0.03092776484329457</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02944160020721942</v>
+        <v>0.02944160020721943</v>
       </c>
       <c r="L8" t="n">
         <v>0.03217988736140667</v>
@@ -4764,10 +4764,10 @@
         <v>0.03046065817257465</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03128267056964501</v>
+        <v>0.031282670569645</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03050631485028195</v>
+        <v>0.03050631485028194</v>
       </c>
       <c r="G9" t="n">
         <v>0.03046030431767107</v>
@@ -4782,7 +4782,7 @@
         <v>0.03059066964220616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03006139484622395</v>
+        <v>0.03006139484622396</v>
       </c>
       <c r="L9" t="n">
         <v>0.03044602812770763</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04813567707127263</v>
+        <v>0.007689051154563467</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04715415737312478</v>
+        <v>0.008876697655600152</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04887256225451098</v>
+        <v>0.007727831958185443</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0475638690105667</v>
+        <v>0.009222478655362106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04592079409050116</v>
+        <v>0.007854791354000102</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04893101094214602</v>
+        <v>0.007730907996527231</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05565301983342469</v>
+        <v>0.008085478990121797</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04555698138073593</v>
+        <v>0.007553405351633568</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05216697397116644</v>
+        <v>0.009761847641259083</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04818729315976187</v>
+        <v>0.009267614473374576</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06257474246420615</v>
+        <v>0.008457497741756274</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05167250166799837</v>
+        <v>0.008482034383285581</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05030259251821578</v>
+        <v>0.00970671171243782</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05252007227402834</v>
+        <v>0.008759924006406308</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05071354296457876</v>
+        <v>0.01027317985273666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04907046804451322</v>
+        <v>0.008015588841208569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05258730037241779</v>
+        <v>0.008784014978489933</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06031967562840725</v>
+        <v>0.01132728294160662</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04870521160514291</v>
+        <v>0.00751783617078109</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05595090036425043</v>
+        <v>0.01238565087272687</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05142830425906715</v>
+        <v>0.01052332557520398</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06827972628791767</v>
+        <v>0.01395845247885465</v>
       </c>
     </row>
     <row r="4">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03058175394805642</v>
+        <v>0.03058175394805644</v>
       </c>
       <c r="C4" t="n">
         <v>0.0288844219530574</v>
@@ -4966,13 +4966,13 @@
         <v>0.02891892149828424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03104995461494515</v>
+        <v>0.03104995461494517</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03504907283668087</v>
+        <v>0.03504907283668088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02901961002217229</v>
+        <v>0.02901961002217228</v>
       </c>
       <c r="J4" t="n">
         <v>0.03155968041796114</v>
@@ -4981,7 +4981,7 @@
         <v>0.02941104675957781</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03916234800331944</v>
+        <v>0.03916234800331945</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07138654583479956</v>
+        <v>0.07138654583479991</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04456279684235391</v>
+        <v>0.04456279684235388</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08028592233328656</v>
+        <v>0.08028592233328655</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04456280031577338</v>
+        <v>0.04456280031577332</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04456280031577338</v>
+        <v>0.04456280031577332</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08212686230809899</v>
+        <v>0.0821268623080991</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1678875518030927</v>
+        <v>0.1678875518030925</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0445622640066357</v>
+        <v>0.04456226400663568</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09382216463277802</v>
+        <v>0.09382216463277804</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05159383022479246</v>
+        <v>0.05159383022479266</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09313866765586827</v>
+        <v>0.0931386676558682</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03268058351742792</v>
+        <v>0.03128826067010834</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02965187909681429</v>
+        <v>0.02965187909681428</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0317521054418386</v>
+        <v>0.03175211490951257</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02957072288842353</v>
+        <v>0.02957072288842352</v>
       </c>
       <c r="F6" t="n">
         <v>0.02971693652702893</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03314878418431663</v>
+        <v>0.03175646133699703</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03723563721061221</v>
+        <v>0.03723563721061222</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03111843959154377</v>
+        <v>0.03111843959154376</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03367065635886427</v>
+        <v>0.03234906384634141</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03007407682333271</v>
+        <v>0.03007407682333268</v>
       </c>
       <c r="L6" t="n">
         <v>0.03992770954726715</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03147822956131627</v>
+        <v>0.03147822956131628</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02991661847115031</v>
+        <v>0.0299166184711503</v>
       </c>
       <c r="D7" t="n">
         <v>0.03191615157195266</v>
@@ -5089,7 +5089,7 @@
         <v>0.03194643022820499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03594554844994071</v>
+        <v>0.0359455484499407</v>
       </c>
       <c r="I7" t="n">
         <v>0.02991608563543212</v>
@@ -5101,7 +5101,7 @@
         <v>0.03030752237283764</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04005882361657927</v>
+        <v>0.04005882361657926</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03274419174082567</v>
+        <v>0.03274419174082569</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03291666242936581</v>
+        <v>0.03291666242937553</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03527716936998579</v>
+        <v>0.03527716936998578</v>
       </c>
       <c r="E8" t="n">
         <v>0.03244220169838245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03123669110017637</v>
+        <v>0.03123669110017636</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03494753077590913</v>
+        <v>0.03494753077590914</v>
       </c>
       <c r="H8" t="n">
         <v>0.03894664899764495</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03291718618313627</v>
+        <v>0.03291718618313626</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03545759758308761</v>
+        <v>0.03545759758308762</v>
       </c>
       <c r="K8" t="n">
         <v>0.03154125346635527</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04487242127955064</v>
+        <v>0.04487242127955062</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03423200380224903</v>
+        <v>0.03423200380224905</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03383707971423991</v>
+        <v>0.0338370797142399</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03583673794510288</v>
+        <v>0.03583673794510289</v>
       </c>
       <c r="E9" t="n">
         <v>0.0351834129897558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0338370812896699</v>
+        <v>0.03383708128966989</v>
       </c>
       <c r="G9" t="n">
         <v>0.03586689147129458</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03986600969303033</v>
+        <v>0.03986600969303034</v>
       </c>
       <c r="I9" t="n">
         <v>0.03383654687852171</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03637661727431057</v>
+        <v>0.03637661727431059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03355200063698701</v>
+        <v>0.03355200063698702</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04397928485966886</v>
+        <v>0.04397928485966885</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04717978002418393</v>
+        <v>0.007606271422085338</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04728472908213835</v>
+        <v>0.008848684089980246</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04871657388533209</v>
+        <v>0.007687149830679107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0477004271871258</v>
+        <v>0.009199216450245398</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04604645718902977</v>
+        <v>0.007822461618923589</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04859355407270718</v>
+        <v>0.007680675542277689</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05371048465540602</v>
+        <v>0.007949946437015439</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04569086881958675</v>
+        <v>0.007527982365324446</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05059689030526414</v>
+        <v>0.009649532500890495</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04812914590431018</v>
+        <v>0.009228384790761355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06116379107088724</v>
+        <v>0.0083500307641789</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05056993011332209</v>
+        <v>0.008108095649802074</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05045033577748717</v>
+        <v>0.009734407347686332</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05233756139953175</v>
+        <v>0.008682762814882632</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05086713019579592</v>
+        <v>0.01030901724955222</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0492131601976999</v>
+        <v>0.008036457838759175</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05219606313153571</v>
+        <v>0.008639027186026663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05808220257251902</v>
+        <v>0.01057757388407124</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04885638004876679</v>
+        <v>0.007550102858072531</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05414134989457739</v>
+        <v>0.0117820083873117</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05135904306216105</v>
+        <v>0.01047726140773735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06665379888029933</v>
+        <v>0.01340899615330363</v>
       </c>
     </row>
     <row r="4">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0299696459675139</v>
+        <v>0.02996964596751391</v>
       </c>
       <c r="C4" t="n">
         <v>0.02895381108456386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03088320479848666</v>
+        <v>0.03088320479848667</v>
       </c>
       <c r="E4" t="n">
         <v>0.0289842556898364</v>
@@ -5362,7 +5362,7 @@
         <v>0.0289842556898364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03080581580801488</v>
+        <v>0.0308058158080149</v>
       </c>
       <c r="H4" t="n">
         <v>0.0338508197788695</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05999439509057947</v>
+        <v>0.0599943950905795</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04472052803048716</v>
+        <v>0.04472052803048714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07482239022664519</v>
+        <v>0.07482239022664545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04472053088706249</v>
+        <v>0.04472053088706247</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04472053088706249</v>
+        <v>0.04472053088706247</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07480559628253471</v>
+        <v>0.0748055962825349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1374925471447039</v>
+        <v>0.1374925471447037</v>
       </c>
       <c r="I5" t="n">
         <v>0.04472005908665106</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07313472961645991</v>
+        <v>0.07313472961645988</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04857921413195968</v>
+        <v>0.04857921413195974</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09600052653895078</v>
+        <v>0.09600052653895087</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03194683270929957</v>
+        <v>0.03066346628090408</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0296917475447891</v>
+        <v>0.02969174754478909</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03160208861538297</v>
+        <v>0.03160208861538301</v>
       </c>
       <c r="E6" t="n">
         <v>0.02961244841167743</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02974499051871684</v>
+        <v>0.02974499051871685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03278300254980052</v>
+        <v>0.03149963612140506</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03589524964447405</v>
+        <v>0.03589524964447404</v>
       </c>
       <c r="I6" t="n">
         <v>0.03103477610602233</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03256170044246768</v>
+        <v>0.03135078263831421</v>
       </c>
       <c r="K6" t="n">
         <v>0.03000239050860296</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03901830300522618</v>
+        <v>0.03901830300522619</v>
       </c>
     </row>
     <row r="7">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03077866873434565</v>
+        <v>0.03077866873434564</v>
       </c>
       <c r="C7" t="n">
         <v>0.02986708107490448</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03169211089882393</v>
+        <v>0.03169211089882395</v>
       </c>
       <c r="E7" t="n">
         <v>0.0298651324168142</v>
@@ -5482,7 +5482,7 @@
         <v>0.0298651324168142</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03161483857484661</v>
+        <v>0.03161483857484662</v>
       </c>
       <c r="H7" t="n">
         <v>0.0346598425457012</v>
@@ -5494,7 +5494,7 @@
         <v>0.03138936176451775</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03014445406777767</v>
+        <v>0.03014445406777768</v>
       </c>
       <c r="L7" t="n">
         <v>0.03908898658374779</v>
@@ -5507,34 +5507,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03193483585726294</v>
+        <v>0.03193483585726295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03260092346960972</v>
+        <v>0.03260092346960974</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03475491535742643</v>
+        <v>0.03475491535742645</v>
       </c>
       <c r="E8" t="n">
         <v>0.03216918119981969</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03107221109010222</v>
+        <v>0.03107221109010223</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03435009244345733</v>
+        <v>0.03435009244345734</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03739509641431219</v>
+        <v>0.0373950964143122</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03260186599967912</v>
+        <v>0.03260186599967913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03412492596868865</v>
+        <v>0.03412492596868866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03127128884370773</v>
+        <v>0.03127128884370774</v>
       </c>
       <c r="L8" t="n">
         <v>0.04347372859911101</v>
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0330595542672902</v>
+        <v>0.03305955426729021</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03314631604667527</v>
+        <v>0.03314631604667529</v>
       </c>
       <c r="D9" t="n">
         <v>0.03497146280772524</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03429839138148421</v>
+        <v>0.03429839138148422</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03314631742293554</v>
+        <v>0.03314631742293555</v>
       </c>
       <c r="G9" t="n">
         <v>0.03489407354661742</v>
@@ -5568,16 +5568,16 @@
         <v>0.037939077517472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0331458471028392</v>
+        <v>0.03314584710283922</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03466859673628854</v>
+        <v>0.03466859673628855</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03216658882117872</v>
+        <v>0.03284524156770029</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04236822155551855</v>
+        <v>0.04236822155551854</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04668477750059651</v>
+        <v>0.0075257485503008</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04749288024203219</v>
+        <v>0.008594232351505053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04788020633593394</v>
+        <v>0.007588661595591697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04778040548624195</v>
+        <v>0.008837728011564596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04652577874162486</v>
+        <v>0.007793374904273578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0479301455849627</v>
+        <v>0.007591289799080744</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05095301115744733</v>
+        <v>0.00774932851547656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0461697785809625</v>
+        <v>0.007498725229078684</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04840588692657549</v>
+        <v>0.008988467060728072</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04779978784971847</v>
+        <v>0.009153530748178974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05947122258606372</v>
+        <v>0.008205860909387207</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05004685556881282</v>
+        <v>0.007895038861151549</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05077685677102944</v>
+        <v>0.009514279557371611</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0514218463617881</v>
+        <v>0.008341254532201874</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0510653555051311</v>
+        <v>0.00991277414968279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04981072876051402</v>
+        <v>0.008188904252698574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05147928684305547</v>
+        <v>0.008362459191679423</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05495678371391979</v>
+        <v>0.009505128487792372</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04945421965123695</v>
+        <v>0.007702265590676049</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05176216284833961</v>
+        <v>0.01030371214183275</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0510270812649007</v>
+        <v>0.01032251685724758</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06475332348025155</v>
+        <v>0.01273786969795205</v>
       </c>
     </row>
     <row r="4">
@@ -5749,31 +5749,31 @@
         <v>0.02926709924101203</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03039448038068906</v>
+        <v>0.03039448038068907</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02929613089560027</v>
+        <v>0.02929613089560028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02929613089560027</v>
+        <v>0.02929613089560028</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03042021617118537</v>
+        <v>0.03042021617118536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03222056071610066</v>
+        <v>0.03222056071610067</v>
       </c>
       <c r="I4" t="n">
         <v>0.02935295548492841</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02966088610241421</v>
+        <v>0.02966088610241422</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02915042681316557</v>
+        <v>0.02915042681316558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03728246949460096</v>
+        <v>0.03728246949460098</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>0.0546394418979539</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04926387934146233</v>
+        <v>0.04926387934146235</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06575821266821653</v>
+        <v>0.0657582126682166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0492638817826215</v>
+        <v>0.04926388178262156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0492638817826215</v>
+        <v>0.04926388178262156</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06754743775675004</v>
+        <v>0.06754743775675001</v>
       </c>
       <c r="H5" t="n">
         <v>0.1037875320762363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04926356612380147</v>
+        <v>0.0492635661238016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05700157007237127</v>
+        <v>0.05700157007237125</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04500604169834101</v>
+        <v>0.04500604169834096</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2067752331449083</v>
+        <v>0.07571086986663332</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03038250762843064</v>
+        <v>0.03038250762843065</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03001315941308092</v>
+        <v>0.03001315941308095</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03235010490595206</v>
+        <v>0.03110382861199992</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02993272184536874</v>
+        <v>0.02993272184536873</v>
       </c>
       <c r="F6" t="n">
         <v>0.03005072766744589</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0311188752069184</v>
+        <v>0.03237566947789181</v>
       </c>
       <c r="H6" t="n">
         <v>0.0342385177579466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03130840879163487</v>
+        <v>0.03005161452066143</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03043277412099627</v>
+        <v>0.03161895638054512</v>
       </c>
       <c r="K6" t="n">
         <v>0.02982883903775237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03802899365718014</v>
+        <v>0.03802899365718016</v>
       </c>
     </row>
     <row r="7">
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0304682691450298</v>
+        <v>0.03046826914502981</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03013768925492134</v>
+        <v>0.03013768925492133</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03117878388475903</v>
+        <v>0.03117878388475902</v>
       </c>
       <c r="E7" t="n">
         <v>0.03013563689690271</v>
@@ -5881,13 +5881,13 @@
         <v>0.03120463672351754</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03300498126843284</v>
+        <v>0.03300498126843286</v>
       </c>
       <c r="I7" t="n">
         <v>0.0301373760372606</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0304453066547464</v>
+        <v>0.03044530665474641</v>
       </c>
       <c r="K7" t="n">
         <v>0.02993484736549776</v>
@@ -5903,22 +5903,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03159630208907811</v>
+        <v>0.03159630208907813</v>
       </c>
       <c r="C8" t="n">
         <v>0.03280422613321259</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03416628770503746</v>
+        <v>0.03416628770503749</v>
       </c>
       <c r="E8" t="n">
         <v>0.03238317800223069</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03131338495086106</v>
+        <v>0.03131338495086107</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03387269020484364</v>
+        <v>0.03387269020484366</v>
       </c>
       <c r="H8" t="n">
         <v>0.03567303474975932</v>
@@ -5927,13 +5927,13 @@
         <v>0.0328054295185867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03311366279401401</v>
+        <v>0.03311366279401402</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03103427363743577</v>
+        <v>0.03103427363743578</v>
       </c>
       <c r="L8" t="n">
-        <v>0.042343623753669</v>
+        <v>0.04234362375366903</v>
       </c>
     </row>
     <row r="9">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03245662975746</v>
+        <v>0.03245662975745999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03303427685763327</v>
+        <v>0.03303427685763329</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03407548894689257</v>
+        <v>0.03407548894689258</v>
       </c>
       <c r="E9" t="n">
         <v>0.03408235302017178</v>
@@ -5958,22 +5958,22 @@
         <v>0.03303427822714249</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0341012243262295</v>
+        <v>0.03410122432622949</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0359015688711448</v>
+        <v>0.03590156887114482</v>
       </c>
       <c r="I9" t="n">
         <v>0.03303396363997255</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03334189425745836</v>
+        <v>0.03334189425745838</v>
       </c>
       <c r="K9" t="n">
         <v>0.03230520485608993</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04096347764964511</v>
+        <v>0.04096347764964513</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04467094092625112</v>
+        <v>0.007212243212030844</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04617400579721184</v>
+        <v>0.008527685910779837</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04536189474035609</v>
+        <v>0.007248606738922384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04656899454941795</v>
+        <v>0.008859325421548228</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04496779195236376</v>
+        <v>0.007526489411953556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04568951831163026</v>
+        <v>0.007265848916765713</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04778614133646904</v>
+        <v>0.007375215359309277</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04458265367327593</v>
+        <v>0.00720768318506727</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0493903720252934</v>
+        <v>0.009266451454015397</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04728039668282919</v>
+        <v>0.008918580818212047</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04830855006697938</v>
+        <v>0.007404683429272373</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04768159012424298</v>
+        <v>0.007019517380366906</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04917060296974166</v>
+        <v>0.009168728698076386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0484763301411151</v>
+        <v>0.007276559281957994</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0495666288414444</v>
+        <v>0.009713738044862341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04796542624439021</v>
+        <v>0.007513676740520147</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04885316511509873</v>
+        <v>0.007400432204221118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05126531533553971</v>
+        <v>0.008187187407937568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0475801922453065</v>
+        <v>0.006987164972204747</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05276204286157685</v>
+        <v>0.01110604198269913</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05038075577518447</v>
+        <v>0.01000690534390317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05186540961869491</v>
+        <v>0.008393847987235265</v>
       </c>
     </row>
     <row r="4">
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02843943117507396</v>
+        <v>0.02843943117507397</v>
       </c>
       <c r="C4" t="n">
         <v>0.02824322261081936</v>
@@ -6163,7 +6163,7 @@
         <v>0.02836372069283287</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02986820515202173</v>
+        <v>0.02986820515202174</v>
       </c>
       <c r="K4" t="n">
         <v>0.02879446574626403</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0374617830616218</v>
+        <v>0.03746178306162188</v>
       </c>
       <c r="C5" t="n">
         <v>0.03657108870698893</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04384524960589991</v>
+        <v>0.04384524960589993</v>
       </c>
       <c r="E5" t="n">
         <v>0.03657109207773229</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03657109207773229</v>
+        <v>0.0365710920777323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04797704841553782</v>
+        <v>0.04797704841553781</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07177312188572671</v>
+        <v>0.0717731218857267</v>
       </c>
       <c r="I5" t="n">
         <v>0.03657086748095219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06542338823059986</v>
+        <v>0.0654233882305999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04324039975834226</v>
+        <v>0.04324039975834231</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08236441270286723</v>
+        <v>0.08236441270286725</v>
       </c>
     </row>
     <row r="6">
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02906722987834624</v>
+        <v>0.03023588988391637</v>
       </c>
       <c r="C6" t="n">
         <v>0.02894830884704664</v>
@@ -6228,25 +6228,25 @@
         <v>0.03066560042023459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02887099237001196</v>
+        <v>0.02887099237001197</v>
       </c>
       <c r="F6" t="n">
         <v>0.02898319296818776</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0296689943087971</v>
+        <v>0.03083765431436723</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0321660246700127</v>
+        <v>0.03092438059173688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02899151939610514</v>
+        <v>0.03016017940167526</v>
       </c>
       <c r="J6" t="n">
         <v>0.03168261314846117</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02940762173266372</v>
+        <v>0.02940762173266373</v>
       </c>
       <c r="L6" t="n">
         <v>0.03123894287948763</v>
@@ -6274,7 +6274,7 @@
         <v>0.0291127601554823</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02979167070418761</v>
+        <v>0.0297916707041876</v>
       </c>
       <c r="H7" t="n">
         <v>0.03104139338285977</v>
@@ -6286,7 +6286,7 @@
         <v>0.03061868025068451</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0295449408449268</v>
+        <v>0.02954494084492679</v>
       </c>
       <c r="L7" t="n">
         <v>0.03135190134583136</v>
@@ -6302,7 +6302,7 @@
         <v>0.03032847018790195</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03178418235134079</v>
+        <v>0.03178418235134078</v>
       </c>
       <c r="D8" t="n">
         <v>0.03258928703245001</v>
@@ -6311,10 +6311,10 @@
         <v>0.03136519490332124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03030064003936856</v>
+        <v>0.03030064003936855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03246256915104058</v>
+        <v>0.03246256915104059</v>
       </c>
       <c r="H8" t="n">
         <v>0.03371229182971277</v>
@@ -6323,13 +6323,13 @@
         <v>0.03178509423834861</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03328987984500052</v>
+        <v>0.03328987984500051</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03065504085845791</v>
+        <v>0.03065504085845792</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03562345134364494</v>
+        <v>0.03562345134364493</v>
       </c>
     </row>
     <row r="9">
@@ -6345,7 +6345,7 @@
         <v>0.03216480210443933</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03265103453861831</v>
+        <v>0.03265103453861832</v>
       </c>
       <c r="E9" t="n">
         <v>0.03324567219252671</v>
@@ -6360,10 +6360,10 @@
         <v>0.03409177846976671</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03216458087840259</v>
+        <v>0.03216458087840258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03366906533759145</v>
+        <v>0.03366906533759147</v>
       </c>
       <c r="K9" t="n">
         <v>0.03205263096617807</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04479928358268693</v>
+        <v>0.007193873487459772</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04670833181785636</v>
+        <v>0.008538116044296724</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04485995585638373</v>
+        <v>0.007197066548719589</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04710966531160649</v>
+        <v>0.008874817465398113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04549693389546989</v>
+        <v>0.007532386307523026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04533694200977978</v>
+        <v>0.007222169382602022</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04442002365324354</v>
+        <v>0.007171294885492926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04510756655810864</v>
+        <v>0.007210192255173754</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04888849546385498</v>
+        <v>0.00922948863684029</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04759600566249213</v>
+        <v>0.008918497785990701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04403887290941185</v>
+        <v>0.007152018098693668</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04782930541307191</v>
+        <v>0.007052067762369794</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04978406493315583</v>
+        <v>0.009361314676383983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04789909109604687</v>
+        <v>0.007073405003185326</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05018626301291635</v>
+        <v>0.009915087717969758</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04857353159677974</v>
+        <v>0.007699187156359802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04844772397983635</v>
+        <v>0.007252304707213289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04739372203257431</v>
+        <v>0.006908511837337841</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04818458593456551</v>
+        <v>0.007167080336489689</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05218206798899893</v>
+        <v>0.01091747122419775</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05074224195847288</v>
+        <v>0.01011948213185678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04695468867915283</v>
+        <v>0.006766939348895197</v>
       </c>
     </row>
     <row r="4">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02848720385505611</v>
+        <v>0.02848720385505612</v>
       </c>
       <c r="C4" t="n">
         <v>0.02856527074823381</v>
@@ -6547,10 +6547,10 @@
         <v>0.0285931818041815</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0285931818041815</v>
+        <v>0.02859318180418151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0288035591864916</v>
+        <v>0.02880355918649161</v>
       </c>
       <c r="H4" t="n">
         <v>0.02826207756487548</v>
@@ -6559,7 +6559,7 @@
         <v>0.02865051961633846</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0295302282456718</v>
+        <v>0.02953022824567181</v>
       </c>
       <c r="K4" t="n">
         <v>0.02894713253128138</v>
@@ -6578,19 +6578,19 @@
         <v>0.03830464219206439</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04078971234711104</v>
+        <v>0.04078971234711106</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03819019148381792</v>
+        <v>0.03819019148381793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04078971501574287</v>
+        <v>0.04078971501574288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04078971501574287</v>
+        <v>0.04078971501574288</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0430669634934054</v>
+        <v>0.04306696349340553</v>
       </c>
       <c r="H5" t="n">
         <v>0.03501645397014591</v>
@@ -6599,13 +6599,13 @@
         <v>0.0407896102293862</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05604544614757198</v>
+        <v>0.05604544614757196</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04499457943278155</v>
+        <v>0.04499457943278154</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03538695389256104</v>
+        <v>0.03538695389256103</v>
       </c>
     </row>
     <row r="6">
@@ -6621,7 +6621,7 @@
         <v>0.02925802381926704</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02914863981012885</v>
+        <v>0.0291486495115434</v>
       </c>
       <c r="E6" t="n">
         <v>0.02918137839092789</v>
@@ -6630,22 +6630,22 @@
         <v>0.02927796722964082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02943682971667383</v>
+        <v>0.03049836407858366</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0288850951019925</v>
+        <v>0.03000585950653761</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02928379014652068</v>
+        <v>0.03034532450843053</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03123027725060555</v>
+        <v>0.03022841701933551</v>
       </c>
       <c r="K6" t="n">
         <v>0.02958373019438238</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02865624019464091</v>
+        <v>0.02865624019464092</v>
       </c>
     </row>
     <row r="7">
@@ -6670,13 +6670,13 @@
         <v>0.0293224985095564</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02947692338878174</v>
+        <v>0.02947692338878175</v>
       </c>
       <c r="H7" t="n">
         <v>0.02893544176716563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0293238838186286</v>
+        <v>0.02932388381862859</v>
       </c>
       <c r="J7" t="n">
         <v>0.03020359244796194</v>
@@ -6695,22 +6695,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03019384706432854</v>
+        <v>0.03019384706432855</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03174276885045866</v>
+        <v>0.03174276885045865</v>
       </c>
       <c r="D8" t="n">
         <v>0.03190392948203635</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03136365093982332</v>
+        <v>0.03136365093982333</v>
       </c>
       <c r="F8" t="n">
         <v>0.03040039813610656</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03189671524590407</v>
+        <v>0.03189671524590408</v>
       </c>
       <c r="H8" t="n">
         <v>0.03135523362428771</v>
@@ -6719,7 +6719,7 @@
         <v>0.03174367567575092</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03262365679443732</v>
+        <v>0.03262365679443733</v>
       </c>
       <c r="K8" t="n">
         <v>0.03062802055253623</v>
@@ -6738,19 +6738,19 @@
         <v>0.03093263437477456</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03190385156352783</v>
+        <v>0.03190385156352784</v>
       </c>
       <c r="D9" t="n">
         <v>0.03177650150212413</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03283603804154987</v>
+        <v>0.03283603804154988</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03190385413741533</v>
+        <v>0.03190385413741534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03205678901595613</v>
+        <v>0.03205678901595615</v>
       </c>
       <c r="H9" t="n">
         <v>0.03151530739434003</v>
@@ -6759,13 +6759,13 @@
         <v>0.03190374944580299</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03278345807513635</v>
+        <v>0.03278345807513636</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03171333149590237</v>
+        <v>0.03173232057178971</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03128888120939276</v>
+        <v>0.03128888120939278</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04545583177263488</v>
+        <v>0.007214851584424843</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04657755796613761</v>
+        <v>0.008297313966362501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0445019104916545</v>
+        <v>0.007164648602047114</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0468550979509388</v>
+        <v>0.008530887547614512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04563032947176258</v>
+        <v>0.007511385939484963</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04520895681747606</v>
+        <v>0.007201859045867988</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04431986442473776</v>
+        <v>0.00715250692767171</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04525943445231268</v>
+        <v>0.007204612701073358</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04785606386925943</v>
+        <v>0.008680973708567116</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04744744080515337</v>
+        <v>0.008892757507081165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04424223992821975</v>
+        <v>0.007149426400137463</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04863190208107698</v>
+        <v>0.007291275971680643</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04972360932158837</v>
+        <v>0.009023963154077648</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0475346950037515</v>
+        <v>0.006934392525150604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05000194516375556</v>
+        <v>0.009407651969120722</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04877717668457935</v>
+        <v>0.00772480506833105</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04834794474265146</v>
+        <v>0.007199059611779507</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04732592445815127</v>
+        <v>0.006865445673253231</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0484068858477542</v>
+        <v>0.007218151313986457</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05113457046903154</v>
+        <v>0.009909481848345558</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05061962921297047</v>
+        <v>0.01005179230339576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04723601635805719</v>
+        <v>0.006837778892971589</v>
       </c>
     </row>
     <row r="4">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0288820579757534</v>
+        <v>0.02888205797575339</v>
       </c>
       <c r="C4" t="n">
         <v>0.02867305441830041</v>
@@ -6946,7 +6946,7 @@
         <v>0.02870002980639543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02873201527830625</v>
+        <v>0.02873201527830623</v>
       </c>
       <c r="H4" t="n">
         <v>0.02820709426658551</v>
@@ -6958,10 +6958,10 @@
         <v>0.02928745835020167</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02886669502238479</v>
+        <v>0.02886669502238478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02816102205594099</v>
+        <v>0.02816102205594098</v>
       </c>
     </row>
     <row r="5">
@@ -6971,25 +6971,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04461079200810288</v>
+        <v>0.04461079200810287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04251865334022485</v>
+        <v>0.04251865334022498</v>
       </c>
       <c r="D5" t="n">
         <v>0.03531600653694261</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04251865562443859</v>
+        <v>0.04251865562443866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04251865562443859</v>
+        <v>0.04251865562443866</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04227722102877477</v>
+        <v>0.0422772210287747</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03434974980742988</v>
+        <v>0.03434974980742986</v>
       </c>
       <c r="I5" t="n">
         <v>0.04251858854725476</v>
@@ -6998,10 +6998,10 @@
         <v>0.0523997978875026</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04345158129929846</v>
+        <v>0.04345158129929844</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0337658609425437</v>
+        <v>0.03882095429164702</v>
       </c>
     </row>
     <row r="6">
@@ -7014,28 +7014,28 @@
         <v>0.02953001807757407</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02937185087916472</v>
+        <v>0.02937185087916469</v>
       </c>
       <c r="D6" t="n">
         <v>0.02894059484227154</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02929381545149424</v>
+        <v>0.02929381545149425</v>
       </c>
       <c r="F6" t="n">
         <v>0.02938754651850137</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03045213835789244</v>
+        <v>0.02937997538012692</v>
       </c>
       <c r="H6" t="n">
         <v>0.02996516086950078</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0293931897666085</v>
+        <v>0.02939318976660849</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03100227418030637</v>
+        <v>0.02999812178198344</v>
       </c>
       <c r="K6" t="n">
         <v>0.02951864261360386</v>
@@ -7051,22 +7051,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02954757964322948</v>
+        <v>0.02954757964322947</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02941081612523414</v>
+        <v>0.02941081612523413</v>
       </c>
       <c r="D7" t="n">
         <v>0.02898039760291226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02940929184438979</v>
+        <v>0.02940929184438978</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02940929184438979</v>
+        <v>0.02940929184438978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02939753694578233</v>
+        <v>0.02939753694578232</v>
       </c>
       <c r="H7" t="n">
         <v>0.0288726159340616</v>
@@ -7075,10 +7075,10 @@
         <v>0.0294107513322639</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02995298001767775</v>
+        <v>0.02995298001767774</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02953221668986087</v>
+        <v>0.02953221668986086</v>
       </c>
       <c r="L7" t="n">
         <v>0.02882654372341707</v>
@@ -7097,7 +7097,7 @@
         <v>0.03181062842430477</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03166648550914456</v>
+        <v>0.03166648550914457</v>
       </c>
       <c r="E8" t="n">
         <v>0.03143466258598143</v>
@@ -7106,10 +7106,10 @@
         <v>0.03047942249067962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03179839401643068</v>
+        <v>0.03179839401643067</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03127347300470966</v>
+        <v>0.03127347300470965</v>
       </c>
       <c r="I8" t="n">
         <v>0.03181160840291226</v>
@@ -7118,10 +7118,10 @@
         <v>0.03235410731448594</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03053253553187024</v>
+        <v>0.03053253553187023</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03266370008807866</v>
+        <v>0.03266370008807865</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03114451941252094</v>
+        <v>0.03114451941252093</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03176416251617715</v>
+        <v>0.03176416251617714</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03133386092487336</v>
+        <v>0.03133386092487335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03263704250917111</v>
+        <v>0.0326370425091711</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03176416471965621</v>
+        <v>0.0317641647196562</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03175088333672533</v>
+        <v>0.03175088333672532</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03122596232500461</v>
+        <v>0.0312259623250046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03176409772320691</v>
+        <v>0.0317640977232069</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03230632640862077</v>
+        <v>0.03230632640862075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03142951741676344</v>
+        <v>0.03142951741676343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03117989011436008</v>
+        <v>0.03117989011436007</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04656467280826547</v>
+        <v>0.007539701725224817</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04686055980496729</v>
+        <v>0.008784425179469925</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04862832639227393</v>
+        <v>0.007648307714605023</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04726313747035189</v>
+        <v>0.009123853696442197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04563962472635834</v>
+        <v>0.007772448950803625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04829838897336189</v>
+        <v>0.007630943763556179</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05537095096182688</v>
+        <v>0.008004359003465673</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04527688614229022</v>
+        <v>0.007471996291689214</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05021135187530338</v>
+        <v>0.009554446548666138</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04806992855536639</v>
+        <v>0.00919132384773011</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06002803151487083</v>
+        <v>0.008255501285572424</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04986317585134688</v>
+        <v>0.007857371994187044</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04996462794909365</v>
+        <v>0.009546843535087996</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05223680495750869</v>
+        <v>0.008628001849519231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05036840046071996</v>
+        <v>0.01010320092374035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04874488771672641</v>
+        <v>0.007872487513148053</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0518573085794294</v>
+        <v>0.008507730803677751</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05999279402570185</v>
+        <v>0.01116538572085428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04838092518691943</v>
+        <v>0.007376274552178035</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05370646797419537</v>
+        <v>0.01156571507162349</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05129162849016618</v>
+        <v>0.01043726931225191</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06534821361906701</v>
+        <v>0.0129573539542152</v>
       </c>
     </row>
     <row r="4">
@@ -7330,22 +7330,22 @@
         <v>0.02962525156227637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02869806496090568</v>
+        <v>0.02869806496090567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03085200617354936</v>
+        <v>0.03085200617354935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02873220250529033</v>
+        <v>0.02873220250529032</v>
       </c>
       <c r="F4" t="n">
         <v>0.02873220250529032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03065141472615994</v>
+        <v>0.03065141472615993</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03485870382603874</v>
+        <v>0.03485870382603872</v>
       </c>
       <c r="I4" t="n">
         <v>0.02883142585563099</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05541653309393463</v>
+        <v>0.05541653309393459</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04210669767255042</v>
+        <v>0.04210669767255038</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07611115070307273</v>
+        <v>0.07611115070307271</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04210670114145363</v>
+        <v>0.04210670114145362</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04210670114145363</v>
+        <v>0.04210670114145362</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07443169447394629</v>
+        <v>0.0744316944739461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1543239475398603</v>
+        <v>0.1543239475398602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0421062135985663</v>
+        <v>0.04210621359856628</v>
       </c>
       <c r="J5" t="n">
         <v>0.0727414272718306</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05035226870432259</v>
+        <v>0.05035226870432253</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2273220132460323</v>
+        <v>0.07557962096529806</v>
       </c>
     </row>
     <row r="6">
@@ -7410,34 +7410,34 @@
         <v>0.03030923782929562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02944622129710994</v>
+        <v>0.02944622129710995</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03156685217851461</v>
+        <v>0.03156685217851462</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02936665553169714</v>
+        <v>0.02936665553169712</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02950644984455379</v>
+        <v>0.02950644984455378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03267913675554504</v>
+        <v>0.03267913675554502</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03698584179354705</v>
+        <v>0.03698584179354703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03085914788501608</v>
+        <v>0.03085914788501607</v>
       </c>
       <c r="J6" t="n">
         <v>0.03245359926558473</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0299697115955404</v>
+        <v>0.02996971159554037</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03836083848193963</v>
+        <v>0.03836083848193962</v>
       </c>
     </row>
     <row r="7">
@@ -7447,25 +7447,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03048207783657194</v>
+        <v>0.03048207783657192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02968873620391067</v>
+        <v>0.02968873620391066</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03170870806577951</v>
+        <v>0.0317087080657795</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02968700557157082</v>
+        <v>0.02968700557157081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02968700557157082</v>
+        <v>0.02968700557157081</v>
       </c>
       <c r="G7" t="n">
         <v>0.0315082410004555</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03571553010033429</v>
+        <v>0.03571553010033427</v>
       </c>
       <c r="I7" t="n">
         <v>0.02968825212992655</v>
@@ -7474,10 +7474,10 @@
         <v>0.0312601908023202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03017812297397494</v>
+        <v>0.03017812297397493</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03848307104285131</v>
+        <v>0.03848307104285129</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03171586861335108</v>
+        <v>0.03171586861335107</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03260342870634399</v>
+        <v>0.03260342870633461</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03497348712935158</v>
+        <v>0.03497348712935156</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03214349285813876</v>
+        <v>0.03214349285813875</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03097488934632014</v>
+        <v>0.03097488934632013</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03442410652527397</v>
+        <v>0.03442410652527395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03863139562515298</v>
+        <v>0.03863139562515294</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03260411765474503</v>
+        <v>0.03260411765474501</v>
       </c>
       <c r="J8" t="n">
-        <v>0.034176386902791</v>
+        <v>0.03417638690279098</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03138066834874845</v>
+        <v>0.03138066834874843</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04315600429458793</v>
+        <v>0.0431560042945879</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03311181060644271</v>
+        <v>0.03311181060644269</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03343665284003387</v>
+        <v>0.03343665284003384</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03545674908037909</v>
+        <v>0.03545674908037906</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03472701447330714</v>
+        <v>0.03472701447330712</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03343665446516648</v>
+        <v>0.03343665446516646</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03525615763657871</v>
+        <v>0.03525615763657868</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03946344673645751</v>
+        <v>0.03946344673645748</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03343616876604977</v>
+        <v>0.03343616876604975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03500810743844342</v>
+        <v>0.0350081074384434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03327815948503513</v>
+        <v>0.03327815948503512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04223098767897455</v>
+        <v>0.04223098767897453</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04438428498681055</v>
+        <v>0.007279818878722075</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04645637840033676</v>
+        <v>0.008616639735762091</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04823070594531392</v>
+        <v>0.007482248374160743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04686391635222414</v>
+        <v>0.008959298543540203</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04523375070463324</v>
+        <v>0.007602356606811491</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04677455794515988</v>
+        <v>0.007405614197055516</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04552108798598484</v>
+        <v>0.0073364279676311</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04487543094897555</v>
+        <v>0.007305745011380853</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04916114538519303</v>
+        <v>0.009358821270154177</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04677578579918763</v>
+        <v>0.008946388097422261</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05346787732729387</v>
+        <v>0.007761672085800395</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04735168795960171</v>
+        <v>0.006962970526593422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04949680057114327</v>
+        <v>0.009313944352544588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05177586884558175</v>
+        <v>0.008397020500069281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0499053158564606</v>
+        <v>0.009876557949030683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0482751502088697</v>
+        <v>0.00763670407672294</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0501009970052551</v>
+        <v>0.007856531348468246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04865995020917587</v>
+        <v>0.007387147629003494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04791629461154485</v>
+        <v>0.007146827083942675</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05249400223856166</v>
+        <v>0.01109821129600282</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04980561149214539</v>
+        <v>0.009832674205224068</v>
       </c>
       <c r="L3" t="n">
-        <v>0.057799329822381</v>
+        <v>0.01039334119928039</v>
       </c>
     </row>
     <row r="4">
@@ -7738,22 +7738,22 @@
         <v>0.02845212369982419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02966892034627971</v>
+        <v>0.0296689203462797</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02892805864134439</v>
+        <v>0.02892805864134438</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02851963998124475</v>
+        <v>0.02851963998124474</v>
       </c>
       <c r="J4" t="n">
         <v>0.02969818045823462</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02849890875183993</v>
+        <v>0.02849890875183994</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03365037314722411</v>
+        <v>0.0336503731472241</v>
       </c>
     </row>
     <row r="5">
@@ -7766,34 +7766,34 @@
         <v>0.03357004980781676</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03811353143068929</v>
+        <v>0.03811353143068928</v>
       </c>
       <c r="D5" t="n">
         <v>0.06846647440996192</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03811353419235477</v>
+        <v>0.03811353419235478</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03811353419235477</v>
+        <v>0.03811353419235478</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05649672094438346</v>
+        <v>0.05649672094438347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04562226216226095</v>
+        <v>0.04562226216226101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03811320089387941</v>
+        <v>0.03811320089387939</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05965362041654998</v>
+        <v>0.05965362041654997</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03728315775093961</v>
+        <v>0.03728315775093963</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04503130954644046</v>
+        <v>0.1370322505735507</v>
       </c>
     </row>
     <row r="6">
@@ -7809,16 +7809,16 @@
         <v>0.0291193944275749</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03122706109921277</v>
+        <v>0.03122707080959167</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02904243627935578</v>
+        <v>0.02904243627935577</v>
       </c>
       <c r="F6" t="n">
         <v>0.02915904660254274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03031453025658778</v>
+        <v>0.0314759139967821</v>
       </c>
       <c r="H6" t="n">
         <v>0.03079128668283957</v>
@@ -7827,7 +7827,7 @@
         <v>0.03032663363174714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03041377518975085</v>
+        <v>0.03041377518975084</v>
       </c>
       <c r="K6" t="n">
         <v>0.02912022748309583</v>
@@ -7846,7 +7846,7 @@
         <v>0.02897645871049791</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02924456372477495</v>
+        <v>0.02924456372477496</v>
       </c>
       <c r="D7" t="n">
         <v>0.03126287716720375</v>
@@ -7873,7 +7873,7 @@
         <v>0.02922350195856026</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03437496635394442</v>
+        <v>0.03437496635394443</v>
       </c>
     </row>
     <row r="8">
@@ -7889,10 +7889,10 @@
         <v>0.03179816273292823</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03412182062033121</v>
+        <v>0.0341218206203312</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03139732590487191</v>
+        <v>0.0313973259048719</v>
       </c>
       <c r="F8" t="n">
         <v>0.03037888562019911</v>
@@ -7904,13 +7904,13 @@
         <v>0.03220749133730302</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0317990726772035</v>
+        <v>0.03179907267720351</v>
       </c>
       <c r="J8" t="n">
         <v>0.03297790126833097</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03028509256547114</v>
+        <v>0.03028509256547113</v>
       </c>
       <c r="L8" t="n">
         <v>0.03846118304630228</v>
@@ -7938,10 +7938,10 @@
         <v>0.03211773050434137</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03326667790422751</v>
+        <v>0.03326667790422752</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03252581619929221</v>
+        <v>0.0325258161992922</v>
       </c>
       <c r="I9" t="n">
         <v>0.03211739753919255</v>
@@ -7950,7 +7950,7 @@
         <v>0.03329593801618243</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03098051204586362</v>
+        <v>0.0315830746974631</v>
       </c>
       <c r="L9" t="n">
         <v>0.03724813070517189</v>

--- a/Results/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -515,25 +515,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007977678264216912</v>
+        <v>0.007977678264216918</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009270658354505594</v>
+        <v>0.009270658354505593</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008249148261677415</v>
+        <v>0.008249148261677419</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009643487227668101</v>
+        <v>0.009643487227668094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008188263545260793</v>
+        <v>0.008188263545260796</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008050553465520001</v>
+        <v>0.008050553465520003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008394948946009456</v>
+        <v>0.008394948946009458</v>
       </c>
       <c r="I2" t="n">
         <v>0.007845830755464675</v>
@@ -542,10 +542,10 @@
         <v>0.01016600694487216</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009563170620994054</v>
+        <v>0.009563170620994058</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008724793519334228</v>
+        <v>0.008724793519334232</v>
       </c>
     </row>
     <row r="3">
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009069548850156492</v>
+        <v>0.009069548850156494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01049020587719172</v>
+        <v>0.01049020587719171</v>
       </c>
       <c r="D3" t="n">
         <v>0.01100489537173959</v>
@@ -570,13 +570,13 @@
         <v>0.008698358134617491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009593946220075802</v>
+        <v>0.009593946220075804</v>
       </c>
       <c r="H3" t="n">
         <v>0.01207180006401295</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008132862109249975</v>
+        <v>0.008132862109249977</v>
       </c>
       <c r="J3" t="n">
         <v>0.01292212781572801</v>
@@ -601,16 +601,16 @@
         <v>0.02988354629654756</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03454956156347593</v>
+        <v>0.03454956156347594</v>
       </c>
       <c r="E4" t="n">
         <v>0.02992137708197926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02992137708197927</v>
+        <v>0.02992137708197926</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03230208747688307</v>
+        <v>0.03230208747688306</v>
       </c>
       <c r="H4" t="n">
         <v>0.03619294442081301</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08638231841200308</v>
+        <v>0.0863823184120031</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05892930352913367</v>
+        <v>0.05892930352913377</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1468556946813556</v>
+        <v>0.1468556946813555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05892930530591885</v>
+        <v>0.05892930530591882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05892930530591885</v>
+        <v>0.05892930530591882</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1055005665940826</v>
+        <v>0.1055005665940824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1967231284565548</v>
+        <v>0.1967231284565547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05892870165701809</v>
+        <v>0.05892870165701822</v>
       </c>
       <c r="J5" t="n">
         <v>0.1008487002917442</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06021280454500023</v>
+        <v>0.06021280454500028</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2831432356029807</v>
+        <v>0.2831432356029813</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03232949854183435</v>
+        <v>0.03232949854183436</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03073926446989161</v>
+        <v>0.03073926446989162</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03551068695426683</v>
+        <v>0.03551068695426685</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03064545234984619</v>
+        <v>0.03064545234984618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03081034970766008</v>
+        <v>0.03081034970766009</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03479554409454548</v>
+        <v>0.03479554409454549</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03878911818979422</v>
+        <v>0.03878911818979423</v>
       </c>
       <c r="I6" t="n">
         <v>0.03245968821215185</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03445472078059639</v>
+        <v>0.03445472078059638</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03083240349162271</v>
+        <v>0.03083240349162273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407480666394228</v>
+        <v>0.04074806663942279</v>
       </c>
     </row>
     <row r="7">
@@ -730,16 +730,16 @@
         <v>0.03104692312242966</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0333838675215093</v>
+        <v>0.03338386752150931</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03727472446543927</v>
+        <v>0.03727472446543926</v>
       </c>
       <c r="I7" t="n">
         <v>0.03104801163911565</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03304302116436607</v>
+        <v>0.03304302116436608</v>
       </c>
       <c r="K7" t="n">
         <v>0.03111799084620084</v>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03402526033955472</v>
+        <v>0.03402526033955473</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03453716175778699</v>
+        <v>0.034537161757787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03954172558590608</v>
+        <v>0.03954172558590609</v>
       </c>
       <c r="E8" t="n">
         <v>0.03398224423128379</v>
@@ -770,10 +770,10 @@
         <v>0.0325723107104127</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03687346323930362</v>
+        <v>0.03687346323930363</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04076432018323364</v>
+        <v>0.04076432018323365</v>
       </c>
       <c r="I8" t="n">
         <v>0.03453760735690999</v>
@@ -801,19 +801,19 @@
         <v>0.03693662499387577</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04151935352149156</v>
+        <v>0.04151935352149157</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03884200013766901</v>
+        <v>0.03884200013766902</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03693662457686041</v>
+        <v>0.03693662457686042</v>
       </c>
       <c r="G9" t="n">
         <v>0.03927187900415392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04316273594808386</v>
+        <v>0.04316273594808388</v>
       </c>
       <c r="I9" t="n">
         <v>0.03693602312176027</v>
@@ -822,7 +822,7 @@
         <v>0.03893103264701069</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03492692750040352</v>
+        <v>0.03492692750040351</v>
       </c>
       <c r="L9" t="n">
         <v>0.04680491791324739</v>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007152263675101958</v>
+        <v>0.007152263675101961</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008286329726259733</v>
+        <v>0.008286329726259738</v>
       </c>
       <c r="D2" t="n">
         <v>0.007183754656800509</v>
@@ -929,19 +929,19 @@
         <v>0.0072110241049365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007178804490114186</v>
+        <v>0.007178804490114187</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007196669869971867</v>
+        <v>0.007196669869971868</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008668601379089841</v>
+        <v>0.008668601379089843</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008830373527198893</v>
+        <v>0.0088303735271989</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007153313094347738</v>
+        <v>0.007153313094347704</v>
       </c>
     </row>
     <row r="3">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006831674759062863</v>
+        <v>0.006831674759062865</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008947746622924822</v>
+        <v>0.008947746622924826</v>
       </c>
       <c r="D3" t="n">
         <v>0.007054987480625639</v>
@@ -963,25 +963,25 @@
         <v>0.00933378785499725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007643853088696435</v>
+        <v>0.007643853088696429</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007249464953963114</v>
+        <v>0.007249464953963112</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007037337757197448</v>
+        <v>0.007037337757197452</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00714680026301105</v>
+        <v>0.007146800263011052</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009789417714153825</v>
+        <v>0.009789417714153821</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009726631593883574</v>
+        <v>0.009726631593883589</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006851196757054698</v>
+        <v>0.006851196757054683</v>
       </c>
     </row>
     <row r="4">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02813976088129934</v>
+        <v>0.02813976088129933</v>
       </c>
       <c r="C4" t="n">
         <v>0.02854503434464875</v>
@@ -1000,22 +1000,22 @@
         <v>0.02849546600615177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02857228864298581</v>
+        <v>0.0285722886429858</v>
       </c>
       <c r="F4" t="n">
         <v>0.0285722886429858</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02880009658585981</v>
+        <v>0.0288000965858598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02846709049744364</v>
+        <v>0.02846709049744363</v>
       </c>
       <c r="I4" t="n">
         <v>0.02861946583195261</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02907484048525808</v>
+        <v>0.02907484048525807</v>
       </c>
       <c r="K4" t="n">
         <v>0.02840012653016375</v>
@@ -1034,34 +1034,34 @@
         <v>0.03260674022926598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04052165078387835</v>
+        <v>0.04052165078387836</v>
       </c>
       <c r="D5" t="n">
         <v>0.03815173671129372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04052165308694818</v>
+        <v>0.04052165308694817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04052165308694818</v>
+        <v>0.04052165308694817</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04352057691933574</v>
+        <v>0.04352057691933577</v>
       </c>
       <c r="H5" t="n">
         <v>0.03905810619727074</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04052154175887698</v>
+        <v>0.04052154175887701</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04943973354514208</v>
+        <v>0.04943973354514197</v>
       </c>
       <c r="K5" t="n">
         <v>0.03641677245722343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03402685022714158</v>
+        <v>0.03402685022714156</v>
       </c>
     </row>
     <row r="6">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02877570871698525</v>
+        <v>0.02877570871698524</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02923640470635017</v>
+        <v>0.02923640470635018</v>
       </c>
       <c r="D6" t="n">
         <v>0.03020522870905466</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02915871219369777</v>
+        <v>0.02915871219369779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02925477041919334</v>
+        <v>0.02925477041919333</v>
       </c>
       <c r="G6" t="n">
         <v>0.03050019637516046</v>
@@ -1095,13 +1095,13 @@
         <v>0.02925541366763852</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02977827278434075</v>
+        <v>0.02977827278434074</v>
       </c>
       <c r="K6" t="n">
         <v>0.02903206329108561</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02880642730771843</v>
+        <v>0.02880642730771842</v>
       </c>
     </row>
     <row r="7">
@@ -1129,7 +1129,7 @@
         <v>0.02947465016944626</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02914164408103011</v>
+        <v>0.0291416440810301</v>
       </c>
       <c r="I7" t="n">
         <v>0.02929401941553908</v>
@@ -1141,7 +1141,7 @@
         <v>0.02907468011375022</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02884521102510345</v>
+        <v>0.02884521102510344</v>
       </c>
     </row>
     <row r="8">
@@ -1157,31 +1157,31 @@
         <v>0.03171680516961933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0318817351011934</v>
+        <v>0.03188173510119341</v>
       </c>
       <c r="E8" t="n">
         <v>0.03133706103814483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03037222037521946</v>
+        <v>0.03037222037521945</v>
       </c>
       <c r="G8" t="n">
         <v>0.03189838535285097</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03156537926443476</v>
+        <v>0.03156537926443477</v>
       </c>
       <c r="I8" t="n">
         <v>0.03171775459894378</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0321734021945065</v>
+        <v>0.03217340219450649</v>
       </c>
       <c r="K8" t="n">
         <v>0.03008379993597954</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03271968207776121</v>
+        <v>0.03271968207776122</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03041807662944831</v>
+        <v>0.0304180766294483</v>
       </c>
       <c r="C9" t="n">
         <v>0.03165969442508541</v>
@@ -1203,10 +1203,10 @@
         <v>0.03253880260213979</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03165969657794195</v>
+        <v>0.03165969657794196</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03184021615399123</v>
+        <v>0.03184021615399124</v>
       </c>
       <c r="H9" t="n">
         <v>0.03150721006557507</v>
@@ -1215,7 +1215,7 @@
         <v>0.03165958540008405</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03211496005338951</v>
+        <v>0.03211496005338953</v>
       </c>
       <c r="K9" t="n">
         <v>0.03099885425527668</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007675113038642964</v>
+        <v>0.007675113038642967</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00731624571055085</v>
+        <v>0.007316245710550854</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007781677032261457</v>
+        <v>0.007781677032261461</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007282735650925775</v>
+        <v>0.007282735650925779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007282690654328672</v>
+        <v>0.007282690654328677</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007761111520437633</v>
+        <v>0.007761111520437632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007937010215365038</v>
+        <v>0.007937010215365041</v>
       </c>
       <c r="I2" t="n">
         <v>0.007694249765852828</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008684075812714737</v>
+        <v>0.008684075812714747</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008522415536322514</v>
+        <v>0.008522415536322518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007830995164726243</v>
+        <v>0.007830995164726247</v>
       </c>
     </row>
     <row r="3">
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007982336608527749</v>
+        <v>0.007982336608527756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007561208588044775</v>
+        <v>0.007561208588044777</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008741452137321066</v>
+        <v>0.008741452137321071</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007440023351873581</v>
+        <v>0.007440023351873586</v>
       </c>
       <c r="F3" t="n">
         <v>0.007439978355276488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008596508578074301</v>
+        <v>0.008596508578074305</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009865603585303178</v>
+        <v>0.009865603585303185</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008119074895289987</v>
+        <v>0.008119074895289988</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01082776002297185</v>
+        <v>0.01082776002297186</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009452346603220845</v>
+        <v>0.009452346603220843</v>
       </c>
       <c r="L3" t="n">
         <v>0.009105223610457652</v>
@@ -1390,7 +1390,7 @@
         <v>0.0285863812641106</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02877384853049349</v>
+        <v>0.0287738485304935</v>
       </c>
       <c r="D4" t="n">
         <v>0.02979007059389049</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0396529250706708</v>
+        <v>0.03965292507067079</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04639409142299505</v>
+        <v>0.04639409142299512</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06127608896579487</v>
+        <v>0.06127608896579486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04373650116611316</v>
+        <v>0.04373650116611319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04373650116611316</v>
+        <v>0.0437365011661132</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05795026581001521</v>
+        <v>0.05795026581001524</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1009845105608364</v>
+        <v>0.1009845105608366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04373625288511945</v>
+        <v>0.04373625288511955</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08591830313449644</v>
+        <v>0.08591830313449637</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0424271529743134</v>
+        <v>0.04242715297431342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07771963769528051</v>
+        <v>0.07771963769528055</v>
       </c>
     </row>
     <row r="6">
@@ -1467,22 +1467,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03045349766779551</v>
+        <v>0.03045349766779552</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02954088770041186</v>
+        <v>0.02954088770041187</v>
       </c>
       <c r="D6" t="n">
         <v>0.03046204369150957</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0293147785546116</v>
+        <v>0.02931477855461161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02942698239460177</v>
+        <v>0.02942698239460178</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03020757759976016</v>
+        <v>0.03020757759976017</v>
       </c>
       <c r="H6" t="n">
         <v>0.03352605851206423</v>
@@ -1494,10 +1494,10 @@
         <v>0.0328903100176815</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02935778233264718</v>
+        <v>0.02935778233264717</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03100927854809865</v>
+        <v>0.03100927854809866</v>
       </c>
     </row>
     <row r="7">
@@ -1522,13 +1522,13 @@
         <v>0.02959175542122517</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03037002153976882</v>
+        <v>0.03037002153976884</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03236635711123517</v>
+        <v>0.03236635711123518</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02959138046935223</v>
+        <v>0.02959138046935224</v>
       </c>
       <c r="J7" t="n">
         <v>0.03182798755849964</v>
@@ -1550,7 +1550,7 @@
         <v>0.03058971957359032</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0325537302633564</v>
+        <v>0.03255373026335642</v>
       </c>
       <c r="D8" t="n">
         <v>0.03375030374536589</v>
@@ -1559,25 +1559,25 @@
         <v>0.03195648130356072</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03082997864133213</v>
+        <v>0.03082997864133214</v>
       </c>
       <c r="G8" t="n">
         <v>0.03317766040856677</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03517399598003565</v>
+        <v>0.03517399598003567</v>
       </c>
       <c r="I8" t="n">
         <v>0.03239901933815016</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03463594496250887</v>
+        <v>0.03463594496250889</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03070642086771106</v>
+        <v>0.03070642086771105</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03566570875626014</v>
+        <v>0.03566570875626013</v>
       </c>
     </row>
     <row r="9">
@@ -1590,34 +1590,34 @@
         <v>0.03163827412049094</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03297634258811675</v>
+        <v>0.03297634258811676</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03383740961001126</v>
+        <v>0.03383740961001128</v>
       </c>
       <c r="E9" t="n">
         <v>0.03397118104543508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03282245760332739</v>
+        <v>0.0328224576033274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03360085125299341</v>
+        <v>0.03360085125299343</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03559718682445975</v>
+        <v>0.03559718682445977</v>
       </c>
       <c r="I9" t="n">
         <v>0.03282221018257683</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0350588172717242</v>
+        <v>0.03505881727172422</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03220376352752549</v>
+        <v>0.0322037635275255</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03439582860575618</v>
+        <v>0.03439582860575619</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00751135522265732</v>
+        <v>0.007511355222657327</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007200653997838573</v>
+        <v>0.007200653997838577</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007599914930645613</v>
+        <v>0.007599914930645619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007176891686289037</v>
+        <v>0.007176891686289049</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007176848641705886</v>
+        <v>0.007176848641705892</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007572499368340393</v>
+        <v>0.007572499368340401</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007649019466956145</v>
+        <v>0.007649019466956143</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00753041136074709</v>
+        <v>0.007530411360747089</v>
       </c>
       <c r="J2" t="n">
         <v>0.008558152847166675</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008406547758477155</v>
+        <v>0.008406547758477144</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007553224986857556</v>
+        <v>0.007553224986857555</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007628621262566122</v>
+        <v>0.007628621262566123</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007300248078032076</v>
+        <v>0.007300248078032075</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008259816693797701</v>
+        <v>0.008259816693797708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007181669472769392</v>
+        <v>0.007181669472769396</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007181626428186236</v>
+        <v>0.007181626428186248</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008065525039652556</v>
+        <v>0.008065525039652559</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008625475673503271</v>
+        <v>0.008625475673503269</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007764990518918991</v>
+        <v>0.00776499051891899</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01019963257738518</v>
+        <v>0.01019963257738519</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009135840691794421</v>
+        <v>0.009135840691794411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007938739542803185</v>
+        <v>0.007938739542803181</v>
       </c>
     </row>
     <row r="4">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02818063076005059</v>
+        <v>0.0281806307600506</v>
       </c>
       <c r="C4" t="n">
         <v>0.028417454816498</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02918095340125682</v>
+        <v>0.0291809534012568</v>
       </c>
       <c r="E4" t="n">
         <v>0.02843581138364655</v>
@@ -1804,16 +1804,16 @@
         <v>0.02975034619746371</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02837095602302417</v>
+        <v>0.02837095602302418</v>
       </c>
       <c r="J4" t="n">
         <v>0.02991308809977091</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02824053379327399</v>
+        <v>0.028240533793274</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02866718684635829</v>
+        <v>0.02866718684635827</v>
       </c>
     </row>
     <row r="5">
@@ -1826,34 +1826,34 @@
         <v>0.03337623346538104</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04028956299439963</v>
+        <v>0.04028956299439965</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05062311397078262</v>
+        <v>0.05062311397078267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03734747647584373</v>
+        <v>0.03734747647584375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03734747647584374</v>
+        <v>0.03734747647584375</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04585455900639616</v>
+        <v>0.04585455900639615</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06442079739902544</v>
+        <v>0.0644207973990254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03734729425409687</v>
+        <v>0.03734729425409686</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06484719747957476</v>
+        <v>0.06484719747957478</v>
       </c>
       <c r="K5" t="n">
         <v>0.03466607059753934</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04399914708494396</v>
+        <v>0.04399914708494398</v>
       </c>
     </row>
     <row r="6">
@@ -1866,13 +1866,13 @@
         <v>0.02993600289017142</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02916086132012333</v>
+        <v>0.02916086132012336</v>
       </c>
       <c r="D6" t="n">
         <v>0.03094725701810165</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02892346681129761</v>
+        <v>0.02892346681129762</v>
       </c>
       <c r="F6" t="n">
         <v>0.02901992429753252</v>
@@ -1881,16 +1881,16 @@
         <v>0.03062280700964121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03161240209297161</v>
+        <v>0.0316124020929716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02901310560656045</v>
+        <v>0.02901310560656044</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03063042149704107</v>
+        <v>0.03063042149704108</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02886837531663766</v>
+        <v>0.02886837531663765</v>
       </c>
       <c r="L6" t="n">
         <v>0.02930489526469586</v>
@@ -1921,16 +1921,16 @@
         <v>0.02960022984655563</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03048314116449895</v>
+        <v>0.03048314116449894</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02910375099005942</v>
+        <v>0.02910375099005943</v>
       </c>
       <c r="J7" t="n">
         <v>0.03064588306680616</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02897332876030925</v>
+        <v>0.02897332876030924</v>
       </c>
       <c r="L7" t="n">
         <v>0.02939998181339354</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03001426767584258</v>
+        <v>0.03001426767584261</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03188401527180415</v>
+        <v>0.03188401527180414</v>
       </c>
       <c r="D8" t="n">
         <v>0.03281625443550604</v>
@@ -1958,22 +1958,22 @@
         <v>0.030255771082503</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03219331049780412</v>
+        <v>0.03219331049780414</v>
       </c>
       <c r="H8" t="n">
         <v>0.03307622181575429</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0316968316413079</v>
+        <v>0.03169683164130789</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03323925698525788</v>
+        <v>0.03323925698525786</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03004645160908507</v>
+        <v>0.03004645160908508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0335518305679544</v>
+        <v>0.03355183056795441</v>
       </c>
     </row>
     <row r="9">
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03065803462021749</v>
+        <v>0.03065803462021748</v>
       </c>
       <c r="C9" t="n">
         <v>0.03185684362661851</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03248589648163798</v>
+        <v>0.03248589648163797</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03263104284815096</v>
+        <v>0.03263104284815095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03167608037278195</v>
+        <v>0.03167608037278194</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03217237741961402</v>
+        <v>0.03217237741961401</v>
       </c>
       <c r="H9" t="n">
         <v>0.03305528873755732</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03167589856311781</v>
+        <v>0.0316758985631178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03321803063986453</v>
+        <v>0.03321803063986454</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03106599739946576</v>
+        <v>0.03106599739946575</v>
       </c>
       <c r="L9" t="n">
         <v>0.03197212938645193</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007236661457165865</v>
+        <v>0.007236661457165895</v>
       </c>
       <c r="C2" t="n">
         <v>0.007069428239555892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007298678853715859</v>
+        <v>0.007298678853715889</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007018418735490317</v>
+        <v>0.007018418735490357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00701837938998699</v>
+        <v>0.007018379389987013</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007275621317358381</v>
+        <v>0.007275621317358411</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007303909516598058</v>
+        <v>0.007303909516598061</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007241361271955951</v>
+        <v>0.007241361271955972</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007905224701450986</v>
+        <v>0.007905224701450995</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008262392491057962</v>
+        <v>0.008262392491057976</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007248859007820491</v>
+        <v>0.007248859007820494</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007214922066159771</v>
+        <v>0.007214922066159782</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007120343315695335</v>
+        <v>0.007120343315695336</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007657270765516331</v>
+        <v>0.007657270765516352</v>
       </c>
       <c r="E3" t="n">
         <v>0.00688135094993571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006881311604432358</v>
+        <v>0.006881311604432372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007493603765316431</v>
+        <v>0.007493603765316438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007708477529021039</v>
+        <v>0.007708477529021043</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007249121239252301</v>
+        <v>0.007249121239252305</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008718117088958829</v>
+        <v>0.008718117088958871</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008928752849470537</v>
+        <v>0.008928752849470572</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007311194281071668</v>
+        <v>0.007311194281071672</v>
       </c>
     </row>
     <row r="4">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02793110986729629</v>
+        <v>0.0279311098672963</v>
       </c>
       <c r="C4" t="n">
         <v>0.02816796619460539</v>
@@ -2203,13 +2203,13 @@
         <v>0.02796114554963898</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02875139501022644</v>
+        <v>0.02875139501022645</v>
       </c>
       <c r="K4" t="n">
         <v>0.02797237602020751</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02808221467573077</v>
+        <v>0.02808221467573078</v>
       </c>
     </row>
     <row r="5">
@@ -2222,34 +2222,34 @@
         <v>0.02996318125757595</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03679348116394879</v>
+        <v>0.03679348116394881</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04221170247033334</v>
+        <v>0.0422117024703333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03121935596099223</v>
+        <v>0.03121935596099224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03121935596099223</v>
+        <v>0.03121935596099224</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03806594499810916</v>
+        <v>0.03806594499810917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0455450550710382</v>
+        <v>0.04554505507103826</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03121919625358346</v>
+        <v>0.03121919625358347</v>
       </c>
       <c r="J5" t="n">
         <v>0.04508524257117087</v>
       </c>
       <c r="K5" t="n">
-        <v>0.031019714310229</v>
+        <v>0.03101971431022902</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0336599347031071</v>
+        <v>0.03365993470310712</v>
       </c>
     </row>
     <row r="6">
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02857050195197186</v>
+        <v>0.02857050195197187</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02891017215658554</v>
+        <v>0.02891017215658553</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02927717671694345</v>
+        <v>0.02927717671694338</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02850834290988113</v>
+        <v>0.02850834290988114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02860571976483928</v>
+        <v>0.02860571976483929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.030094679703444</v>
+        <v>0.03009467970344401</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03053499608882596</v>
+        <v>0.03053499608882597</v>
       </c>
       <c r="I6" t="n">
         <v>0.02968821376842611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03048764006187986</v>
+        <v>0.03048764006187988</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02860789829934189</v>
+        <v>0.02860789829934181</v>
       </c>
       <c r="L6" t="n">
         <v>0.02871341140721868</v>
@@ -2308,25 +2308,25 @@
         <v>0.02932749020546228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02866507123905975</v>
+        <v>0.02866507123905977</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02866507123905975</v>
+        <v>0.02866507123905977</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02906358186893423</v>
+        <v>0.02906358186893424</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02940525546028006</v>
+        <v>0.02940525546028007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02865711593391632</v>
+        <v>0.02865711593391633</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02944736539450379</v>
+        <v>0.0294473653945038</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02866834640448485</v>
+        <v>0.02866834640448486</v>
       </c>
       <c r="L7" t="n">
         <v>0.02877818506000813</v>
@@ -2342,34 +2342,34 @@
         <v>0.02970559108225652</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03153301731328134</v>
+        <v>0.03153301731328136</v>
       </c>
       <c r="D8" t="n">
         <v>0.03216101275395302</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03079878469932075</v>
+        <v>0.03079878469932077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02978657367592805</v>
+        <v>0.02978657367592806</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0315956042576109</v>
+        <v>0.03159560425761093</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0319372778489629</v>
+        <v>0.03193727784896291</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03118913832259301</v>
+        <v>0.03118913832259302</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03197967343920146</v>
+        <v>0.03197967343920147</v>
       </c>
       <c r="K8" t="n">
         <v>0.02971985751179634</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03282852181107722</v>
+        <v>0.03282852181107723</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03007244297876285</v>
+        <v>0.03007244297876286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03117259241231635</v>
+        <v>0.03117259241231638</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03150705883268719</v>
+        <v>0.03150705883268722</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03168387500157692</v>
+        <v>0.03168387500157693</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03083673840672254</v>
+        <v>0.03083673840672255</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03124304487239515</v>
+        <v>0.03124304487239516</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03158471846374099</v>
+        <v>0.03158471846374101</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03083657893737725</v>
+        <v>0.03083657893737727</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03162682839796471</v>
+        <v>0.03162682839796472</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03040521244016756</v>
+        <v>0.03040521244016757</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03095764806346904</v>
+        <v>0.03095764806346906</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007481017676850396</v>
+        <v>0.007481017676850391</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007108401974699086</v>
+        <v>0.00710840197469909</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007551464351878433</v>
+        <v>0.007551464351878426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007136540391258354</v>
+        <v>0.007136540391258364</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00713649447315831</v>
+        <v>0.007136494473158319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00755457264429176</v>
+        <v>0.007554572644291755</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007712071018342349</v>
+        <v>0.007712071018342358</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007505430214054826</v>
+        <v>0.007505430214054838</v>
       </c>
       <c r="J2" t="n">
         <v>0.008554930462063818</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008395162487898478</v>
+        <v>0.008395162487898483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007663246356107645</v>
+        <v>0.007663246356107656</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007539405911698661</v>
+        <v>0.007539405911698659</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006894691932553958</v>
+        <v>0.006894691932553959</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008041734110871609</v>
+        <v>0.008041734110871607</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007105336302933103</v>
+        <v>0.007105336302933096</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007105290384833063</v>
+        <v>0.007105290384833059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008064843650344433</v>
+        <v>0.008064843650344431</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009199655849097831</v>
+        <v>0.009199655849097843</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007714035861928354</v>
+        <v>0.007714035861928358</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01061751397585424</v>
+        <v>0.01061751397585423</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0092117174312999</v>
+        <v>0.009211717431299914</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008844999966073783</v>
+        <v>0.008844999966073791</v>
       </c>
     </row>
     <row r="4">
@@ -2581,31 +2581,31 @@
         <v>0.02780689316790278</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02883111166202395</v>
+        <v>0.02883111166202394</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02828295103119974</v>
+        <v>0.02828295103119975</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02828295103119974</v>
+        <v>0.02828295103119975</v>
       </c>
       <c r="G4" t="n">
         <v>0.028862138432127</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03064956832397351</v>
+        <v>0.0306495683239735</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02828461848997678</v>
+        <v>0.02828461848997679</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03071925753603251</v>
+        <v>0.0307192575360325</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02837121340848192</v>
+        <v>0.02837121340848191</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03008661369003798</v>
+        <v>0.03008661369003797</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03126179487687555</v>
+        <v>0.03126179487687556</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03043756837715896</v>
+        <v>0.03043756837715898</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04582808055767786</v>
+        <v>0.04582808055767785</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03658611305725868</v>
+        <v>0.03658611305725878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03658611305725868</v>
+        <v>0.03658611305725878</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04698400749769178</v>
+        <v>0.04698400749769182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0847770955788883</v>
+        <v>0.08477709557888828</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03658591194607803</v>
+        <v>0.03658591194607814</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08222533729383563</v>
+        <v>0.08222533729383566</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03764041679051978</v>
+        <v>0.03764041679051976</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07431465595279838</v>
+        <v>0.07431465595279842</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02864650062517603</v>
+        <v>0.02864650062517604</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02852259761182947</v>
+        <v>0.02852259761182934</v>
       </c>
       <c r="D6" t="n">
         <v>0.02944801601819532</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02879444986848481</v>
+        <v>0.02879444986848484</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02889681180895216</v>
+        <v>0.02889681180895217</v>
       </c>
       <c r="G6" t="n">
         <v>0.02947325499679235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03251083703557149</v>
+        <v>0.0325108370355715</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03004841395561803</v>
+        <v>0.03004841395561804</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03140609327114993</v>
+        <v>0.03140609327114994</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02896025264675766</v>
+        <v>0.02896025264675767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03070596939677014</v>
+        <v>0.03070596939677015</v>
       </c>
     </row>
     <row r="7">
@@ -2701,7 +2701,7 @@
         <v>0.02873423623342052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0296006029152138</v>
+        <v>0.02960060291521379</v>
       </c>
       <c r="E7" t="n">
         <v>0.02906482745728954</v>
@@ -2710,22 +2710,22 @@
         <v>0.02906482745728954</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029631742680365</v>
+        <v>0.02963174268036501</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0314191725722115</v>
+        <v>0.03141917257221152</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02905422273821477</v>
+        <v>0.02905422273821479</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03148886178427051</v>
+        <v>0.03148886178427052</v>
       </c>
       <c r="K7" t="n">
         <v>0.02914081765671991</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03085621793827597</v>
+        <v>0.03085621793827598</v>
       </c>
     </row>
     <row r="8">
@@ -2747,25 +2747,25 @@
         <v>0.03133924367723638</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03025646825598692</v>
+        <v>0.03025646825598693</v>
       </c>
       <c r="G8" t="n">
         <v>0.03233232478036894</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03411975467221626</v>
+        <v>0.03411975467221625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03175480483821871</v>
+        <v>0.03175480483821872</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03418974930389776</v>
+        <v>0.03418974930389777</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03025845897702594</v>
+        <v>0.03025845897702596</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03518015931383325</v>
+        <v>0.03518015931383327</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03081148106486917</v>
+        <v>0.03081148106486918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03165497731833</v>
+        <v>0.03165497731833002</v>
       </c>
       <c r="D9" t="n">
         <v>0.03252145736689747</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03303018764014477</v>
+        <v>0.03303018764014478</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03197516428116945</v>
+        <v>0.03197516428116947</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03255248376527448</v>
+        <v>0.03255248376527449</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03433991365712099</v>
+        <v>0.034339913657121</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03197496382312426</v>
+        <v>0.03197496382312427</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03440960286917999</v>
+        <v>0.03440960286918001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03153183982574537</v>
+        <v>0.03153183982574539</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03377695902318546</v>
+        <v>0.03377695902318548</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007250233732208979</v>
+        <v>0.007250233732208984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006983315168614485</v>
+        <v>0.00698331516861448</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007255327646322868</v>
+        <v>0.007255327646322858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007001380696848178</v>
+        <v>0.007001380696848185</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007001336218100075</v>
+        <v>0.00700133621810008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007261319882195671</v>
+        <v>0.007261319882195668</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007262711769106465</v>
+        <v>0.007262711769106463</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00726881497505022</v>
+        <v>0.007268814975050227</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008270245453367206</v>
+        <v>0.008270245453367197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008222595871409662</v>
+        <v>0.008222595871409676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007272755193762586</v>
+        <v>0.00727275519376259</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007227022642073088</v>
+        <v>0.007227022642073077</v>
       </c>
       <c r="C3" t="n">
         <v>0.006786294384599383</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007263973161388062</v>
+        <v>0.00726397316138806</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006918914544709782</v>
+        <v>0.006918914544709777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006918870065961661</v>
+        <v>0.006918870065961651</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007306877591136474</v>
+        <v>0.007306877591136469</v>
       </c>
       <c r="H3" t="n">
         <v>0.007328559852726567</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007360138841851212</v>
+        <v>0.007360138841851202</v>
       </c>
       <c r="J3" t="n">
         <v>0.009338674023643483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008848520657871468</v>
+        <v>0.008848520657871471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007393020701381395</v>
+        <v>0.007393020701381392</v>
       </c>
     </row>
     <row r="4">
@@ -2989,13 +2989,13 @@
         <v>0.02795840376848448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02799748362681098</v>
+        <v>0.02799748362681097</v>
       </c>
       <c r="I4" t="n">
         <v>0.02802420001397345</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02871527641632723</v>
+        <v>0.02871527641632722</v>
       </c>
       <c r="K4" t="n">
         <v>0.02786913725332786</v>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02941259440213805</v>
+        <v>0.02941259440213806</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0297165421061093</v>
+        <v>0.02971654210610929</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03073859456413064</v>
+        <v>0.03073859456413063</v>
       </c>
       <c r="E5" t="n">
         <v>0.03336206758032323</v>
@@ -3026,19 +3026,19 @@
         <v>0.03336206758032323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03200354021084442</v>
+        <v>0.03200354021084449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0331214060854652</v>
+        <v>0.03312140608546521</v>
       </c>
       <c r="I5" t="n">
         <v>0.03336201580753671</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04555746802302987</v>
+        <v>0.04555746802302986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03032413083723602</v>
+        <v>0.03032413083723601</v>
       </c>
       <c r="L5" t="n">
         <v>0.03516463584939981</v>
@@ -3051,16 +3051,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02842740676235757</v>
+        <v>0.02842740676235756</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02838959273385976</v>
+        <v>0.02838959273385975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02951945770774985</v>
+        <v>0.02951945770774986</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02854646920878157</v>
+        <v>0.02854646920878159</v>
       </c>
       <c r="F6" t="n">
         <v>0.02862451469370635</v>
@@ -3078,10 +3078,10 @@
         <v>0.03033908106051166</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02845430008863916</v>
+        <v>0.0284543000886391</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02868196863013469</v>
+        <v>0.02868196863013468</v>
       </c>
     </row>
     <row r="7">
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02849566768643242</v>
+        <v>0.02849566768643241</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02848820453471084</v>
+        <v>0.02848820453471083</v>
       </c>
       <c r="D7" t="n">
         <v>0.02855309865780013</v>
@@ -3106,7 +3106,7 @@
         <v>0.02869651218471449</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02861743602106195</v>
+        <v>0.02861743602106194</v>
       </c>
       <c r="H7" t="n">
         <v>0.02865651587938843</v>
@@ -3115,10 +3115,10 @@
         <v>0.0286832322665509</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02937430866890468</v>
+        <v>0.02937430866890467</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02852816950590532</v>
+        <v>0.02852816950590531</v>
       </c>
       <c r="L7" t="n">
         <v>0.02875564312487097</v>
@@ -3134,10 +3134,10 @@
         <v>0.02953264071987209</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03092072047177976</v>
+        <v>0.03092072047177977</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03125934691296339</v>
+        <v>0.03125934691296338</v>
       </c>
       <c r="E8" t="n">
         <v>0.03073629626280497</v>
@@ -3149,19 +3149,19 @@
         <v>0.03103690715674118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03107598701507034</v>
+        <v>0.03107598701507035</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03110270340223016</v>
+        <v>0.03110270340223015</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03179405150478899</v>
+        <v>0.03179405150478897</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02953946192734107</v>
+        <v>0.02953946192734108</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03261924913070173</v>
+        <v>0.03261924913070172</v>
       </c>
     </row>
     <row r="9">
@@ -3186,19 +3186,19 @@
         <v>0.03093120679806867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03086535881634317</v>
+        <v>0.03086535881634316</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03090443867466966</v>
+        <v>0.03090443867466965</v>
       </c>
       <c r="I9" t="n">
         <v>0.03093115506183212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0316222314641859</v>
+        <v>0.03162223146418591</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03035097363686095</v>
+        <v>0.03035097363686094</v>
       </c>
       <c r="L9" t="n">
         <v>0.03100356592015219</v>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006978816891301013</v>
+        <v>0.006978816891301009</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0068960090122638</v>
+        <v>0.006896009012263797</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006983234516052088</v>
+        <v>0.006983234516052086</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006885444512047889</v>
+        <v>0.006885444512047895</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006885403696086255</v>
+        <v>0.006885403696086257</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006982719352559409</v>
+        <v>0.006982719352559408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006981936582705012</v>
+        <v>0.006981936582705013</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006988275433153258</v>
+        <v>0.006988275433153255</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007660919618905605</v>
+        <v>0.007660919618905603</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008105668868261709</v>
+        <v>0.008105668868261707</v>
       </c>
       <c r="L2" t="n">
         <v>0.006980547983759076</v>
@@ -3327,34 +3327,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006879413614084725</v>
+        <v>0.006879413614084721</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006746298578985473</v>
+        <v>0.006746298578985471</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006911566430839352</v>
+        <v>0.006911566430839345</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006778034733838931</v>
+        <v>0.006778034733838923</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006777993917877297</v>
+        <v>0.006777993917877304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006908033336369976</v>
+        <v>0.00690803333636998</v>
       </c>
       <c r="H3" t="n">
         <v>0.006913605856926578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006947538433764605</v>
+        <v>0.006947538433764602</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008087653104884627</v>
+        <v>0.008087653104884624</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008739088629680401</v>
+        <v>0.008739088629680413</v>
       </c>
       <c r="L3" t="n">
         <v>0.006897146536805697</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02778570759088548</v>
+        <v>0.02778570759088547</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02767890420597318</v>
+        <v>0.02767890420597317</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02783560669465666</v>
+        <v>0.02783560669465665</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02794149887305907</v>
+        <v>0.02794149887305906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02794149887305907</v>
+        <v>0.02794149887305906</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02782652701217046</v>
+        <v>0.02782652701217027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02784046969648134</v>
+        <v>0.02784046969648135</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02787153703193232</v>
+        <v>0.02787153703193234</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02795323715309543</v>
+        <v>0.02795323715309542</v>
       </c>
       <c r="K4" t="n">
         <v>0.02778342529795141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02781268159829586</v>
+        <v>0.02781268159829587</v>
       </c>
     </row>
     <row r="5">
@@ -3407,31 +3407,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02909194744794721</v>
+        <v>0.02909194744794718</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02953649738362106</v>
+        <v>0.02953649738362105</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03029787213484759</v>
+        <v>0.03029787213484758</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03128125372640965</v>
+        <v>0.0312812537264096</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03128125372640965</v>
+        <v>0.0312812537264096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03026613725175685</v>
+        <v>0.03026613725175677</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03074414854750102</v>
+        <v>0.03074414854750101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03128119864752225</v>
+        <v>0.0312811986475222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03253825850889601</v>
+        <v>0.03253825850889602</v>
       </c>
       <c r="K5" t="n">
         <v>0.02941852441084917</v>
@@ -3447,31 +3447,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02940536659779654</v>
+        <v>0.02940536659779655</v>
       </c>
       <c r="C6" t="n">
         <v>0.02835811572744265</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02842442321965216</v>
+        <v>0.02842442321965217</v>
       </c>
       <c r="E6" t="n">
         <v>0.02839447907556469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02847557880364359</v>
+        <v>0.02847557880364358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02944618601908133</v>
+        <v>0.02944618601908135</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02843147884226542</v>
+        <v>0.02843147884226541</v>
       </c>
       <c r="I6" t="n">
         <v>0.02949119603884343</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02861141079111235</v>
+        <v>0.02861141079111234</v>
       </c>
       <c r="K6" t="n">
         <v>0.02838068523991557</v>
@@ -3487,28 +3487,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0284169826230215</v>
+        <v>0.02841698262302149</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02841749821618891</v>
+        <v>0.0284174982161889</v>
       </c>
       <c r="D7" t="n">
         <v>0.02846677365649481</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02851363726255291</v>
+        <v>0.0285136372625529</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02851363726255291</v>
+        <v>0.0285136372625529</v>
       </c>
       <c r="G7" t="n">
         <v>0.0284578020443063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02847174472861738</v>
+        <v>0.02847174472861739</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02850281206406838</v>
+        <v>0.02850281206406837</v>
       </c>
       <c r="J7" t="n">
         <v>0.02858451218523145</v>
@@ -3517,7 +3517,7 @@
         <v>0.02841470033008744</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02844395663043189</v>
+        <v>0.0284439566304319</v>
       </c>
     </row>
     <row r="8">
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02943855253229956</v>
+        <v>0.02943855253229958</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03079823383015342</v>
+        <v>0.03079823383015341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03111653861174864</v>
+        <v>0.03111653861174866</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03051365004358099</v>
+        <v>0.03051365004358098</v>
       </c>
       <c r="F8" t="n">
         <v>0.0295736709145976</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03082784438594723</v>
+        <v>0.03082784438594724</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03084178707026127</v>
+        <v>0.03084178707026126</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03087285440570932</v>
+        <v>0.03087285440570931</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03095481954007535</v>
+        <v>0.03095481954007536</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02941122167164599</v>
+        <v>0.029411221671646</v>
       </c>
       <c r="L8" t="n">
         <v>0.03222259118487455</v>
@@ -3573,7 +3573,7 @@
         <v>0.03043227380150033</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03048165781026701</v>
+        <v>0.03048165781026704</v>
       </c>
       <c r="E9" t="n">
         <v>0.03129651402547423</v>
@@ -3582,7 +3582,7 @@
         <v>0.03051764269335681</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03047257762961772</v>
+        <v>0.03047257762961773</v>
       </c>
       <c r="H9" t="n">
         <v>0.03048652031392882</v>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007345708980999326</v>
+        <v>0.007345708980999408</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007039541771541195</v>
+        <v>0.007039541771541279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007357054477805587</v>
+        <v>0.007357054477805549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007058401278115844</v>
+        <v>0.007058401278115968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007058354771276688</v>
+        <v>0.007058354771276785</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007374404549752502</v>
+        <v>0.00737440454975248</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007537251564272797</v>
+        <v>0.00753725156427286</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007368335352141126</v>
+        <v>0.007368335352141106</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00824220961057958</v>
+        <v>0.008242209610579624</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008283403596429317</v>
+        <v>0.008283403596429376</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007492583323217169</v>
+        <v>0.007492583323217167</v>
       </c>
     </row>
     <row r="3">
@@ -3723,34 +3723,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007374448169222252</v>
+        <v>0.007374448169222257</v>
       </c>
       <c r="C3" t="n">
         <v>0.006844730957757286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0074558700315749</v>
+        <v>0.00745587003157488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007024971896432665</v>
+        <v>0.007024971896432647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007024925389593481</v>
+        <v>0.007024925389593466</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007579908149937679</v>
+        <v>0.007579908149937676</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008749359512027632</v>
+        <v>0.008749359512027634</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007536355150602523</v>
+        <v>0.007536355150602534</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009071808580643013</v>
+        <v>0.009071808580643007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008968779570738706</v>
+        <v>0.008968779570738711</v>
       </c>
       <c r="L3" t="n">
         <v>0.008424255695821966</v>
@@ -3781,7 +3781,7 @@
         <v>0.02827473050884924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03011864097281325</v>
+        <v>0.03011864097281323</v>
       </c>
       <c r="I4" t="n">
         <v>0.02818545084280188</v>
@@ -3809,31 +3809,31 @@
         <v>0.03006270347585164</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03330003229791199</v>
+        <v>0.03330003229791197</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03563307550114659</v>
+        <v>0.03563307550114658</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03563307550114659</v>
+        <v>0.03563307550114658</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03705958338835826</v>
+        <v>0.03705958338835849</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07505662813287375</v>
+        <v>0.0750566281328737</v>
       </c>
       <c r="I5" t="n">
         <v>0.03563298636642095</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03955442295212823</v>
+        <v>0.03955442295212827</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03272084920115693</v>
+        <v>0.03272084920115691</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06537504837566752</v>
+        <v>0.0653750483756675</v>
       </c>
     </row>
     <row r="6">
@@ -3852,7 +3852,7 @@
         <v>0.02865608878222565</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02867824619508445</v>
+        <v>0.02867824619508444</v>
       </c>
       <c r="F6" t="n">
         <v>0.02876709984451683</v>
@@ -3870,7 +3870,7 @@
         <v>0.02903967194479628</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02860894671979079</v>
+        <v>0.02860894671979087</v>
       </c>
       <c r="L6" t="n">
         <v>0.03018775775155723</v>
@@ -3901,19 +3901,19 @@
         <v>0.02900095493953782</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03084486540350182</v>
+        <v>0.03084486540350181</v>
       </c>
       <c r="I7" t="n">
         <v>0.02891167527349046</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02912623113406127</v>
+        <v>0.02912623113406126</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0287752418669362</v>
+        <v>0.02877524186693621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03032897298597544</v>
+        <v>0.03032897298597545</v>
       </c>
     </row>
     <row r="8">
@@ -3941,13 +3941,13 @@
         <v>0.03161688309847926</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03346079356244379</v>
+        <v>0.0334607935624438</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03152760343243192</v>
+        <v>0.03152760343243191</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03174245399267211</v>
+        <v>0.03174245399267209</v>
       </c>
       <c r="K8" t="n">
         <v>0.0298637889364883</v>
@@ -3972,16 +3972,16 @@
         <v>0.03149057444459721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03257493213716674</v>
+        <v>0.03257493213716676</v>
       </c>
       <c r="F9" t="n">
         <v>0.03159357596615592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03168276705996711</v>
+        <v>0.03168276705996709</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03352667752393112</v>
+        <v>0.03352667752393111</v>
       </c>
       <c r="I9" t="n">
         <v>0.03159348739391974</v>
@@ -3990,10 +3990,10 @@
         <v>0.03180804325449055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03096432263988127</v>
+        <v>0.03096432263988126</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03301078510640472</v>
+        <v>0.03301078510640473</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007017087402692039</v>
+        <v>0.007017087402692006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006972818637188093</v>
+        <v>0.006972818637188089</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007019360872640077</v>
+        <v>0.007019360872640041</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006986423503851077</v>
+        <v>0.00698642350385106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006986378933502979</v>
+        <v>0.006986378933502967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007020737922073407</v>
+        <v>0.007020737922073372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007018422767622619</v>
+        <v>0.007018422767622622</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007032761451797277</v>
+        <v>0.007032761451797244</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008182203835188711</v>
+        <v>0.008182203835188697</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008216894673675109</v>
+        <v>0.008216894673675097</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007017126491974617</v>
+        <v>0.00701712649197462</v>
       </c>
     </row>
     <row r="3">
@@ -4119,34 +4119,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006874426730239279</v>
+        <v>0.006874426730239266</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006795408680437999</v>
+        <v>0.006795408680438</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006891268876710498</v>
+        <v>0.006891268876710485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006910545769127301</v>
+        <v>0.006910545769127306</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006910501198779203</v>
+        <v>0.006910501198779216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006901242224488308</v>
+        <v>0.006901242224488305</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006896172436404622</v>
+        <v>0.006896172436404624</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006986812022172648</v>
+        <v>0.006986812022172642</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008892912869455075</v>
+        <v>0.008892912869455068</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008874658726676352</v>
+        <v>0.008874658726676346</v>
       </c>
       <c r="L3" t="n">
         <v>0.006880350209799989</v>
@@ -4162,10 +4162,10 @@
         <v>0.02784530868844816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0277039590001172</v>
+        <v>0.02770395900011721</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02787098857735907</v>
+        <v>0.02787098857735908</v>
       </c>
       <c r="E4" t="n">
         <v>0.02810638450806517</v>
@@ -4174,16 +4174,16 @@
         <v>0.02810638450806517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02788313431784579</v>
+        <v>0.02788313431784581</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02788035718309412</v>
+        <v>0.02788035718309413</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02800033550974281</v>
+        <v>0.02800033550974282</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02803943479124946</v>
+        <v>0.02803943479124947</v>
       </c>
       <c r="K4" t="n">
         <v>0.02788464802407224</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02972263244029694</v>
+        <v>0.02972263244029695</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981923479694937</v>
+        <v>0.02981923479694936</v>
       </c>
       <c r="D5" t="n">
         <v>0.03049619417858711</v>
@@ -4214,10 +4214,10 @@
         <v>0.03310086479488131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03084317715790464</v>
+        <v>0.03084317715790478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03105134622974487</v>
+        <v>0.03105134622974488</v>
       </c>
       <c r="I5" t="n">
         <v>0.03310082358173223</v>
@@ -4226,10 +4226,10 @@
         <v>0.03365270823873837</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03074114723088088</v>
+        <v>0.03074114723088089</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03059850147453602</v>
+        <v>0.030598501474536</v>
       </c>
     </row>
     <row r="6">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0294648059189143</v>
+        <v>0.02946480591891431</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02838499784220897</v>
+        <v>0.02838499784220894</v>
       </c>
       <c r="D6" t="n">
         <v>0.02845548407203242</v>
@@ -4257,10 +4257,10 @@
         <v>0.02847104989083479</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02957175260899339</v>
+        <v>0.02957175260899341</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02961983274020896</v>
+        <v>0.02961983274020897</v>
       </c>
       <c r="J6" t="n">
         <v>0.02868814248768888</v>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02849227891730982</v>
+        <v>0.02849227891730981</v>
       </c>
       <c r="C7" t="n">
         <v>0.02847310442807461</v>
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02952074413464758</v>
+        <v>0.02952074413464759</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03088487601354343</v>
+        <v>0.03088487601354344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03119754862156101</v>
+        <v>0.03119754862156103</v>
       </c>
       <c r="E8" t="n">
         <v>0.03068341613320838</v>
@@ -4340,16 +4340,16 @@
         <v>0.03092334610528808</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03104332443193463</v>
+        <v>0.03104332443193465</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03108269247657824</v>
+        <v>0.03108269247657825</v>
       </c>
       <c r="K8" t="n">
         <v>0.02953468046237514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03232505867191691</v>
+        <v>0.03232505867191693</v>
       </c>
     </row>
     <row r="9">
@@ -4362,34 +4362,34 @@
         <v>0.02999273086077621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03069931869035207</v>
+        <v>0.03069931869035208</v>
       </c>
       <c r="D9" t="n">
         <v>0.03074417359010499</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03171107600262738</v>
+        <v>0.03171107600262739</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03087356120588199</v>
+        <v>0.03087356120588201</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03075631880898492</v>
+        <v>0.03075631880898493</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03075354167423325</v>
+        <v>0.03075354167423326</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03087352000088193</v>
+        <v>0.03087352000088195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03091261928238859</v>
+        <v>0.0309126192823886</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02984396807252336</v>
+        <v>0.02984396807252335</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03072673028249816</v>
+        <v>0.03072673028249818</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006872754708786644</v>
+        <v>0.006872754708786638</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00687137268117303</v>
+        <v>0.006871372681173034</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006874998203953969</v>
+        <v>0.006874998203953963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0068522420571715</v>
+        <v>0.006852242057171501</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006852201251794603</v>
+        <v>0.006852201251794605</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006875252321436733</v>
+        <v>0.006875252321436728</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006873814013184109</v>
+        <v>0.006873814013184108</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00688087379957083</v>
+        <v>0.006880873799570825</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007623226634715133</v>
+        <v>0.007623226634715128</v>
       </c>
       <c r="K2" t="n">
         <v>0.008081021007326467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006873042346772898</v>
+        <v>0.006873042346772899</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006766818662769325</v>
+        <v>0.006766818662769324</v>
       </c>
       <c r="C3" t="n">
         <v>0.006761786288761675</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006783470918134592</v>
+        <v>0.006783470918134586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006778362685593326</v>
+        <v>0.006778362685593323</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00677832188021643</v>
+        <v>0.006778321880216431</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006785416617909465</v>
+        <v>0.006785416617909457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006786286475253074</v>
+        <v>0.006786286475253075</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006825387730080814</v>
+        <v>0.006825387730080811</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00808200559228427</v>
+        <v>0.008082005592284258</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008777331191908129</v>
+        <v>0.008777331191908124</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006774275390141173</v>
+        <v>0.006774275390141175</v>
       </c>
     </row>
     <row r="4">
@@ -4582,7 +4582,7 @@
         <v>0.02795242240344641</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02782876421642778</v>
+        <v>0.02782876421642777</v>
       </c>
       <c r="L4" t="n">
         <v>0.02780778088894788</v>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02936580889323374</v>
+        <v>0.02936580889323375</v>
       </c>
       <c r="C5" t="n">
         <v>0.02958333405882497</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03014584063198043</v>
+        <v>0.03014584063198044</v>
       </c>
       <c r="E5" t="n">
         <v>0.03128982570046054</v>
@@ -4610,7 +4610,7 @@
         <v>0.03128982570046054</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03026181609650593</v>
+        <v>0.03026181609650602</v>
       </c>
       <c r="H5" t="n">
         <v>0.0305977658838505</v>
@@ -4619,13 +4619,13 @@
         <v>0.03128976956021982</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03259974524289372</v>
+        <v>0.03259974524289373</v>
       </c>
       <c r="K5" t="n">
         <v>0.03026481349568233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03025443907001019</v>
+        <v>0.03025443907001018</v>
       </c>
     </row>
     <row r="6">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02941907363779988</v>
+        <v>0.02941907363779987</v>
       </c>
       <c r="C6" t="n">
         <v>0.02835943092795816</v>
@@ -4644,10 +4644,10 @@
         <v>0.02841391919188069</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02839476331711562</v>
+        <v>0.02839476331711563</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02847565431854325</v>
+        <v>0.02847565431854326</v>
       </c>
       <c r="G6" t="n">
         <v>0.02842233419703891</v>
@@ -4656,7 +4656,7 @@
         <v>0.02951758675048365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02846828861608557</v>
+        <v>0.02846828861608558</v>
       </c>
       <c r="J6" t="n">
         <v>0.02957249789268893</v>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02841986185461976</v>
+        <v>0.02841986185461975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02840740966845592</v>
+        <v>0.02840740966845593</v>
       </c>
       <c r="D7" t="n">
         <v>0.0284450954453648</v>
@@ -4693,16 +4693,16 @@
         <v>0.02844484980833874</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02845134562427226</v>
+        <v>0.02845134562427225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0284908042273854</v>
+        <v>0.02849080422738541</v>
       </c>
       <c r="J7" t="n">
         <v>0.02857521513287383</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0284515569458552</v>
+        <v>0.02845155694585519</v>
       </c>
       <c r="L7" t="n">
         <v>0.0284305736183753</v>
@@ -4724,7 +4724,7 @@
         <v>0.03107480878667908</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03048831429505322</v>
+        <v>0.03048831429505323</v>
       </c>
       <c r="F8" t="n">
         <v>0.02955560679816256</v>
@@ -4733,16 +4733,16 @@
         <v>0.03079713668148122</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03080363249741753</v>
+        <v>0.03080363249741752</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03084309110052788</v>
+        <v>0.03084309110052789</v>
       </c>
       <c r="J8" t="n">
         <v>0.03092776484329457</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02944160020721943</v>
+        <v>0.02944160020721941</v>
       </c>
       <c r="L8" t="n">
         <v>0.03217988736140667</v>
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02976255246433077</v>
+        <v>0.02976255246433078</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03042286417778825</v>
+        <v>0.03042286417778826</v>
       </c>
       <c r="D9" t="n">
         <v>0.03046065817257465</v>
       </c>
       <c r="E9" t="n">
-        <v>0.031282670569645</v>
+        <v>0.03128267056964502</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03050631485028194</v>
+        <v>0.03050631485028195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03046030431767107</v>
+        <v>0.03046030431767108</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03046680013360459</v>
+        <v>0.0304668001336046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03050625873671774</v>
+        <v>0.03050625873671775</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03059066964220616</v>
+        <v>0.03059066964220617</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03006139484622396</v>
+        <v>0.03006139484622397</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03044602812770763</v>
+        <v>0.03044602812770764</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007689051154563467</v>
+        <v>0.007689051154563465</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008876697655600152</v>
+        <v>0.00887669765560015</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007727831958185443</v>
+        <v>0.007727831958185447</v>
       </c>
       <c r="E2" t="n">
         <v>0.009222478655362106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007854791354000102</v>
+        <v>0.007854791354000105</v>
       </c>
       <c r="G2" t="n">
         <v>0.007730907996527231</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008085478990121797</v>
+        <v>0.008085478990121799</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007553405351633568</v>
+        <v>0.00755340535163357</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009761847641259083</v>
+        <v>0.009761847641259072</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009267614473374576</v>
+        <v>0.009267614473374573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008457497741756274</v>
+        <v>0.008457497741756271</v>
       </c>
     </row>
     <row r="3">
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008482034383285581</v>
+        <v>0.008482034383285568</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00970671171243782</v>
+        <v>0.009706711712437813</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008759924006406308</v>
+        <v>0.008759924006406312</v>
       </c>
       <c r="E3" t="n">
         <v>0.01027317985273666</v>
@@ -4926,22 +4926,22 @@
         <v>0.008015588841208569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008784014978489933</v>
+        <v>0.008784014978489931</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01132728294160662</v>
+        <v>0.01132728294160661</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00751783617078109</v>
+        <v>0.007517836170781091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01238565087272687</v>
+        <v>0.01238565087272686</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01052332557520398</v>
+        <v>0.01052332557520397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01395845247885465</v>
+        <v>0.01395845247885464</v>
       </c>
     </row>
     <row r="4">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03058175394805644</v>
+        <v>0.03058175394805642</v>
       </c>
       <c r="C4" t="n">
         <v>0.0288844219530574</v>
@@ -4966,22 +4966,22 @@
         <v>0.02891892149828424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03104995461494517</v>
+        <v>0.03104995461494516</v>
       </c>
       <c r="H4" t="n">
         <v>0.03504907283668088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02901961002217228</v>
+        <v>0.02901961002217229</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03155968041796114</v>
+        <v>0.03155968041796115</v>
       </c>
       <c r="K4" t="n">
         <v>0.02941104675957781</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03916234800331945</v>
+        <v>0.03916234800331944</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07138654583479991</v>
+        <v>0.07138654583479975</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04456279684235388</v>
+        <v>0.0445627968423539</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08028592233328655</v>
+        <v>0.08028592233328659</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04456280031577332</v>
+        <v>0.04456280031577337</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04456280031577332</v>
+        <v>0.04456280031577338</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0821268623080991</v>
+        <v>0.08212686230809915</v>
       </c>
       <c r="H5" t="n">
         <v>0.1678875518030925</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04456226400663568</v>
+        <v>0.0445622640066357</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09382216463277804</v>
+        <v>0.093822164632778</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05159383022479266</v>
+        <v>0.05159383022479262</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0931386676558682</v>
+        <v>0.09313866765586824</v>
       </c>
     </row>
     <row r="6">
@@ -5031,22 +5031,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03128826067010834</v>
+        <v>0.03128826067010831</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02965187909681428</v>
+        <v>0.0296518790968143</v>
       </c>
       <c r="D6" t="n">
         <v>0.03175211490951257</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02957072288842352</v>
+        <v>0.02957072288842353</v>
       </c>
       <c r="F6" t="n">
         <v>0.02971693652702893</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03175646133699703</v>
+        <v>0.03175646133699704</v>
       </c>
       <c r="H6" t="n">
         <v>0.03723563721061222</v>
@@ -5055,10 +5055,10 @@
         <v>0.03111843959154376</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03234906384634141</v>
+        <v>0.0323490638463414</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03007407682333268</v>
+        <v>0.03007407682333271</v>
       </c>
       <c r="L6" t="n">
         <v>0.03992770954726715</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03147822956131628</v>
+        <v>0.03147822956131625</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0299166184711503</v>
+        <v>0.02991661847115031</v>
       </c>
       <c r="D7" t="n">
         <v>0.03191615157195266</v>
@@ -5089,7 +5089,7 @@
         <v>0.03194643022820499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0359455484499407</v>
+        <v>0.03594554844994072</v>
       </c>
       <c r="I7" t="n">
         <v>0.02991608563543212</v>
@@ -5098,10 +5098,10 @@
         <v>0.03245615603122098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03030752237283764</v>
+        <v>0.03030752237283765</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04005882361657926</v>
+        <v>0.04005882361657927</v>
       </c>
     </row>
     <row r="8">
@@ -5111,22 +5111,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03274419174082569</v>
+        <v>0.03274419174082568</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03291666242937553</v>
+        <v>0.03291666242937555</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03527716936998578</v>
+        <v>0.03527716936998577</v>
       </c>
       <c r="E8" t="n">
         <v>0.03244220169838245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03123669110017636</v>
+        <v>0.03123669110017635</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03494753077590914</v>
+        <v>0.03494753077590911</v>
       </c>
       <c r="H8" t="n">
         <v>0.03894664899764495</v>
@@ -5135,13 +5135,13 @@
         <v>0.03291718618313626</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03545759758308762</v>
+        <v>0.03545759758308761</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03154125346635527</v>
+        <v>0.03154125346635526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04487242127955062</v>
+        <v>0.04487242127955065</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03423200380224905</v>
+        <v>0.03423200380224904</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0338370797142399</v>
+        <v>0.03383707971423991</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03583673794510289</v>
+        <v>0.03583673794510288</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0351834129897558</v>
+        <v>0.03518341298975581</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03383708128966989</v>
+        <v>0.0338370812896699</v>
       </c>
       <c r="G9" t="n">
         <v>0.03586689147129458</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03986600969303034</v>
+        <v>0.03986600969303033</v>
       </c>
       <c r="I9" t="n">
         <v>0.03383654687852171</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03637661727431059</v>
+        <v>0.03637661727431057</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03355200063698702</v>
+        <v>0.03355200063698701</v>
       </c>
       <c r="L9" t="n">
         <v>0.04397928485966885</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007606271422085338</v>
+        <v>0.007606271422085342</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008848684089980246</v>
+        <v>0.008848684089980248</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007687149830679107</v>
+        <v>0.00768714983067911</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009199216450245398</v>
+        <v>0.0091992164502454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007822461618923589</v>
+        <v>0.007822461618923592</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007680675542277689</v>
+        <v>0.00768067554227769</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007949946437015439</v>
+        <v>0.007949946437015441</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007527982365324446</v>
+        <v>0.007527982365324451</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009649532500890495</v>
+        <v>0.009649532500890498</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009228384790761355</v>
+        <v>0.009228384790761358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0083500307641789</v>
+        <v>0.008350030764178912</v>
       </c>
     </row>
     <row r="3">
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008108095649802074</v>
+        <v>0.008108095649802076</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009734407347686332</v>
+        <v>0.009734407347686337</v>
       </c>
       <c r="D3" t="n">
         <v>0.008682762814882632</v>
@@ -5325,19 +5325,19 @@
         <v>0.008639027186026663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01057757388407124</v>
+        <v>0.01057757388407125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007550102858072531</v>
+        <v>0.007550102858072532</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0117820083873117</v>
+        <v>0.01178200838731171</v>
       </c>
       <c r="K3" t="n">
         <v>0.01047726140773735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01340899615330363</v>
+        <v>0.01340899615330365</v>
       </c>
     </row>
     <row r="4">
@@ -5353,7 +5353,7 @@
         <v>0.02895381108456386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03088320479848667</v>
+        <v>0.03088320479848668</v>
       </c>
       <c r="E4" t="n">
         <v>0.0289842556898364</v>
@@ -5362,10 +5362,10 @@
         <v>0.0289842556898364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0308058158080149</v>
+        <v>0.03080581580801489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0338508197788695</v>
+        <v>0.03385081977886949</v>
       </c>
       <c r="I4" t="n">
         <v>0.02905758936423668</v>
@@ -5374,7 +5374,7 @@
         <v>0.03058033899768603</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02933543130094594</v>
+        <v>0.02933543130094595</v>
       </c>
       <c r="L4" t="n">
         <v>0.03827996381691606</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0599943950905795</v>
+        <v>0.05999439509057953</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04472052803048714</v>
+        <v>0.04472052803048721</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07482239022664545</v>
+        <v>0.07482239022664554</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04472053088706247</v>
+        <v>0.04472053088706249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04472053088706247</v>
+        <v>0.04472053088706249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0748055962825349</v>
+        <v>0.07480559628253493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1374925471447037</v>
+        <v>0.137492547144704</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04472005908665106</v>
+        <v>0.0447200590866511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07313472961645988</v>
+        <v>0.07313472961645991</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04857921413195974</v>
+        <v>0.04857921413195966</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09600052653895087</v>
+        <v>0.09600052653895071</v>
       </c>
     </row>
     <row r="6">
@@ -5445,7 +5445,7 @@
         <v>0.03149963612140506</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03589524964447404</v>
+        <v>0.03589524964447405</v>
       </c>
       <c r="I6" t="n">
         <v>0.03103477610602233</v>
@@ -5457,7 +5457,7 @@
         <v>0.03000239050860296</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03901830300522619</v>
+        <v>0.03901830300522618</v>
       </c>
     </row>
     <row r="7">
@@ -5470,7 +5470,7 @@
         <v>0.03077866873434564</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02986708107490448</v>
+        <v>0.02986708107490447</v>
       </c>
       <c r="D7" t="n">
         <v>0.03169211089882395</v>
@@ -5488,7 +5488,7 @@
         <v>0.0346598425457012</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02986661213106841</v>
+        <v>0.02986661213106842</v>
       </c>
       <c r="J7" t="n">
         <v>0.03138936176451775</v>
@@ -5510,7 +5510,7 @@
         <v>0.03193483585726295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03260092346960974</v>
+        <v>0.03260092346960972</v>
       </c>
       <c r="D8" t="n">
         <v>0.03475491535742645</v>
@@ -5522,13 +5522,13 @@
         <v>0.03107221109010223</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03435009244345734</v>
+        <v>0.03435009244345735</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0373950964143122</v>
+        <v>0.03739509641431221</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03260186599967913</v>
+        <v>0.03260186599967912</v>
       </c>
       <c r="J8" t="n">
         <v>0.03412492596868866</v>
@@ -5550,10 +5550,10 @@
         <v>0.03305955426729021</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03314631604667529</v>
+        <v>0.03314631604667528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03497146280772524</v>
+        <v>0.03497146280772526</v>
       </c>
       <c r="E9" t="n">
         <v>0.03429839138148422</v>
@@ -5565,7 +5565,7 @@
         <v>0.03489407354661742</v>
       </c>
       <c r="H9" t="n">
-        <v>0.037939077517472</v>
+        <v>0.03793907751747202</v>
       </c>
       <c r="I9" t="n">
         <v>0.03314584710283922</v>
@@ -5574,10 +5574,10 @@
         <v>0.03466859673628855</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03284524156770029</v>
+        <v>0.0328452415677003</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04236822155551854</v>
+        <v>0.04236822155551857</v>
       </c>
     </row>
   </sheetData>
@@ -5663,31 +5663,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0075257485503008</v>
+        <v>0.007525748550300803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008594232351505053</v>
+        <v>0.008594232351505051</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007588661595591697</v>
+        <v>0.007588661595591704</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008837728011564596</v>
+        <v>0.0088377280115646</v>
       </c>
       <c r="F2" t="n">
         <v>0.007793374904273578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007591289799080744</v>
+        <v>0.007591289799080755</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00774932851547656</v>
+        <v>0.007749328515476562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007498725229078684</v>
+        <v>0.007498725229078691</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008988467060728072</v>
+        <v>0.008988467060728067</v>
       </c>
       <c r="K2" t="n">
         <v>0.009153530748178974</v>
@@ -5703,34 +5703,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007895038861151549</v>
+        <v>0.007895038861151551</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009514279557371611</v>
+        <v>0.009514279557371616</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008341254532201874</v>
+        <v>0.008341254532201883</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00991277414968279</v>
+        <v>0.009912774149682788</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008188904252698574</v>
+        <v>0.008188904252698572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008362459191679423</v>
+        <v>0.008362459191679432</v>
       </c>
       <c r="H3" t="n">
         <v>0.009505128487792372</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007702265590676049</v>
+        <v>0.007702265590676037</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01030371214183275</v>
+        <v>0.01030371214183274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01032251685724758</v>
+        <v>0.01032251685724759</v>
       </c>
       <c r="L3" t="n">
         <v>0.01273786969795205</v>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02968384859269762</v>
+        <v>0.02968384859269764</v>
       </c>
       <c r="C4" t="n">
         <v>0.02926709924101203</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03039448038068907</v>
+        <v>0.03039448038068908</v>
       </c>
       <c r="E4" t="n">
         <v>0.02929613089560028</v>
@@ -5767,13 +5767,13 @@
         <v>0.02935295548492841</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02966088610241422</v>
+        <v>0.02966088610241423</v>
       </c>
       <c r="K4" t="n">
         <v>0.02915042681316558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03728246949460098</v>
+        <v>0.037282469494601</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0546394418979539</v>
+        <v>0.05463944189795394</v>
       </c>
       <c r="C5" t="n">
         <v>0.04926387934146235</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0657582126682166</v>
+        <v>0.06575821266821659</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04926388178262156</v>
+        <v>0.04926388178262157</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04926388178262156</v>
+        <v>0.04926388178262157</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06754743775675001</v>
+        <v>0.06754743775675019</v>
       </c>
       <c r="H5" t="n">
         <v>0.1037875320762363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0492635661238016</v>
+        <v>0.04926356612380159</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05700157007237125</v>
+        <v>0.05700157007237126</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04500604169834096</v>
+        <v>0.04500604169834103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07571086986663332</v>
+        <v>0.07571086986663358</v>
       </c>
     </row>
     <row r="6">
@@ -5823,13 +5823,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03038250762843065</v>
+        <v>0.03038250762843062</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03001315941308095</v>
+        <v>0.03001315941308094</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03110382861199992</v>
+        <v>0.03110382861199993</v>
       </c>
       <c r="E6" t="n">
         <v>0.02993272184536873</v>
@@ -5838,13 +5838,13 @@
         <v>0.03005072766744589</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03237566947789181</v>
+        <v>0.03237566947789185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0342385177579466</v>
+        <v>0.03423851775794661</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03005161452066143</v>
+        <v>0.03005161452066141</v>
       </c>
       <c r="J6" t="n">
         <v>0.03161895638054512</v>
@@ -5869,7 +5869,7 @@
         <v>0.03013768925492133</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03117878388475902</v>
+        <v>0.03117878388475905</v>
       </c>
       <c r="E7" t="n">
         <v>0.03013563689690271</v>
@@ -5878,7 +5878,7 @@
         <v>0.03013563689690271</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03120463672351754</v>
+        <v>0.03120463672351756</v>
       </c>
       <c r="H7" t="n">
         <v>0.03300498126843286</v>
@@ -5906,7 +5906,7 @@
         <v>0.03159630208907813</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03280422613321259</v>
+        <v>0.03280422613321261</v>
       </c>
       <c r="D8" t="n">
         <v>0.03416628770503749</v>
@@ -5918,19 +5918,19 @@
         <v>0.03131338495086107</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03387269020484366</v>
+        <v>0.03387269020484365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03567303474975932</v>
+        <v>0.03567303474975934</v>
       </c>
       <c r="I8" t="n">
         <v>0.0328054295185867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03311366279401402</v>
+        <v>0.03311366279401403</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03103427363743578</v>
+        <v>0.03103427363743579</v>
       </c>
       <c r="L8" t="n">
         <v>0.04234362375366903</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03245662975745999</v>
+        <v>0.03245662975746001</v>
       </c>
       <c r="C9" t="n">
         <v>0.03303427685763329</v>
@@ -5958,7 +5958,7 @@
         <v>0.03303427822714249</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03410122432622949</v>
+        <v>0.03410122432622952</v>
       </c>
       <c r="H9" t="n">
         <v>0.03590156887114482</v>
@@ -5970,10 +5970,10 @@
         <v>0.03334189425745838</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03230520485608993</v>
+        <v>0.03230520485608995</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04096347764964513</v>
+        <v>0.04096347764964514</v>
       </c>
     </row>
   </sheetData>
@@ -6065,28 +6065,28 @@
         <v>0.008527685910779837</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007248606738922384</v>
+        <v>0.007248606738922385</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008859325421548228</v>
+        <v>0.008859325421548226</v>
       </c>
       <c r="F2" t="n">
         <v>0.007526489411953556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007265848916765713</v>
+        <v>0.007265848916765714</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007375215359309277</v>
+        <v>0.007375215359309278</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00720768318506727</v>
+        <v>0.007207683185067269</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009266451454015397</v>
+        <v>0.009266451454015407</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008918580818212047</v>
+        <v>0.008918580818212051</v>
       </c>
       <c r="L2" t="n">
         <v>0.007404683429272373</v>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007019517380366906</v>
+        <v>0.007019517380366901</v>
       </c>
       <c r="C3" t="n">
         <v>0.009168728698076386</v>
@@ -6108,22 +6108,22 @@
         <v>0.007276559281957994</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009713738044862341</v>
+        <v>0.009713738044862346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007513676740520147</v>
+        <v>0.00751367674052014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007400432204221118</v>
+        <v>0.007400432204221114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008187187407937568</v>
+        <v>0.008187187407937566</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006987164972204747</v>
+        <v>0.006987164972204743</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01110604198269913</v>
+        <v>0.01110604198269915</v>
       </c>
       <c r="K3" t="n">
         <v>0.01000690534390317</v>
@@ -6166,7 +6166,7 @@
         <v>0.02986820515202174</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02879446574626403</v>
+        <v>0.02879446574626402</v>
       </c>
       <c r="L4" t="n">
         <v>0.03060142624716859</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03746178306162188</v>
+        <v>0.0374617830616218</v>
       </c>
       <c r="C5" t="n">
         <v>0.03657108870698893</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04384524960589993</v>
+        <v>0.04384524960589992</v>
       </c>
       <c r="E5" t="n">
         <v>0.03657109207773229</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0365710920777323</v>
+        <v>0.03657109207773229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04797704841553781</v>
+        <v>0.04797704841553787</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0717731218857267</v>
+        <v>0.07177312188572664</v>
       </c>
       <c r="I5" t="n">
         <v>0.03657086748095219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0654233882305999</v>
+        <v>0.06542338823059991</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04324039975834231</v>
+        <v>0.04324039975834228</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08236441270286725</v>
+        <v>0.08236441270286721</v>
       </c>
     </row>
     <row r="6">
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03023588988391637</v>
+        <v>0.03023588988391636</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02894830884704664</v>
+        <v>0.02894830884704665</v>
       </c>
       <c r="D6" t="n">
         <v>0.03066560042023459</v>
@@ -6274,7 +6274,7 @@
         <v>0.0291127601554823</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0297916707041876</v>
+        <v>0.02979167070418761</v>
       </c>
       <c r="H7" t="n">
         <v>0.03104139338285977</v>
@@ -6286,7 +6286,7 @@
         <v>0.03061868025068451</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02954494084492679</v>
+        <v>0.0295449408449268</v>
       </c>
       <c r="L7" t="n">
         <v>0.03135190134583136</v>
@@ -6302,7 +6302,7 @@
         <v>0.03032847018790195</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03178418235134078</v>
+        <v>0.03178418235134079</v>
       </c>
       <c r="D8" t="n">
         <v>0.03258928703245001</v>
@@ -6311,25 +6311,25 @@
         <v>0.03136519490332124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03030064003936855</v>
+        <v>0.03030064003936856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03246256915104059</v>
+        <v>0.03246256915104058</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03371229182971277</v>
+        <v>0.03371229182971278</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03178509423834861</v>
+        <v>0.0317850942383486</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03328987984500051</v>
+        <v>0.03328987984500052</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03065504085845792</v>
+        <v>0.03065504085845791</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03562345134364493</v>
+        <v>0.03562345134364495</v>
       </c>
     </row>
     <row r="9">
@@ -6342,7 +6342,7 @@
         <v>0.03130364748565911</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03216480210443933</v>
+        <v>0.03216480210443932</v>
       </c>
       <c r="D9" t="n">
         <v>0.03265103453861832</v>
@@ -6357,7 +6357,7 @@
         <v>0.03284205579109455</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03409177846976671</v>
+        <v>0.0340917784697667</v>
       </c>
       <c r="I9" t="n">
         <v>0.03216458087840258</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007193873487459772</v>
+        <v>0.007193873487459769</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008538116044296724</v>
+        <v>0.008538116044296723</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007197066548719589</v>
+        <v>0.007197066548719586</v>
       </c>
       <c r="E2" t="n">
         <v>0.008874817465398113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007532386307523026</v>
+        <v>0.007532386307523025</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007222169382602022</v>
+        <v>0.007222169382602021</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007171294885492926</v>
+        <v>0.007171294885492924</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007210192255173754</v>
+        <v>0.007210192255173751</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00922948863684029</v>
+        <v>0.009229488636840288</v>
       </c>
       <c r="K2" t="n">
         <v>0.008918497785990701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007152018098693668</v>
+        <v>0.007152018098693665</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007052067762369794</v>
+        <v>0.007052067762369791</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009361314676383983</v>
+        <v>0.009361314676383979</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007073405003185326</v>
+        <v>0.007073405003185322</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009915087717969758</v>
+        <v>0.009915087717969761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007699187156359802</v>
+        <v>0.007699187156359799</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007252304707213289</v>
+        <v>0.00725230470721329</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006908511837337841</v>
+        <v>0.00690851183733784</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007167080336489689</v>
+        <v>0.007167080336489686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01091747122419775</v>
+        <v>0.01091747122419774</v>
       </c>
       <c r="K3" t="n">
         <v>0.01011948213185678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006766939348895197</v>
+        <v>0.006766939348895199</v>
       </c>
     </row>
     <row r="4">
@@ -6547,16 +6547,16 @@
         <v>0.0285931818041815</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02859318180418151</v>
+        <v>0.0285931818041815</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02880355918649161</v>
+        <v>0.0288035591864916</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02826207756487548</v>
+        <v>0.02826207756487549</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02865051961633846</v>
+        <v>0.02865051961633845</v>
       </c>
       <c r="J4" t="n">
         <v>0.02953022824567181</v>
@@ -6575,22 +6575,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03830464219206439</v>
+        <v>0.03830464219206441</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04078971234711106</v>
+        <v>0.04078971234711104</v>
       </c>
       <c r="D5" t="n">
         <v>0.03819019148381793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04078971501574288</v>
+        <v>0.04078971501574287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04078971501574288</v>
+        <v>0.04078971501574287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04306696349340553</v>
+        <v>0.04306696349340543</v>
       </c>
       <c r="H5" t="n">
         <v>0.03501645397014591</v>
@@ -6599,13 +6599,13 @@
         <v>0.0407896102293862</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05604544614757196</v>
+        <v>0.05604544614757191</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04499457943278154</v>
+        <v>0.04499457943278155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03538695389256103</v>
+        <v>0.03538695389256105</v>
       </c>
     </row>
     <row r="6">
@@ -6618,19 +6618,19 @@
         <v>0.0301820087471482</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02925802381926704</v>
+        <v>0.02925802381926702</v>
       </c>
       <c r="D6" t="n">
         <v>0.0291486495115434</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02918137839092789</v>
+        <v>0.02918137839092788</v>
       </c>
       <c r="F6" t="n">
         <v>0.02927796722964082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03049836407858366</v>
+        <v>0.03049836407858367</v>
       </c>
       <c r="H6" t="n">
         <v>0.03000585950653761</v>
@@ -6658,19 +6658,19 @@
         <v>0.02916056805734626</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02932398593635344</v>
+        <v>0.02932398593635343</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02919651928350185</v>
+        <v>0.02919651928350184</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0293224985095564</v>
+        <v>0.02932249850955639</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0293224985095564</v>
+        <v>0.02932249850955639</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02947692338878175</v>
+        <v>0.02947692338878174</v>
       </c>
       <c r="H7" t="n">
         <v>0.02893544176716563</v>
@@ -6682,7 +6682,7 @@
         <v>0.03020359244796194</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02962049673357152</v>
+        <v>0.02962049673357153</v>
       </c>
       <c r="L7" t="n">
         <v>0.02870901558221837</v>
@@ -6698,28 +6698,28 @@
         <v>0.03019384706432855</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03174276885045865</v>
+        <v>0.03174276885045866</v>
       </c>
       <c r="D8" t="n">
         <v>0.03190392948203635</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03136365093982333</v>
+        <v>0.03136365093982332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03040039813610656</v>
+        <v>0.03040039813610655</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03189671524590408</v>
+        <v>0.03189671524590407</v>
       </c>
       <c r="H8" t="n">
         <v>0.03135523362428771</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03174367567575092</v>
+        <v>0.03174367567575091</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03262365679443733</v>
+        <v>0.03262365679443732</v>
       </c>
       <c r="K8" t="n">
         <v>0.03062802055253623</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03093263437477456</v>
+        <v>0.03093263437477455</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03190385156352784</v>
+        <v>0.03190385156352783</v>
       </c>
       <c r="D9" t="n">
         <v>0.03177650150212413</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03283603804154988</v>
+        <v>0.03283603804154987</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03190385413741534</v>
+        <v>0.03190385413741533</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03205678901595615</v>
+        <v>0.03205678901595613</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03151530739434003</v>
+        <v>0.03151530739434002</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03190374944580299</v>
+        <v>0.03190374944580298</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03278345807513636</v>
+        <v>0.03278345807513635</v>
       </c>
       <c r="K9" t="n">
         <v>0.03173232057178971</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03128888120939278</v>
+        <v>0.03128888120939277</v>
       </c>
     </row>
   </sheetData>
@@ -6851,28 +6851,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007214851584424843</v>
+        <v>0.007214851584424846</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008297313966362501</v>
+        <v>0.008297313966362503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007164648602047114</v>
+        <v>0.00716464860204712</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008530887547614512</v>
+        <v>0.008530887547614515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007511385939484963</v>
+        <v>0.007511385939484959</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007201859045867988</v>
+        <v>0.007201859045867991</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00715250692767171</v>
+        <v>0.007152506927671709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007204612701073358</v>
+        <v>0.00720461270107336</v>
       </c>
       <c r="J2" t="n">
         <v>0.008680973708567116</v>
@@ -6881,7 +6881,7 @@
         <v>0.008892757507081165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007149426400137463</v>
+        <v>0.007149426400137462</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007291275971680643</v>
+        <v>0.007291275971680641</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009023963154077648</v>
+        <v>0.009023963154077649</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006934392525150604</v>
+        <v>0.006934392525150602</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009407651969120722</v>
+        <v>0.009407651969120724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00772480506833105</v>
+        <v>0.007724805068331054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007199059611779507</v>
+        <v>0.007199059611779505</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006865445673253231</v>
+        <v>0.006865445673253235</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007218151313986457</v>
+        <v>0.007218151313986461</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009909481848345558</v>
+        <v>0.009909481848345562</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01005179230339576</v>
+        <v>0.01005179230339577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006837778892971589</v>
+        <v>0.006837778892971588</v>
       </c>
     </row>
     <row r="4">
@@ -6940,10 +6940,10 @@
         <v>0.02831499219528406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02870002980639543</v>
+        <v>0.02870002980639544</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02870002980639543</v>
+        <v>0.02870002980639544</v>
       </c>
       <c r="G4" t="n">
         <v>0.02873201527830623</v>
@@ -6952,10 +6952,10 @@
         <v>0.02820709426658551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02874522966478781</v>
+        <v>0.02874522966478782</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02928745835020167</v>
+        <v>0.02928745835020166</v>
       </c>
       <c r="K4" t="n">
         <v>0.02886669502238478</v>
@@ -6974,34 +6974,34 @@
         <v>0.04461079200810287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04251865334022498</v>
+        <v>0.042518653340225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03531600653694261</v>
+        <v>0.03531600653694258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04251865562443866</v>
+        <v>0.04251865562443867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04251865562443866</v>
+        <v>0.04251865562443867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0422772210287747</v>
+        <v>0.04227722102877476</v>
       </c>
       <c r="H5" t="n">
         <v>0.03434974980742986</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04251858854725476</v>
+        <v>0.04251858854725478</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0523997978875026</v>
+        <v>0.05239979788750265</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04345158129929844</v>
+        <v>0.04345158129929846</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03882095429164702</v>
+        <v>0.03882095429164701</v>
       </c>
     </row>
     <row r="6">
@@ -7014,10 +7014,10 @@
         <v>0.02953001807757407</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02937185087916469</v>
+        <v>0.0293718508791647</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02894059484227154</v>
+        <v>0.02894059484227153</v>
       </c>
       <c r="E6" t="n">
         <v>0.02929381545149425</v>
@@ -7038,7 +7038,7 @@
         <v>0.02999812178198344</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02951864261360386</v>
+        <v>0.02951864261360385</v>
       </c>
       <c r="L6" t="n">
         <v>0.02880267521528395</v>
@@ -7054,7 +7054,7 @@
         <v>0.02954757964322947</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02941081612523413</v>
+        <v>0.02941081612523414</v>
       </c>
       <c r="D7" t="n">
         <v>0.02898039760291226</v>
@@ -7078,10 +7078,10 @@
         <v>0.02995298001767774</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02953221668986086</v>
+        <v>0.02953221668986087</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02882654372341707</v>
+        <v>0.02882654372341706</v>
       </c>
     </row>
     <row r="8">
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03057343975957995</v>
+        <v>0.03057343975957996</v>
       </c>
       <c r="C8" t="n">
         <v>0.03181062842430477</v>
@@ -7100,7 +7100,7 @@
         <v>0.03166648550914457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03143466258598143</v>
+        <v>0.03143466258598144</v>
       </c>
       <c r="F8" t="n">
         <v>0.03047942249067962</v>
@@ -7112,10 +7112,10 @@
         <v>0.03127347300470965</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03181160840291226</v>
+        <v>0.03181160840291225</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03235410731448594</v>
+        <v>0.03235410731448595</v>
       </c>
       <c r="K8" t="n">
         <v>0.03053253553187023</v>
@@ -7131,34 +7131,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03114451941252093</v>
+        <v>0.03114451941252094</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03176416251617714</v>
+        <v>0.03176416251617715</v>
       </c>
       <c r="D9" t="n">
         <v>0.03133386092487335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0326370425091711</v>
+        <v>0.03263704250917111</v>
       </c>
       <c r="F9" t="n">
         <v>0.0317641647196562</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03175088333672532</v>
+        <v>0.03175088333672533</v>
       </c>
       <c r="H9" t="n">
         <v>0.0312259623250046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0317640977232069</v>
+        <v>0.03176409772320691</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03230632640862075</v>
+        <v>0.03230632640862077</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03142951741676343</v>
+        <v>0.03142951741676344</v>
       </c>
       <c r="L9" t="n">
         <v>0.03117989011436007</v>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007539701725224817</v>
+        <v>0.007539701725224811</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008784425179469925</v>
+        <v>0.008784425179469927</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007648307714605023</v>
+        <v>0.007648307714605018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009123853696442197</v>
+        <v>0.009123853696442183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007772448950803625</v>
+        <v>0.007772448950803617</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007630943763556179</v>
+        <v>0.007630943763556173</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008004359003465673</v>
+        <v>0.00800435900346567</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007471996291689214</v>
+        <v>0.007471996291689207</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009554446548666138</v>
+        <v>0.009554446548666131</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00919132384773011</v>
+        <v>0.009191323847730118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008255501285572424</v>
+        <v>0.008255501285572418</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007857371994187044</v>
+        <v>0.00785737199418704</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009546843535087996</v>
+        <v>0.009546843535087998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008628001849519231</v>
+        <v>0.008628001849519232</v>
       </c>
       <c r="E3" t="n">
         <v>0.01010320092374035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007872487513148053</v>
+        <v>0.007872487513148061</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008507730803677751</v>
+        <v>0.008507730803677753</v>
       </c>
       <c r="H3" t="n">
         <v>0.01116538572085428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007376274552178035</v>
+        <v>0.007376274552178028</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01156571507162349</v>
+        <v>0.01156571507162347</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01043726931225191</v>
+        <v>0.0104372693122519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0129573539542152</v>
+        <v>0.01295735395421521</v>
       </c>
     </row>
     <row r="4">
@@ -7342,13 +7342,13 @@
         <v>0.02873220250529032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03065141472615993</v>
+        <v>0.03065141472615994</v>
       </c>
       <c r="H4" t="n">
         <v>0.03485870382603872</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02883142585563099</v>
+        <v>0.02883142585563098</v>
       </c>
       <c r="J4" t="n">
         <v>0.03040336452802465</v>
@@ -7357,7 +7357,7 @@
         <v>0.02932129669967937</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03762624476855576</v>
+        <v>0.03762624476855575</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05541653309393459</v>
+        <v>0.05541653309393455</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04210669767255038</v>
+        <v>0.0421066976725503</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07611115070307271</v>
+        <v>0.07611115070307281</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04210670114145362</v>
+        <v>0.04210670114145355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04210670114145362</v>
+        <v>0.04210670114145355</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0744316944739461</v>
+        <v>0.07443169447394618</v>
       </c>
       <c r="H5" t="n">
         <v>0.1543239475398602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04210621359856628</v>
+        <v>0.04210621359856623</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0727414272718306</v>
+        <v>0.07274142727183057</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05035226870432253</v>
+        <v>0.05035226870432254</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07557962096529806</v>
+        <v>0.07557962096529834</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03030923782929562</v>
+        <v>0.03030923782929561</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02944622129710995</v>
+        <v>0.02944622129710993</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03156685217851462</v>
+        <v>0.03156685217851463</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02936665553169712</v>
+        <v>0.02936665553169713</v>
       </c>
       <c r="F6" t="n">
         <v>0.02950644984455378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03267913675554502</v>
+        <v>0.03267913675554503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03698584179354703</v>
+        <v>0.03698584179354704</v>
       </c>
       <c r="I6" t="n">
         <v>0.03085914788501607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03245359926558473</v>
+        <v>0.03245359926558472</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02996971159554037</v>
+        <v>0.0299697115955404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03836083848193962</v>
+        <v>0.03836083848193963</v>
       </c>
     </row>
     <row r="7">
@@ -7453,7 +7453,7 @@
         <v>0.02968873620391066</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0317087080657795</v>
+        <v>0.03170870806577952</v>
       </c>
       <c r="E7" t="n">
         <v>0.02968700557157081</v>
@@ -7465,7 +7465,7 @@
         <v>0.0315082410004555</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03571553010033427</v>
+        <v>0.03571553010033428</v>
       </c>
       <c r="I7" t="n">
         <v>0.02968825212992655</v>
@@ -7477,7 +7477,7 @@
         <v>0.03017812297397493</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03848307104285129</v>
+        <v>0.0384830710428513</v>
       </c>
     </row>
     <row r="8">
@@ -7490,10 +7490,10 @@
         <v>0.03171586861335107</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03260342870633461</v>
+        <v>0.03260342870633459</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03497348712935156</v>
+        <v>0.03497348712935155</v>
       </c>
       <c r="E8" t="n">
         <v>0.03214349285813875</v>
@@ -7505,7 +7505,7 @@
         <v>0.03442410652527395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03863139562515294</v>
+        <v>0.03863139562515296</v>
       </c>
       <c r="I8" t="n">
         <v>0.03260411765474501</v>
@@ -7514,7 +7514,7 @@
         <v>0.03417638690279098</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03138066834874843</v>
+        <v>0.03138066834874844</v>
       </c>
       <c r="L8" t="n">
         <v>0.0431560042945879</v>
@@ -7527,22 +7527,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03311181060644269</v>
+        <v>0.03311181060644271</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03343665284003384</v>
+        <v>0.03343665284003386</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03545674908037906</v>
+        <v>0.03545674908037907</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03472701447330712</v>
+        <v>0.03472701447330713</v>
       </c>
       <c r="F9" t="n">
         <v>0.03343665446516646</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03525615763657868</v>
+        <v>0.03525615763657871</v>
       </c>
       <c r="H9" t="n">
         <v>0.03946344673645748</v>
@@ -7551,13 +7551,13 @@
         <v>0.03343616876604975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0350081074384434</v>
+        <v>0.03500810743844341</v>
       </c>
       <c r="K9" t="n">
         <v>0.03327815948503512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04223098767897453</v>
+        <v>0.04223098767897454</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007279818878722075</v>
+        <v>0.007279818878722073</v>
       </c>
       <c r="C2" t="n">
         <v>0.008616639735762091</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007482248374160743</v>
+        <v>0.007482248374160744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008959298543540203</v>
+        <v>0.008959298543540205</v>
       </c>
       <c r="F2" t="n">
         <v>0.007602356606811491</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007405614197055516</v>
+        <v>0.007405614197055515</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0073364279676311</v>
+        <v>0.007336427967631097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007305745011380853</v>
+        <v>0.007305745011380852</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009358821270154177</v>
+        <v>0.009358821270154182</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008946388097422261</v>
+        <v>0.008946388097422263</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007761672085800395</v>
+        <v>0.007761672085800397</v>
       </c>
     </row>
     <row r="3">
@@ -7683,28 +7683,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006962970526593422</v>
+        <v>0.006962970526593423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009313944352544588</v>
+        <v>0.009313944352544594</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008397020500069281</v>
+        <v>0.008397020500069283</v>
       </c>
       <c r="E3" t="n">
         <v>0.009876557949030683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00763670407672294</v>
+        <v>0.007636704076722943</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007856531348468246</v>
+        <v>0.007856531348468247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007387147629003494</v>
+        <v>0.007387147629003497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007146827083942675</v>
+        <v>0.007146827083942677</v>
       </c>
       <c r="J3" t="n">
         <v>0.01109821129600282</v>
@@ -7738,13 +7738,13 @@
         <v>0.02845212369982419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0296689203462797</v>
+        <v>0.02966892034627971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02892805864134438</v>
+        <v>0.02892805864134439</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02851963998124474</v>
+        <v>0.02851963998124475</v>
       </c>
       <c r="J4" t="n">
         <v>0.02969818045823462</v>
@@ -7753,7 +7753,7 @@
         <v>0.02849890875183994</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0336503731472241</v>
+        <v>0.03365037314722409</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03357004980781676</v>
+        <v>0.03357004980781674</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03811353143068928</v>
+        <v>0.0381135314306893</v>
       </c>
       <c r="D5" t="n">
         <v>0.06846647440996192</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03811353419235478</v>
+        <v>0.03811353419235479</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03811353419235478</v>
+        <v>0.03811353419235479</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05649672094438347</v>
+        <v>0.05649672094438339</v>
       </c>
       <c r="H5" t="n">
         <v>0.04562226216226101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03811320089387939</v>
+        <v>0.03811320089387941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05965362041654997</v>
+        <v>0.05965362041654999</v>
       </c>
       <c r="K5" t="n">
         <v>0.03728315775093963</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1370322505735507</v>
+        <v>0.1370322505735505</v>
       </c>
     </row>
     <row r="6">
@@ -7806,19 +7806,19 @@
         <v>0.03005885915427998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0291193944275749</v>
+        <v>0.02911939442757489</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03122707080959167</v>
+        <v>0.03122707080959166</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02904243627935577</v>
+        <v>0.02904243627935578</v>
       </c>
       <c r="F6" t="n">
         <v>0.02915904660254274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0314759139967821</v>
+        <v>0.03147591399678209</v>
       </c>
       <c r="H6" t="n">
         <v>0.03079128668283957</v>
@@ -7852,13 +7852,13 @@
         <v>0.03126287716720375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02924281801127574</v>
+        <v>0.02924281801127575</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02924281801127574</v>
+        <v>0.02924281801127575</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03039351355300003</v>
+        <v>0.03039351355300002</v>
       </c>
       <c r="H7" t="n">
         <v>0.02965265184806471</v>
@@ -7873,7 +7873,7 @@
         <v>0.02922350195856026</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03437496635394443</v>
+        <v>0.03437496635394442</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>0.03006528133334229</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03179816273292823</v>
+        <v>0.03179816273292824</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0341218206203312</v>
+        <v>0.03412182062033122</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0313973259048719</v>
+        <v>0.03139732590487192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03037888562019911</v>
+        <v>0.03037888562019912</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03294835304223848</v>
+        <v>0.03294835304223849</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03220749133730302</v>
+        <v>0.03220749133730304</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03179907267720351</v>
+        <v>0.03179907267720352</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03297790126833097</v>
+        <v>0.03297790126833099</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03028509256547113</v>
+        <v>0.03028509256547114</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03846118304630228</v>
+        <v>0.0384611830463023</v>
       </c>
     </row>
     <row r="9">
@@ -7929,7 +7929,7 @@
         <v>0.03211772807600245</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03413615828856995</v>
+        <v>0.03413615828856996</v>
       </c>
       <c r="E9" t="n">
         <v>0.0331406347632042</v>
@@ -7938,22 +7938,22 @@
         <v>0.03211773050434137</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03326667790422752</v>
+        <v>0.03326667790422751</v>
       </c>
       <c r="H9" t="n">
         <v>0.0325258161992922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03211739753919255</v>
+        <v>0.03211739753919256</v>
       </c>
       <c r="J9" t="n">
         <v>0.03329593801618243</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0315830746974631</v>
+        <v>0.03158307469746309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03724813070517189</v>
+        <v>0.03724813070517188</v>
       </c>
     </row>
   </sheetData>
